--- a/Outcome/Appendix/figure_data/fig6.xlsx
+++ b/Outcome/Appendix/figure_data/fig6.xlsx
@@ -116,10 +116,10 @@
     <t xml:space="preserve">Sexually ID</t>
   </si>
   <si>
-    <t xml:space="preserve">Syphilis</t>
+    <t xml:space="preserve">HBV</t>
   </si>
   <si>
-    <t xml:space="preserve">HBV</t>
+    <t xml:space="preserve">Syphilis</t>
   </si>
   <si>
     <t xml:space="preserve">CA</t>
@@ -152,10 +152,10 @@
     <t xml:space="preserve">Rubella</t>
   </si>
   <si>
-    <t xml:space="preserve">Pertussis</t>
+    <t xml:space="preserve">Other tetanus</t>
   </si>
   <si>
-    <t xml:space="preserve">Other tetanus</t>
+    <t xml:space="preserve">Pertussis</t>
   </si>
   <si>
     <t xml:space="preserve">HFMD</t>
@@ -557,25 +557,25 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-4.15</v>
+        <v>-4.14</v>
       </c>
       <c r="E2" t="n">
         <v>-1.49</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.34</v>
+        <v>-1.33</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.32</v>
+        <v>-1.31</v>
       </c>
       <c r="H2" t="s">
         <v>12</v>
       </c>
       <c r="I2" t="n">
-        <v>12198</v>
+        <v>11789</v>
       </c>
       <c r="J2" t="n">
-        <v>0.00330651186039678</v>
+        <v>0.00334851892868981</v>
       </c>
     </row>
     <row r="3">
@@ -589,25 +589,25 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>2.43</v>
+        <v>2.06</v>
       </c>
       <c r="E3" t="n">
-        <v>0.79</v>
+        <v>0.65</v>
       </c>
       <c r="F3" t="n">
-        <v>0.69</v>
+        <v>0.61</v>
       </c>
       <c r="G3" t="n">
-        <v>0.95</v>
+        <v>0.81</v>
       </c>
       <c r="H3" t="s">
         <v>12</v>
       </c>
       <c r="I3" t="n">
-        <v>12198</v>
+        <v>11789</v>
       </c>
       <c r="J3" t="n">
-        <v>0.00330651186039678</v>
+        <v>0.00334851892868981</v>
       </c>
     </row>
     <row r="4">
@@ -621,25 +621,25 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-2.67</v>
+        <v>-2.64</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.77</v>
+        <v>-0.76</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.94</v>
+        <v>-0.93</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.97</v>
+        <v>-0.96</v>
       </c>
       <c r="H4" t="s">
         <v>12</v>
       </c>
       <c r="I4" t="n">
-        <v>12198</v>
+        <v>11789</v>
       </c>
       <c r="J4" t="n">
-        <v>0.00330651186039678</v>
+        <v>0.00334851892868981</v>
       </c>
     </row>
     <row r="5">
@@ -653,25 +653,25 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>1.42</v>
+        <v>1.69</v>
       </c>
       <c r="E5" t="n">
-        <v>0.41</v>
+        <v>0.5</v>
       </c>
       <c r="F5" t="n">
-        <v>0.46</v>
+        <v>0.53</v>
       </c>
       <c r="G5" t="n">
-        <v>0.55</v>
+        <v>0.66</v>
       </c>
       <c r="H5" t="s">
         <v>12</v>
       </c>
       <c r="I5" t="n">
-        <v>12198</v>
+        <v>11789</v>
       </c>
       <c r="J5" t="n">
-        <v>0.00330651186039678</v>
+        <v>0.00334851892868981</v>
       </c>
     </row>
     <row r="6">
@@ -685,25 +685,25 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.5</v>
+        <v>-0.59</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.11</v>
+        <v>-0.13</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.15</v>
+        <v>-0.17</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.25</v>
+        <v>-0.29</v>
       </c>
       <c r="H6" t="s">
         <v>12</v>
       </c>
       <c r="I6" t="n">
-        <v>12198</v>
+        <v>11789</v>
       </c>
       <c r="J6" t="n">
-        <v>0.00330651186039678</v>
+        <v>0.00334851892868981</v>
       </c>
     </row>
     <row r="7">
@@ -717,25 +717,25 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>3.47</v>
+        <v>3.62</v>
       </c>
       <c r="E7" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="F7" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="G7" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="H7" t="s">
         <v>12</v>
       </c>
       <c r="I7" t="n">
-        <v>12198</v>
+        <v>11789</v>
       </c>
       <c r="J7" t="n">
-        <v>0.00330651186039678</v>
+        <v>0.00334851892868981</v>
       </c>
     </row>
     <row r="8">
@@ -749,13 +749,13 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.42</v>
+        <v>-3.1</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.75</v>
+        <v>-1.63</v>
       </c>
       <c r="F8" t="n">
-        <v>0.36</v>
+        <v>0.57</v>
       </c>
       <c r="G8" t="n">
         <v>-2.03</v>
@@ -764,10 +764,10 @@
         <v>12</v>
       </c>
       <c r="I8" t="n">
-        <v>704</v>
+        <v>690</v>
       </c>
       <c r="J8" t="n">
-        <v>0.000285713010209776</v>
+        <v>0.000306863468437758</v>
       </c>
     </row>
     <row r="9">
@@ -781,25 +781,25 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.39</v>
+        <v>-1.81</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1</v>
+        <v>-0.39</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.75</v>
+        <v>-1.89</v>
       </c>
       <c r="G9" t="n">
-        <v>0.46</v>
+        <v>0.48</v>
       </c>
       <c r="H9" t="s">
         <v>12</v>
       </c>
       <c r="I9" t="n">
-        <v>704</v>
+        <v>690</v>
       </c>
       <c r="J9" t="n">
-        <v>0.000285713010209776</v>
+        <v>0.000306863468437758</v>
       </c>
     </row>
     <row r="10">
@@ -810,28 +810,28 @@
         <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.81</v>
+        <v>2.05</v>
       </c>
       <c r="E10" t="n">
-        <v>0.83</v>
+        <v>1.03</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.49</v>
+        <v>0.56</v>
       </c>
       <c r="G10" t="n">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="H10" t="s">
         <v>12</v>
       </c>
       <c r="I10" t="n">
-        <v>704</v>
+        <v>690</v>
       </c>
       <c r="J10" t="n">
-        <v>0.000285713010209776</v>
+        <v>0.000306863468437758</v>
       </c>
     </row>
     <row r="11">
@@ -842,28 +842,28 @@
         <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>2.21</v>
+        <v>1.93</v>
       </c>
       <c r="E11" t="n">
-        <v>0.78</v>
+        <v>0.98</v>
       </c>
       <c r="F11" t="n">
-        <v>1.03</v>
+        <v>0.57</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="H11" t="s">
         <v>12</v>
       </c>
       <c r="I11" t="n">
-        <v>704</v>
+        <v>690</v>
       </c>
       <c r="J11" t="n">
-        <v>0.000285713010209776</v>
+        <v>0.000306863468437758</v>
       </c>
     </row>
     <row r="12">
@@ -877,25 +877,25 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>1.28</v>
+        <v>0.41</v>
       </c>
       <c r="E12" t="n">
-        <v>0.67</v>
+        <v>0.3</v>
       </c>
       <c r="F12" t="n">
-        <v>0.15</v>
+        <v>-0.37</v>
       </c>
       <c r="G12" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="H12" t="s">
         <v>12</v>
       </c>
       <c r="I12" t="n">
-        <v>704</v>
+        <v>690</v>
       </c>
       <c r="J12" t="n">
-        <v>0.000285713010209776</v>
+        <v>0.000306863468437758</v>
       </c>
     </row>
     <row r="13">
@@ -909,25 +909,25 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.42</v>
+        <v>-0.28</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7</v>
+        <v>0.57</v>
       </c>
       <c r="G13" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="H13" t="s">
         <v>12</v>
       </c>
       <c r="I13" t="n">
-        <v>704</v>
+        <v>690</v>
       </c>
       <c r="J13" t="n">
-        <v>0.000285713010209776</v>
+        <v>0.000306863468437758</v>
       </c>
     </row>
     <row r="14">
@@ -941,16 +941,16 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>-5.35</v>
+        <v>-5.33</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.55</v>
+        <v>-1.48</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.8</v>
+        <v>-1.84</v>
       </c>
       <c r="G14" t="n">
-        <v>-2</v>
+        <v>-2.01</v>
       </c>
       <c r="H14" t="s">
         <v>12</v>
@@ -973,16 +973,16 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.09</v>
+        <v>-0.77</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.74</v>
+        <v>-0.67</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.4</v>
+        <v>-0.19</v>
       </c>
       <c r="G15" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="H15" t="s">
         <v>12</v>
@@ -1005,16 +1005,16 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>0.41</v>
+        <v>0.68</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.02</v>
+        <v>0.07</v>
       </c>
       <c r="F16" t="n">
-        <v>0.13</v>
+        <v>0.3</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="H16" t="s">
         <v>12</v>
@@ -1034,19 +1034,19 @@
         <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>2.69</v>
+        <v>0.66</v>
       </c>
       <c r="E17" t="n">
-        <v>1.08</v>
+        <v>0.11</v>
       </c>
       <c r="F17" t="n">
-        <v>0.97</v>
+        <v>0.06</v>
       </c>
       <c r="G17" t="n">
-        <v>0.64</v>
+        <v>0.5</v>
       </c>
       <c r="H17" t="s">
         <v>12</v>
@@ -1066,19 +1066,19 @@
         <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.01</v>
+        <v>3.01</v>
       </c>
       <c r="E18" t="n">
-        <v>0.88</v>
+        <v>1.44</v>
       </c>
       <c r="F18" t="n">
-        <v>0.68</v>
+        <v>1.04</v>
       </c>
       <c r="G18" t="n">
-        <v>0.45</v>
+        <v>0.53</v>
       </c>
       <c r="H18" t="s">
         <v>12</v>
@@ -1101,16 +1101,16 @@
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>1.33</v>
+        <v>1.74</v>
       </c>
       <c r="E19" t="n">
-        <v>0.35</v>
+        <v>0.53</v>
       </c>
       <c r="F19" t="n">
-        <v>0.42</v>
+        <v>0.63</v>
       </c>
       <c r="G19" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="H19" t="s">
         <v>12</v>
@@ -1133,16 +1133,16 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>-5.5</v>
+        <v>-5.43</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.56</v>
+        <v>-1.58</v>
       </c>
       <c r="F20" t="n">
         <v>-2.01</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.93</v>
+        <v>-1.84</v>
       </c>
       <c r="H20" t="s">
         <v>12</v>
@@ -1165,16 +1165,16 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.05</v>
+        <v>-0.22</v>
       </c>
       <c r="E21" t="n">
         <v>-0.59</v>
       </c>
       <c r="F21" t="n">
-        <v>0.54</v>
+        <v>0.48</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.01</v>
+        <v>-0.11</v>
       </c>
       <c r="H21" t="s">
         <v>12</v>
@@ -1197,16 +1197,16 @@
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>1.21</v>
+        <v>1.34</v>
       </c>
       <c r="E22" t="n">
-        <v>0.31</v>
+        <v>0.44</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="G22" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="H22" t="s">
         <v>12</v>
@@ -1229,16 +1229,16 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>2.61</v>
+        <v>2.88</v>
       </c>
       <c r="E23" t="n">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="F23" t="n">
-        <v>0.62</v>
+        <v>0.68</v>
       </c>
       <c r="G23" t="n">
-        <v>0.8</v>
+        <v>0.91</v>
       </c>
       <c r="H23" t="s">
         <v>12</v>
@@ -1261,16 +1261,16 @@
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>0.96</v>
+        <v>0.56</v>
       </c>
       <c r="E24" t="n">
-        <v>0.82</v>
+        <v>0.56</v>
       </c>
       <c r="F24" t="n">
-        <v>0.11</v>
+        <v>0.17</v>
       </c>
       <c r="G24" t="n">
-        <v>0.03</v>
+        <v>-0.17</v>
       </c>
       <c r="H24" t="s">
         <v>12</v>
@@ -1293,16 +1293,16 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>0.78</v>
+        <v>0.86</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.18</v>
+        <v>-0.11</v>
       </c>
       <c r="F25" t="n">
-        <v>0.35</v>
+        <v>0.31</v>
       </c>
       <c r="G25" t="n">
-        <v>0.61</v>
+        <v>0.66</v>
       </c>
       <c r="H25" t="s">
         <v>12</v>
@@ -1325,13 +1325,13 @@
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.29</v>
+        <v>-2.46</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.31</v>
+        <v>-0.42</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.18</v>
+        <v>-0.24</v>
       </c>
       <c r="G26" t="n">
         <v>-1.8</v>
@@ -1357,16 +1357,16 @@
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.14</v>
+        <v>-0.1</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.11</v>
+        <v>-0.08</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.29</v>
+        <v>-0.28</v>
       </c>
       <c r="G27" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="H27" t="s">
         <v>12</v>
@@ -1389,16 +1389,16 @@
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>-2.92</v>
+        <v>-2.93</v>
       </c>
       <c r="E28" t="n">
-        <v>-1.38</v>
+        <v>-1.37</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.41</v>
+        <v>-1.4</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.13</v>
+        <v>-0.16</v>
       </c>
       <c r="H28" t="s">
         <v>12</v>
@@ -1421,16 +1421,16 @@
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>0.44</v>
+        <v>0.49</v>
       </c>
       <c r="E29" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="F29" t="n">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="G29" t="n">
-        <v>0.23</v>
+        <v>0.26</v>
       </c>
       <c r="H29" t="s">
         <v>12</v>
@@ -1453,16 +1453,16 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>0.24</v>
+        <v>0.33</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.01</v>
+        <v>0.04</v>
       </c>
       <c r="F30" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="G30" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="H30" t="s">
         <v>12</v>
@@ -1485,13 +1485,13 @@
         <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>4.67</v>
+        <v>4.66</v>
       </c>
       <c r="E31" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="F31" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="G31" t="n">
         <v>1.25</v>
@@ -1517,16 +1517,16 @@
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>-5.69</v>
+        <v>-5.59</v>
       </c>
       <c r="E32" t="n">
-        <v>-1.95</v>
+        <v>-1.89</v>
       </c>
       <c r="F32" t="n">
-        <v>-1.71</v>
+        <v>-1.67</v>
       </c>
       <c r="G32" t="n">
-        <v>-2.03</v>
+        <v>-2.02</v>
       </c>
       <c r="H32" t="s">
         <v>12</v>
@@ -1546,19 +1546,19 @@
         <v>13</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>1.87</v>
+        <v>2.25</v>
       </c>
       <c r="E33" t="n">
-        <v>0.78</v>
+        <v>0.99</v>
       </c>
       <c r="F33" t="n">
-        <v>0.59</v>
+        <v>0.73</v>
       </c>
       <c r="G33" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="H33" t="s">
         <v>12</v>
@@ -1581,16 +1581,16 @@
         <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.1</v>
+        <v>-0.29</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.03</v>
+        <v>-0.13</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.4</v>
+        <v>-0.47</v>
       </c>
       <c r="G34" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="H34" t="s">
         <v>12</v>
@@ -1613,16 +1613,16 @@
         <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="E35" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="F35" t="n">
         <v>0.28</v>
       </c>
-      <c r="F35" t="n">
-        <v>0.33</v>
-      </c>
       <c r="G35" t="n">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="H35" t="s">
         <v>12</v>
@@ -1645,16 +1645,16 @@
         <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>0.46</v>
+        <v>0.38</v>
       </c>
       <c r="E36" t="n">
-        <v>0.26</v>
+        <v>0.22</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="G36" t="n">
-        <v>0.23</v>
+        <v>0.2</v>
       </c>
       <c r="H36" t="s">
         <v>12</v>
@@ -1674,19 +1674,19 @@
         <v>17</v>
       </c>
       <c r="C37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="E37" t="n">
-        <v>0.66</v>
+        <v>0.54</v>
       </c>
       <c r="F37" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="G37" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="H37" t="s">
         <v>12</v>
@@ -1709,16 +1709,16 @@
         <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>-4.92</v>
+        <v>-2.8</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.81</v>
+        <v>-1.1</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.75</v>
+        <v>-1.59</v>
       </c>
       <c r="G38" t="n">
-        <v>-1.37</v>
+        <v>-0.1</v>
       </c>
       <c r="H38" t="s">
         <v>12</v>
@@ -1727,7 +1727,7 @@
         <v>1</v>
       </c>
       <c r="J38" t="n">
-        <v>0.000391696043869957</v>
+        <v>0.000398565165404544</v>
       </c>
     </row>
     <row r="39">
@@ -1741,16 +1741,16 @@
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>1.59</v>
+        <v>1.71</v>
       </c>
       <c r="E39" t="n">
-        <v>0.71</v>
+        <v>0.85</v>
       </c>
       <c r="F39" t="n">
-        <v>0.18</v>
+        <v>0.28</v>
       </c>
       <c r="G39" t="n">
-        <v>0.71</v>
+        <v>0.57</v>
       </c>
       <c r="H39" t="s">
         <v>12</v>
@@ -1759,7 +1759,7 @@
         <v>1</v>
       </c>
       <c r="J39" t="n">
-        <v>0.000391696043869957</v>
+        <v>0.000398565165404544</v>
       </c>
     </row>
     <row r="40">
@@ -1773,16 +1773,16 @@
         <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.26</v>
+        <v>-3.02</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.01</v>
+        <v>-0.76</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.37</v>
+        <v>-0.59</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.88</v>
+        <v>-1.67</v>
       </c>
       <c r="H40" t="s">
         <v>12</v>
@@ -1791,7 +1791,7 @@
         <v>1</v>
       </c>
       <c r="J40" t="n">
-        <v>0.000391696043869957</v>
+        <v>0.000398565165404544</v>
       </c>
     </row>
     <row r="41">
@@ -1805,16 +1805,16 @@
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>1.66</v>
+        <v>1.89</v>
       </c>
       <c r="E41" t="n">
-        <v>0.88</v>
+        <v>1.28</v>
       </c>
       <c r="F41" t="n">
         <v>0.57</v>
       </c>
       <c r="G41" t="n">
-        <v>0.21</v>
+        <v>0.03</v>
       </c>
       <c r="H41" t="s">
         <v>12</v>
@@ -1823,7 +1823,7 @@
         <v>1</v>
       </c>
       <c r="J41" t="n">
-        <v>0.000391696043869957</v>
+        <v>0.000398565165404544</v>
       </c>
     </row>
     <row r="42">
@@ -1837,16 +1837,16 @@
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>0.75</v>
+        <v>0.32</v>
       </c>
       <c r="E42" t="n">
-        <v>0.58</v>
+        <v>0.49</v>
       </c>
       <c r="F42" t="n">
-        <v>0.2</v>
+        <v>0.02</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.02</v>
+        <v>-0.19</v>
       </c>
       <c r="H42" t="s">
         <v>12</v>
@@ -1855,7 +1855,7 @@
         <v>1</v>
       </c>
       <c r="J42" t="n">
-        <v>0.000391696043869957</v>
+        <v>0.000398565165404544</v>
       </c>
     </row>
     <row r="43">
@@ -1869,16 +1869,16 @@
         <v>1</v>
       </c>
       <c r="D43" t="n">
-        <v>2.18</v>
+        <v>1.9</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.35</v>
+        <v>-0.77</v>
       </c>
       <c r="F43" t="n">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="G43" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="H43" t="s">
         <v>12</v>
@@ -1887,7 +1887,7 @@
         <v>1</v>
       </c>
       <c r="J43" t="n">
-        <v>0.000391696043869957</v>
+        <v>0.000398565165404544</v>
       </c>
     </row>
     <row r="44">
@@ -1901,25 +1901,25 @@
         <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.75</v>
+        <v>-0.8</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.06</v>
+        <v>-0.11</v>
       </c>
       <c r="F44" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="G44" t="n">
-        <v>-0.74</v>
+        <v>-0.72</v>
       </c>
       <c r="H44" t="s">
         <v>25</v>
       </c>
       <c r="I44" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="J44" t="n">
-        <v>0.0000820845308811254</v>
+        <v>0.0000815030114164145</v>
       </c>
     </row>
     <row r="45">
@@ -1933,25 +1933,25 @@
         <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>0.24</v>
+        <v>0.51</v>
       </c>
       <c r="E45" t="n">
-        <v>0.45</v>
+        <v>0.58</v>
       </c>
       <c r="F45" t="n">
-        <v>-1.33</v>
+        <v>-1.31</v>
       </c>
       <c r="G45" t="n">
-        <v>1.12</v>
+        <v>1.23</v>
       </c>
       <c r="H45" t="s">
         <v>25</v>
       </c>
       <c r="I45" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="J45" t="n">
-        <v>0.0000820845308811254</v>
+        <v>0.0000815030114164145</v>
       </c>
     </row>
     <row r="46">
@@ -1965,25 +1965,25 @@
         <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>-2.46</v>
+        <v>-2.38</v>
       </c>
       <c r="E46" t="n">
-        <v>-1.15</v>
+        <v>-1.13</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.44</v>
+        <v>-0.42</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.87</v>
+        <v>-0.82</v>
       </c>
       <c r="H46" t="s">
         <v>25</v>
       </c>
       <c r="I46" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="J46" t="n">
-        <v>0.0000820845308811254</v>
+        <v>0.0000815030114164145</v>
       </c>
     </row>
     <row r="47">
@@ -1997,25 +1997,25 @@
         <v>0</v>
       </c>
       <c r="D47" t="n">
-        <v>1.7</v>
+        <v>1.23</v>
       </c>
       <c r="E47" t="n">
-        <v>0.53</v>
+        <v>0.41</v>
       </c>
       <c r="F47" t="n">
-        <v>0.71</v>
+        <v>0.6</v>
       </c>
       <c r="G47" t="n">
-        <v>0.46</v>
+        <v>0.22</v>
       </c>
       <c r="H47" t="s">
         <v>25</v>
       </c>
       <c r="I47" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="J47" t="n">
-        <v>0.0000820845308811254</v>
+        <v>0.0000815030114164145</v>
       </c>
     </row>
     <row r="48">
@@ -2029,25 +2029,25 @@
         <v>1</v>
       </c>
       <c r="D48" t="n">
-        <v>3.95</v>
+        <v>4.07</v>
       </c>
       <c r="E48" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="F48" t="n">
-        <v>1.51</v>
+        <v>1.59</v>
       </c>
       <c r="G48" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="H48" t="s">
         <v>25</v>
       </c>
       <c r="I48" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="J48" t="n">
-        <v>0.0000820845308811254</v>
+        <v>0.0000815030114164145</v>
       </c>
     </row>
     <row r="49">
@@ -2061,25 +2061,25 @@
         <v>0</v>
       </c>
       <c r="D49" t="n">
-        <v>-2.69</v>
+        <v>-2.63</v>
       </c>
       <c r="E49" t="n">
-        <v>-1.15</v>
+        <v>-1.13</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.5</v>
+        <v>-0.48</v>
       </c>
       <c r="G49" t="n">
-        <v>-1.05</v>
+        <v>-1.01</v>
       </c>
       <c r="H49" t="s">
         <v>25</v>
       </c>
       <c r="I49" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="J49" t="n">
-        <v>0.0000820845308811254</v>
+        <v>0.0000815030114164145</v>
       </c>
     </row>
     <row r="50">
@@ -2093,25 +2093,25 @@
         <v>0</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.78</v>
+        <v>-0.6</v>
       </c>
       <c r="E50" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="F50" t="n">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="G50" t="n">
-        <v>-1.55</v>
+        <v>-1.37</v>
       </c>
       <c r="H50" t="s">
         <v>25</v>
       </c>
       <c r="I50" t="n">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="J50" t="n">
-        <v>0.000933508510238958</v>
+        <v>0.000938296990961405</v>
       </c>
     </row>
     <row r="51">
@@ -2125,25 +2125,25 @@
         <v>0</v>
       </c>
       <c r="D51" t="n">
-        <v>0.24</v>
+        <v>0.02</v>
       </c>
       <c r="E51" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="F51" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="G51" t="n">
-        <v>-0.52</v>
+        <v>-0.72</v>
       </c>
       <c r="H51" t="s">
         <v>25</v>
       </c>
       <c r="I51" t="n">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="J51" t="n">
-        <v>0.000933508510238958</v>
+        <v>0.000938296990961405</v>
       </c>
     </row>
     <row r="52">
@@ -2157,7 +2157,7 @@
         <v>0</v>
       </c>
       <c r="D52" t="n">
-        <v>0.49</v>
+        <v>0.45</v>
       </c>
       <c r="E52" t="n">
         <v>0.32</v>
@@ -2166,16 +2166,16 @@
         <v>0.4</v>
       </c>
       <c r="G52" t="n">
-        <v>-0.23</v>
+        <v>-0.27</v>
       </c>
       <c r="H52" t="s">
         <v>25</v>
       </c>
       <c r="I52" t="n">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="J52" t="n">
-        <v>0.000933508510238958</v>
+        <v>0.000938296990961405</v>
       </c>
     </row>
     <row r="53">
@@ -2189,25 +2189,25 @@
         <v>1</v>
       </c>
       <c r="D53" t="n">
-        <v>1.96</v>
+        <v>2.01</v>
       </c>
       <c r="E53" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="F53" t="n">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="G53" t="n">
-        <v>0.98</v>
+        <v>1.03</v>
       </c>
       <c r="H53" t="s">
         <v>25</v>
       </c>
       <c r="I53" t="n">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="J53" t="n">
-        <v>0.000933508510238958</v>
+        <v>0.000938296990961405</v>
       </c>
     </row>
     <row r="54">
@@ -2221,7 +2221,7 @@
         <v>0</v>
       </c>
       <c r="D54" t="n">
-        <v>1.03</v>
+        <v>0.99</v>
       </c>
       <c r="E54" t="n">
         <v>0.42</v>
@@ -2230,16 +2230,16 @@
         <v>0.43</v>
       </c>
       <c r="G54" t="n">
-        <v>0.18</v>
+        <v>0.14</v>
       </c>
       <c r="H54" t="s">
         <v>25</v>
       </c>
       <c r="I54" t="n">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="J54" t="n">
-        <v>0.000933508510238958</v>
+        <v>0.000938296990961405</v>
       </c>
     </row>
     <row r="55">
@@ -2253,7 +2253,7 @@
         <v>0</v>
       </c>
       <c r="D55" t="n">
-        <v>-2.94</v>
+        <v>-2.88</v>
       </c>
       <c r="E55" t="n">
         <v>-2.04</v>
@@ -2262,16 +2262,16 @@
         <v>-2.04</v>
       </c>
       <c r="G55" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="H55" t="s">
         <v>25</v>
       </c>
       <c r="I55" t="n">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="J55" t="n">
-        <v>0.000933508510238958</v>
+        <v>0.000938296990961405</v>
       </c>
     </row>
     <row r="56">
@@ -2285,16 +2285,16 @@
         <v>0</v>
       </c>
       <c r="D56" t="n">
-        <v>-2.84</v>
+        <v>-3.02</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.57</v>
+        <v>-0.6</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.85</v>
+        <v>-0.92</v>
       </c>
       <c r="G56" t="n">
-        <v>-1.42</v>
+        <v>-1.49</v>
       </c>
       <c r="H56" t="s">
         <v>25</v>
@@ -2303,7 +2303,7 @@
         <v>93</v>
       </c>
       <c r="J56" t="n">
-        <v>0.000750478127193938</v>
+        <v>0.0007695171900211</v>
       </c>
     </row>
     <row r="57">
@@ -2317,16 +2317,16 @@
         <v>0</v>
       </c>
       <c r="D57" t="n">
-        <v>3.32</v>
+        <v>2.86</v>
       </c>
       <c r="E57" t="n">
-        <v>1.12</v>
+        <v>0.94</v>
       </c>
       <c r="F57" t="n">
-        <v>0.98</v>
+        <v>0.87</v>
       </c>
       <c r="G57" t="n">
-        <v>1.22</v>
+        <v>1.06</v>
       </c>
       <c r="H57" t="s">
         <v>25</v>
@@ -2335,7 +2335,7 @@
         <v>93</v>
       </c>
       <c r="J57" t="n">
-        <v>0.000750478127193938</v>
+        <v>0.0007695171900211</v>
       </c>
     </row>
     <row r="58">
@@ -2349,16 +2349,16 @@
         <v>0</v>
       </c>
       <c r="D58" t="n">
-        <v>-3.4</v>
+        <v>-3.45</v>
       </c>
       <c r="E58" t="n">
-        <v>-1.37</v>
+        <v>-1.43</v>
       </c>
       <c r="F58" t="n">
         <v>-1.22</v>
       </c>
       <c r="G58" t="n">
-        <v>-0.81</v>
+        <v>-0.79</v>
       </c>
       <c r="H58" t="s">
         <v>25</v>
@@ -2367,7 +2367,7 @@
         <v>93</v>
       </c>
       <c r="J58" t="n">
-        <v>0.000750478127193938</v>
+        <v>0.0007695171900211</v>
       </c>
     </row>
     <row r="59">
@@ -2381,16 +2381,16 @@
         <v>0</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.38</v>
+        <v>0.34</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.32</v>
+        <v>-0.02</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.14</v>
+        <v>0.07</v>
       </c>
       <c r="G59" t="n">
-        <v>0.08</v>
+        <v>0.29</v>
       </c>
       <c r="H59" t="s">
         <v>25</v>
@@ -2399,7 +2399,7 @@
         <v>93</v>
       </c>
       <c r="J59" t="n">
-        <v>0.000750478127193938</v>
+        <v>0.0007695171900211</v>
       </c>
     </row>
     <row r="60">
@@ -2413,16 +2413,16 @@
         <v>0</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.15</v>
+        <v>-0.37</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.06</v>
+        <v>-0.18</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.11</v>
+        <v>-0.16</v>
       </c>
       <c r="G60" t="n">
-        <v>0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="H60" t="s">
         <v>25</v>
@@ -2431,7 +2431,7 @@
         <v>93</v>
       </c>
       <c r="J60" t="n">
-        <v>0.000750478127193938</v>
+        <v>0.0007695171900211</v>
       </c>
     </row>
     <row r="61">
@@ -2445,16 +2445,16 @@
         <v>1</v>
       </c>
       <c r="D61" t="n">
-        <v>3.45</v>
+        <v>3.63</v>
       </c>
       <c r="E61" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="F61" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="G61" t="n">
-        <v>0.91</v>
+        <v>0.97</v>
       </c>
       <c r="H61" t="s">
         <v>25</v>
@@ -2463,7 +2463,7 @@
         <v>93</v>
       </c>
       <c r="J61" t="n">
-        <v>0.000750478127193938</v>
+        <v>0.0007695171900211</v>
       </c>
     </row>
     <row r="62">
@@ -2474,19 +2474,19 @@
         <v>11</v>
       </c>
       <c r="C62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D62" t="n">
-        <v>1.17</v>
+        <v>1.56</v>
       </c>
       <c r="E62" t="n">
-        <v>0.99</v>
+        <v>0.47</v>
       </c>
       <c r="F62" t="n">
-        <v>0.78</v>
+        <v>0.53</v>
       </c>
       <c r="G62" t="n">
-        <v>-0.6</v>
+        <v>0.57</v>
       </c>
       <c r="H62" t="s">
         <v>25</v>
@@ -2495,7 +2495,7 @@
         <v>1</v>
       </c>
       <c r="J62" t="n">
-        <v>0.0000113005842402052</v>
+        <v>0.0000113329857884358</v>
       </c>
     </row>
     <row r="63">
@@ -2506,16 +2506,16 @@
         <v>13</v>
       </c>
       <c r="C63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D63" t="n">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="E63" t="n">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
       <c r="F63" t="n">
-        <v>0.83</v>
+        <v>0.56</v>
       </c>
       <c r="G63"/>
       <c r="H63" t="s">
@@ -2525,7 +2525,7 @@
         <v>1</v>
       </c>
       <c r="J63" t="n">
-        <v>0.0000113005842402052</v>
+        <v>0.0000113329857884358</v>
       </c>
     </row>
     <row r="64">
@@ -2539,16 +2539,16 @@
         <v>0</v>
       </c>
       <c r="D64" t="n">
-        <v>-2.26</v>
+        <v>-2.87</v>
       </c>
       <c r="E64" t="n">
-        <v>-1.4</v>
+        <v>-1.43</v>
       </c>
       <c r="F64" t="n">
-        <v>-1.8</v>
+        <v>-1.95</v>
       </c>
       <c r="G64" t="n">
-        <v>0.94</v>
+        <v>0.5</v>
       </c>
       <c r="H64" t="s">
         <v>25</v>
@@ -2557,7 +2557,7 @@
         <v>1</v>
       </c>
       <c r="J64" t="n">
-        <v>0.0000113005842402052</v>
+        <v>0.0000113329857884358</v>
       </c>
     </row>
     <row r="65">
@@ -2571,16 +2571,16 @@
         <v>0</v>
       </c>
       <c r="D65" t="n">
-        <v>-2.4</v>
+        <v>-0.95</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.69</v>
+        <v>0.31</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.26</v>
+        <v>0.52</v>
       </c>
       <c r="G65" t="n">
-        <v>-1.45</v>
+        <v>-1.78</v>
       </c>
       <c r="H65" t="s">
         <v>25</v>
@@ -2589,7 +2589,7 @@
         <v>1</v>
       </c>
       <c r="J65" t="n">
-        <v>0.0000113005842402052</v>
+        <v>0.0000113329857884358</v>
       </c>
     </row>
     <row r="66">
@@ -2603,16 +2603,16 @@
         <v>0</v>
       </c>
       <c r="D66" t="n">
-        <v>0.05</v>
+        <v>-0.8</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.5</v>
+        <v>-1.07</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.17</v>
+        <v>-0.2</v>
       </c>
       <c r="G66" t="n">
-        <v>0.72</v>
+        <v>0.47</v>
       </c>
       <c r="H66" t="s">
         <v>25</v>
@@ -2621,7 +2621,7 @@
         <v>1</v>
       </c>
       <c r="J66" t="n">
-        <v>0.0000113005842402052</v>
+        <v>0.0000113329857884358</v>
       </c>
     </row>
     <row r="67">
@@ -2635,16 +2635,16 @@
         <v>0</v>
       </c>
       <c r="D67" t="n">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="E67" t="n">
-        <v>0.61</v>
+        <v>0.75</v>
       </c>
       <c r="F67" t="n">
-        <v>0.61</v>
+        <v>0.55</v>
       </c>
       <c r="G67" t="n">
-        <v>0.39</v>
+        <v>0.24</v>
       </c>
       <c r="H67" t="s">
         <v>25</v>
@@ -2653,7 +2653,7 @@
         <v>1</v>
       </c>
       <c r="J67" t="n">
-        <v>0.0000113005842402052</v>
+        <v>0.0000113329857884358</v>
       </c>
     </row>
     <row r="68">
@@ -2667,25 +2667,25 @@
         <v>0</v>
       </c>
       <c r="D68" t="n">
-        <v>-1.19</v>
+        <v>-1.16</v>
       </c>
       <c r="E68" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="F68" t="n">
-        <v>0.32</v>
+        <v>0.29</v>
       </c>
       <c r="G68" t="n">
-        <v>-1.94</v>
+        <v>-1.87</v>
       </c>
       <c r="H68" t="s">
         <v>25</v>
       </c>
       <c r="I68" t="n">
-        <v>777</v>
+        <v>761</v>
       </c>
       <c r="J68" t="n">
-        <v>0.0135613927916921</v>
+        <v>0.013649489713558</v>
       </c>
     </row>
     <row r="69">
@@ -2699,25 +2699,25 @@
         <v>1</v>
       </c>
       <c r="D69" t="n">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="E69" t="n">
-        <v>0.91</v>
+        <v>0.84</v>
       </c>
       <c r="F69" t="n">
-        <v>0.86</v>
+        <v>0.79</v>
       </c>
       <c r="G69" t="n">
-        <v>0.86</v>
+        <v>0.93</v>
       </c>
       <c r="H69" t="s">
         <v>25</v>
       </c>
       <c r="I69" t="n">
-        <v>777</v>
+        <v>761</v>
       </c>
       <c r="J69" t="n">
-        <v>0.0135613927916921</v>
+        <v>0.013649489713558</v>
       </c>
     </row>
     <row r="70">
@@ -2731,25 +2731,25 @@
         <v>0</v>
       </c>
       <c r="D70" t="n">
-        <v>1.54</v>
+        <v>1.85</v>
       </c>
       <c r="E70" t="n">
-        <v>0.51</v>
+        <v>0.64</v>
       </c>
       <c r="F70" t="n">
-        <v>0.42</v>
+        <v>0.52</v>
       </c>
       <c r="G70" t="n">
-        <v>0.61</v>
+        <v>0.7</v>
       </c>
       <c r="H70" t="s">
         <v>25</v>
       </c>
       <c r="I70" t="n">
-        <v>777</v>
+        <v>761</v>
       </c>
       <c r="J70" t="n">
-        <v>0.0135613927916921</v>
+        <v>0.013649489713558</v>
       </c>
     </row>
     <row r="71">
@@ -2763,25 +2763,25 @@
         <v>0</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.39</v>
+        <v>-0.21</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.61</v>
+        <v>-0.56</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.1</v>
+        <v>-0.02</v>
       </c>
       <c r="G71" t="n">
-        <v>0.32</v>
+        <v>0.38</v>
       </c>
       <c r="H71" t="s">
         <v>25</v>
       </c>
       <c r="I71" t="n">
-        <v>777</v>
+        <v>761</v>
       </c>
       <c r="J71" t="n">
-        <v>0.0135613927916921</v>
+        <v>0.013649489713558</v>
       </c>
     </row>
     <row r="72">
@@ -2795,25 +2795,25 @@
         <v>0</v>
       </c>
       <c r="D72" t="n">
-        <v>1.17</v>
+        <v>0.77</v>
       </c>
       <c r="E72" t="n">
-        <v>0.51</v>
+        <v>0.45</v>
       </c>
       <c r="F72" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="G72" t="n">
-        <v>0.21</v>
+        <v>-0.08</v>
       </c>
       <c r="H72" t="s">
         <v>25</v>
       </c>
       <c r="I72" t="n">
-        <v>777</v>
+        <v>761</v>
       </c>
       <c r="J72" t="n">
-        <v>0.0135613927916921</v>
+        <v>0.013649489713558</v>
       </c>
     </row>
     <row r="73">
@@ -2827,25 +2827,25 @@
         <v>0</v>
       </c>
       <c r="D73" t="n">
-        <v>-3.76</v>
+        <v>-3.81</v>
       </c>
       <c r="E73" t="n">
-        <v>-1.75</v>
+        <v>-1.79</v>
       </c>
       <c r="F73" t="n">
-        <v>-1.94</v>
+        <v>-1.97</v>
       </c>
       <c r="G73" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="H73" t="s">
         <v>25</v>
       </c>
       <c r="I73" t="n">
-        <v>777</v>
+        <v>761</v>
       </c>
       <c r="J73" t="n">
-        <v>0.0135613927916921</v>
+        <v>0.013649489713558</v>
       </c>
     </row>
     <row r="74">
@@ -2859,25 +2859,25 @@
         <v>0</v>
       </c>
       <c r="D74" t="n">
-        <v>-4.84</v>
+        <v>-4.75</v>
       </c>
       <c r="E74" t="n">
-        <v>-1.93</v>
+        <v>-1.89</v>
       </c>
       <c r="F74" t="n">
-        <v>-1.28</v>
+        <v>-1.3</v>
       </c>
       <c r="G74" t="n">
-        <v>-1.64</v>
+        <v>-1.55</v>
       </c>
       <c r="H74" t="s">
         <v>25</v>
       </c>
       <c r="I74" t="n">
-        <v>240</v>
+        <v>214</v>
       </c>
       <c r="J74" t="n">
-        <v>0.0532386867790594</v>
+        <v>0.0534599050711966</v>
       </c>
     </row>
     <row r="75">
@@ -2891,25 +2891,25 @@
         <v>0</v>
       </c>
       <c r="D75" t="n">
-        <v>1.12</v>
+        <v>1.38</v>
       </c>
       <c r="E75" t="n">
-        <v>0.47</v>
+        <v>0.64</v>
       </c>
       <c r="F75" t="n">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
       <c r="G75" t="n">
-        <v>0.48</v>
+        <v>0.55</v>
       </c>
       <c r="H75" t="s">
         <v>25</v>
       </c>
       <c r="I75" t="n">
-        <v>240</v>
+        <v>214</v>
       </c>
       <c r="J75" t="n">
-        <v>0.0532386867790594</v>
+        <v>0.0534599050711966</v>
       </c>
     </row>
     <row r="76">
@@ -2923,25 +2923,25 @@
         <v>0</v>
       </c>
       <c r="D76" t="n">
-        <v>2.2</v>
+        <v>1.87</v>
       </c>
       <c r="E76" t="n">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="F76" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="G76" t="n">
-        <v>0.72</v>
+        <v>0.61</v>
       </c>
       <c r="H76" t="s">
         <v>25</v>
       </c>
       <c r="I76" t="n">
-        <v>240</v>
+        <v>214</v>
       </c>
       <c r="J76" t="n">
-        <v>0.0532386867790594</v>
+        <v>0.0534599050711966</v>
       </c>
     </row>
     <row r="77">
@@ -2955,25 +2955,25 @@
         <v>0</v>
       </c>
       <c r="D77" t="n">
-        <v>1.29</v>
+        <v>1.8</v>
       </c>
       <c r="E77" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="F77" t="n">
-        <v>0.23</v>
+        <v>0.45</v>
       </c>
       <c r="G77" t="n">
-        <v>0.49</v>
+        <v>0.71</v>
       </c>
       <c r="H77" t="s">
         <v>25</v>
       </c>
       <c r="I77" t="n">
-        <v>240</v>
+        <v>214</v>
       </c>
       <c r="J77" t="n">
-        <v>0.0532386867790594</v>
+        <v>0.0534599050711966</v>
       </c>
     </row>
     <row r="78">
@@ -2987,25 +2987,25 @@
         <v>1</v>
       </c>
       <c r="D78" t="n">
-        <v>2.22</v>
+        <v>1.94</v>
       </c>
       <c r="E78" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="F78" t="n">
-        <v>0.58</v>
+        <v>0.51</v>
       </c>
       <c r="G78" t="n">
-        <v>0.79</v>
+        <v>0.67</v>
       </c>
       <c r="H78" t="s">
         <v>25</v>
       </c>
       <c r="I78" t="n">
-        <v>240</v>
+        <v>214</v>
       </c>
       <c r="J78" t="n">
-        <v>0.0532386867790594</v>
+        <v>0.0534599050711966</v>
       </c>
     </row>
     <row r="79">
@@ -3019,25 +3019,25 @@
         <v>0</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.98</v>
+        <v>-2.24</v>
       </c>
       <c r="E79" t="n">
-        <v>-0.08</v>
+        <v>-0.15</v>
       </c>
       <c r="F79" t="n">
-        <v>-1.06</v>
+        <v>-1.11</v>
       </c>
       <c r="G79" t="n">
-        <v>-0.84</v>
+        <v>-0.98</v>
       </c>
       <c r="H79" t="s">
         <v>25</v>
       </c>
       <c r="I79" t="n">
-        <v>240</v>
+        <v>214</v>
       </c>
       <c r="J79" t="n">
-        <v>0.0532386867790594</v>
+        <v>0.0534599050711966</v>
       </c>
     </row>
     <row r="80">
@@ -3048,19 +3048,19 @@
         <v>11</v>
       </c>
       <c r="C80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D80" t="n">
-        <v>0.89</v>
+        <v>2.31</v>
       </c>
       <c r="E80" t="n">
-        <v>0.65</v>
+        <v>1.13</v>
       </c>
       <c r="F80" t="n">
-        <v>-0.74</v>
+        <v>0.03</v>
       </c>
       <c r="G80" t="n">
-        <v>0.98</v>
+        <v>1.16</v>
       </c>
       <c r="H80" t="s">
         <v>25</v>
@@ -3080,19 +3080,19 @@
         <v>13</v>
       </c>
       <c r="C81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D81" t="n">
-        <v>1.55</v>
+        <v>0.93</v>
       </c>
       <c r="E81" t="n">
-        <v>-0.2</v>
+        <v>-0.41</v>
       </c>
       <c r="F81" t="n">
-        <v>0.48</v>
+        <v>0.21</v>
       </c>
       <c r="G81" t="n">
-        <v>1.26</v>
+        <v>1.12</v>
       </c>
       <c r="H81" t="s">
         <v>25</v>
@@ -3115,16 +3115,16 @@
         <v>0</v>
       </c>
       <c r="D82" t="n">
-        <v>0.78</v>
+        <v>0.29</v>
       </c>
       <c r="E82" t="n">
-        <v>1.22</v>
+        <v>0.88</v>
       </c>
       <c r="F82" t="n">
-        <v>1.03</v>
+        <v>0.88</v>
       </c>
       <c r="G82" t="n">
-        <v>-1.47</v>
+        <v>-1.46</v>
       </c>
       <c r="H82" t="s">
         <v>25</v>
@@ -3147,16 +3147,16 @@
         <v>0</v>
       </c>
       <c r="D83" t="n">
-        <v>0.3</v>
+        <v>-0.09</v>
       </c>
       <c r="E83" t="n">
-        <v>0</v>
+        <v>-0.15</v>
       </c>
       <c r="F83" t="n">
-        <v>0.47</v>
+        <v>0.28</v>
       </c>
       <c r="G83" t="n">
-        <v>-0.18</v>
+        <v>-0.22</v>
       </c>
       <c r="H83" t="s">
         <v>25</v>
@@ -3179,16 +3179,16 @@
         <v>0</v>
       </c>
       <c r="D84" t="n">
-        <v>-0.01</v>
+        <v>0.3</v>
       </c>
       <c r="E84" t="n">
-        <v>0.08</v>
+        <v>0.21</v>
       </c>
       <c r="F84" t="n">
-        <v>0.42</v>
+        <v>0.55</v>
       </c>
       <c r="G84" t="n">
-        <v>-0.51</v>
+        <v>-0.46</v>
       </c>
       <c r="H84" t="s">
         <v>25</v>
@@ -3211,16 +3211,16 @@
         <v>0</v>
       </c>
       <c r="D85" t="n">
-        <v>-3.5</v>
+        <v>-3.73</v>
       </c>
       <c r="E85" t="n">
-        <v>-1.75</v>
+        <v>-1.65</v>
       </c>
       <c r="F85" t="n">
-        <v>-1.66</v>
+        <v>-1.95</v>
       </c>
       <c r="G85" t="n">
-        <v>-0.09</v>
+        <v>-0.13</v>
       </c>
       <c r="H85" t="s">
         <v>25</v>
@@ -3243,16 +3243,16 @@
         <v>0</v>
       </c>
       <c r="D86" t="n">
-        <v>0.93</v>
+        <v>1.09</v>
       </c>
       <c r="E86" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="F86" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="G86" t="n">
-        <v>-1.9</v>
+        <v>-1.84</v>
       </c>
       <c r="H86" t="s">
         <v>33</v>
@@ -3275,16 +3275,16 @@
         <v>0</v>
       </c>
       <c r="D87" t="n">
-        <v>-1.92</v>
+        <v>-2.04</v>
       </c>
       <c r="E87" t="n">
-        <v>-0.97</v>
+        <v>-0.98</v>
       </c>
       <c r="F87" t="n">
         <v>-1.01</v>
       </c>
       <c r="G87" t="n">
-        <v>0.06</v>
+        <v>-0.06</v>
       </c>
       <c r="H87" t="s">
         <v>33</v>
@@ -3307,16 +3307,16 @@
         <v>0</v>
       </c>
       <c r="D88" t="n">
-        <v>-2.19</v>
+        <v>-2.05</v>
       </c>
       <c r="E88" t="n">
-        <v>-1.26</v>
+        <v>-1.18</v>
       </c>
       <c r="F88" t="n">
-        <v>-1.2</v>
+        <v>-1.16</v>
       </c>
       <c r="G88" t="n">
-        <v>0.27</v>
+        <v>0.29</v>
       </c>
       <c r="H88" t="s">
         <v>33</v>
@@ -3339,16 +3339,16 @@
         <v>1</v>
       </c>
       <c r="D89" t="n">
-        <v>2.48</v>
+        <v>2.57</v>
       </c>
       <c r="E89" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="F89" t="n">
         <v>0.74</v>
       </c>
       <c r="G89" t="n">
-        <v>1.09</v>
+        <v>1.19</v>
       </c>
       <c r="H89" t="s">
         <v>33</v>
@@ -3371,16 +3371,16 @@
         <v>0</v>
       </c>
       <c r="D90" t="n">
-        <v>0.5</v>
+        <v>0.17</v>
       </c>
       <c r="E90" t="n">
-        <v>0.08</v>
+        <v>-0.04</v>
       </c>
       <c r="F90" t="n">
-        <v>0.17</v>
+        <v>0.07</v>
       </c>
       <c r="G90" t="n">
-        <v>0.24</v>
+        <v>0.14</v>
       </c>
       <c r="H90" t="s">
         <v>33</v>
@@ -3403,16 +3403,16 @@
         <v>0</v>
       </c>
       <c r="D91" t="n">
-        <v>0.21</v>
+        <v>0.27</v>
       </c>
       <c r="E91" t="n">
-        <v>0.06</v>
+        <v>0.07</v>
       </c>
       <c r="F91" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="G91" t="n">
-        <v>0.24</v>
+        <v>0.27</v>
       </c>
       <c r="H91" t="s">
         <v>33</v>
@@ -3435,25 +3435,25 @@
         <v>0</v>
       </c>
       <c r="D92" t="n">
-        <v>-3.38</v>
+        <v>1.61</v>
       </c>
       <c r="E92" t="n">
-        <v>-1.85</v>
+        <v>0.39</v>
       </c>
       <c r="F92" t="n">
-        <v>-1.94</v>
+        <v>0.54</v>
       </c>
       <c r="G92" t="n">
-        <v>0.42</v>
+        <v>0.68</v>
       </c>
       <c r="H92" t="s">
         <v>33</v>
       </c>
       <c r="I92" t="n">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="J92" t="n">
-        <v>0.0000873675289841777</v>
+        <v>0.000418808300019037</v>
       </c>
     </row>
     <row r="93">
@@ -3467,25 +3467,25 @@
         <v>0</v>
       </c>
       <c r="D93" t="n">
-        <v>-1.02</v>
+        <v>-1.59</v>
       </c>
       <c r="E93" t="n">
-        <v>0.06</v>
+        <v>-0.3</v>
       </c>
       <c r="F93" t="n">
-        <v>0.33</v>
+        <v>0.04</v>
       </c>
       <c r="G93" t="n">
-        <v>-1.41</v>
+        <v>-1.34</v>
       </c>
       <c r="H93" t="s">
         <v>33</v>
       </c>
       <c r="I93" t="n">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="J93" t="n">
-        <v>0.0000873675289841777</v>
+        <v>0.000418808300019037</v>
       </c>
     </row>
     <row r="94">
@@ -3496,28 +3496,28 @@
         <v>14</v>
       </c>
       <c r="C94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D94" t="n">
-        <v>2.85</v>
+        <v>-4.94</v>
       </c>
       <c r="E94" t="n">
-        <v>1.09</v>
+        <v>-1.82</v>
       </c>
       <c r="F94" t="n">
-        <v>0.81</v>
+        <v>-1.93</v>
       </c>
       <c r="G94" t="n">
-        <v>0.96</v>
+        <v>-1.19</v>
       </c>
       <c r="H94" t="s">
         <v>33</v>
       </c>
       <c r="I94" t="n">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="J94" t="n">
-        <v>0.0000873675289841777</v>
+        <v>0.000418808300019037</v>
       </c>
     </row>
     <row r="95">
@@ -3528,28 +3528,28 @@
         <v>15</v>
       </c>
       <c r="C95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D95" t="n">
-        <v>-0.65</v>
+        <v>3.05</v>
       </c>
       <c r="E95" t="n">
-        <v>0.1</v>
+        <v>1.12</v>
       </c>
       <c r="F95" t="n">
-        <v>0.34</v>
+        <v>0.94</v>
       </c>
       <c r="G95" t="n">
-        <v>-1.1</v>
+        <v>0.99</v>
       </c>
       <c r="H95" t="s">
         <v>33</v>
       </c>
       <c r="I95" t="n">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="J95" t="n">
-        <v>0.0000873675289841777</v>
+        <v>0.000418808300019037</v>
       </c>
     </row>
     <row r="96">
@@ -3563,25 +3563,25 @@
         <v>0</v>
       </c>
       <c r="D96" t="n">
-        <v>0.64</v>
+        <v>0.98</v>
       </c>
       <c r="E96" t="n">
-        <v>-0.01</v>
+        <v>0.27</v>
       </c>
       <c r="F96" t="n">
-        <v>-0.12</v>
+        <v>0.27</v>
       </c>
       <c r="G96" t="n">
-        <v>0.77</v>
+        <v>0.44</v>
       </c>
       <c r="H96" t="s">
         <v>33</v>
       </c>
       <c r="I96" t="n">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="J96" t="n">
-        <v>0.0000873675289841777</v>
+        <v>0.000418808300019037</v>
       </c>
     </row>
     <row r="97">
@@ -3595,25 +3595,25 @@
         <v>0</v>
       </c>
       <c r="D97" t="n">
-        <v>1.56</v>
+        <v>0.9</v>
       </c>
       <c r="E97" t="n">
-        <v>0.62</v>
+        <v>0.33</v>
       </c>
       <c r="F97" t="n">
-        <v>0.58</v>
+        <v>0.15</v>
       </c>
       <c r="G97" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="H97" t="s">
         <v>33</v>
       </c>
       <c r="I97" t="n">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="J97" t="n">
-        <v>0.0000873675289841777</v>
+        <v>0.000418808300019037</v>
       </c>
     </row>
     <row r="98">
@@ -3627,25 +3627,25 @@
         <v>0</v>
       </c>
       <c r="D98" t="n">
-        <v>1.73</v>
+        <v>-3.54</v>
       </c>
       <c r="E98" t="n">
-        <v>0.46</v>
+        <v>-1.89</v>
       </c>
       <c r="F98" t="n">
-        <v>0.61</v>
+        <v>-2.01</v>
       </c>
       <c r="G98" t="n">
-        <v>0.66</v>
+        <v>0.36</v>
       </c>
       <c r="H98" t="s">
         <v>33</v>
       </c>
       <c r="I98" t="n">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="J98" t="n">
-        <v>0.000386850596541204</v>
+        <v>0.0000786681482501254</v>
       </c>
     </row>
     <row r="99">
@@ -3659,25 +3659,25 @@
         <v>0</v>
       </c>
       <c r="D99" t="n">
-        <v>-2.28</v>
+        <v>-1.23</v>
       </c>
       <c r="E99" t="n">
-        <v>-0.53</v>
+        <v>-0.07</v>
       </c>
       <c r="F99" t="n">
-        <v>-0.24</v>
+        <v>0.22</v>
       </c>
       <c r="G99" t="n">
-        <v>-1.52</v>
+        <v>-1.38</v>
       </c>
       <c r="H99" t="s">
         <v>33</v>
       </c>
       <c r="I99" t="n">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="J99" t="n">
-        <v>0.000386850596541204</v>
+        <v>0.0000786681482501254</v>
       </c>
     </row>
     <row r="100">
@@ -3688,28 +3688,28 @@
         <v>14</v>
       </c>
       <c r="C100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D100" t="n">
-        <v>-4.55</v>
+        <v>2.45</v>
       </c>
       <c r="E100" t="n">
-        <v>-1.72</v>
+        <v>0.89</v>
       </c>
       <c r="F100" t="n">
-        <v>-1.86</v>
+        <v>0.67</v>
       </c>
       <c r="G100" t="n">
-        <v>-0.97</v>
+        <v>0.9</v>
       </c>
       <c r="H100" t="s">
         <v>33</v>
       </c>
       <c r="I100" t="n">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="J100" t="n">
-        <v>0.000386850596541204</v>
+        <v>0.0000786681482501254</v>
       </c>
     </row>
     <row r="101">
@@ -3720,28 +3720,28 @@
         <v>15</v>
       </c>
       <c r="C101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D101" t="n">
-        <v>3.12</v>
+        <v>-0.92</v>
       </c>
       <c r="E101" t="n">
-        <v>1.16</v>
+        <v>-0.03</v>
       </c>
       <c r="F101" t="n">
-        <v>0.99</v>
+        <v>0.22</v>
       </c>
       <c r="G101" t="n">
-        <v>0.97</v>
+        <v>-1.11</v>
       </c>
       <c r="H101" t="s">
         <v>33</v>
       </c>
       <c r="I101" t="n">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="J101" t="n">
-        <v>0.000386850596541204</v>
+        <v>0.0000786681482501254</v>
       </c>
     </row>
     <row r="102">
@@ -3755,25 +3755,25 @@
         <v>0</v>
       </c>
       <c r="D102" t="n">
-        <v>0.9</v>
+        <v>2.02</v>
       </c>
       <c r="E102" t="n">
-        <v>0.25</v>
+        <v>0.66</v>
       </c>
       <c r="F102" t="n">
-        <v>0.28</v>
+        <v>0.45</v>
       </c>
       <c r="G102" t="n">
-        <v>0.38</v>
+        <v>0.92</v>
       </c>
       <c r="H102" t="s">
         <v>33</v>
       </c>
       <c r="I102" t="n">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="J102" t="n">
-        <v>0.000386850596541204</v>
+        <v>0.0000786681482501254</v>
       </c>
     </row>
     <row r="103">
@@ -3787,25 +3787,25 @@
         <v>0</v>
       </c>
       <c r="D103" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="E103" t="n">
-        <v>0.39</v>
+        <v>0.45</v>
       </c>
       <c r="F103" t="n">
-        <v>0.21</v>
+        <v>0.45</v>
       </c>
       <c r="G103" t="n">
-        <v>0.48</v>
+        <v>0.31</v>
       </c>
       <c r="H103" t="s">
         <v>33</v>
       </c>
       <c r="I103" t="n">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="J103" t="n">
-        <v>0.000386850596541204</v>
+        <v>0.0000786681482501254</v>
       </c>
     </row>
     <row r="104">
@@ -3819,16 +3819,16 @@
         <v>0</v>
       </c>
       <c r="D104" t="n">
-        <v>-1.68</v>
+        <v>-1.88</v>
       </c>
       <c r="E104" t="n">
-        <v>0.33</v>
+        <v>0.24</v>
       </c>
       <c r="F104" t="n">
-        <v>-0.15</v>
+        <v>-0.23</v>
       </c>
       <c r="G104" t="n">
-        <v>-1.85</v>
+        <v>-1.89</v>
       </c>
       <c r="H104" t="s">
         <v>33</v>
@@ -3851,16 +3851,16 @@
         <v>0</v>
       </c>
       <c r="D105" t="n">
-        <v>0.95</v>
+        <v>1.5</v>
       </c>
       <c r="E105" t="n">
-        <v>0.21</v>
+        <v>0.38</v>
       </c>
       <c r="F105" t="n">
-        <v>0.46</v>
+        <v>0.7</v>
       </c>
       <c r="G105" t="n">
-        <v>0.27</v>
+        <v>0.43</v>
       </c>
       <c r="H105" t="s">
         <v>33</v>
@@ -3883,16 +3883,16 @@
         <v>0</v>
       </c>
       <c r="D106" t="n">
-        <v>-3.73</v>
+        <v>-3.83</v>
       </c>
       <c r="E106" t="n">
-        <v>-1.97</v>
+        <v>-1.99</v>
       </c>
       <c r="F106" t="n">
         <v>-1.72</v>
       </c>
       <c r="G106" t="n">
-        <v>-0.05</v>
+        <v>-0.12</v>
       </c>
       <c r="H106" t="s">
         <v>33</v>
@@ -3915,16 +3915,16 @@
         <v>0</v>
       </c>
       <c r="D107" t="n">
-        <v>0.83</v>
+        <v>0.59</v>
       </c>
       <c r="E107" t="n">
-        <v>0.3</v>
+        <v>0.23</v>
       </c>
       <c r="F107" t="n">
-        <v>-0.22</v>
+        <v>-0.3</v>
       </c>
       <c r="G107" t="n">
-        <v>0.74</v>
+        <v>0.66</v>
       </c>
       <c r="H107" t="s">
         <v>33</v>
@@ -3947,16 +3947,16 @@
         <v>0</v>
       </c>
       <c r="D108" t="n">
-        <v>0.48</v>
+        <v>0.8</v>
       </c>
       <c r="E108" t="n">
-        <v>0.21</v>
+        <v>0.33</v>
       </c>
       <c r="F108" t="n">
-        <v>0.34</v>
+        <v>0.43</v>
       </c>
       <c r="G108" t="n">
-        <v>-0.08</v>
+        <v>0.04</v>
       </c>
       <c r="H108" t="s">
         <v>33</v>
@@ -3979,16 +3979,16 @@
         <v>1</v>
       </c>
       <c r="D109" t="n">
-        <v>3.17</v>
+        <v>2.82</v>
       </c>
       <c r="E109" t="n">
-        <v>0.92</v>
+        <v>0.82</v>
       </c>
       <c r="F109" t="n">
-        <v>1.29</v>
+        <v>1.11</v>
       </c>
       <c r="G109" t="n">
-        <v>0.96</v>
+        <v>0.89</v>
       </c>
       <c r="H109" t="s">
         <v>33</v>
@@ -4011,16 +4011,16 @@
         <v>0</v>
       </c>
       <c r="D110" t="n">
-        <v>0.5</v>
+        <v>0.35</v>
       </c>
       <c r="E110" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="F110" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="G110" t="n">
-        <v>-1.99</v>
+        <v>-2.01</v>
       </c>
       <c r="H110" t="s">
         <v>33</v>
@@ -4043,16 +4043,16 @@
         <v>0</v>
       </c>
       <c r="D111" t="n">
-        <v>-1.23</v>
+        <v>-2.38</v>
       </c>
       <c r="E111" t="n">
-        <v>-0.87</v>
+        <v>-1.28</v>
       </c>
       <c r="F111" t="n">
-        <v>-1.03</v>
+        <v>-1.51</v>
       </c>
       <c r="G111" t="n">
-        <v>0.67</v>
+        <v>0.41</v>
       </c>
       <c r="H111" t="s">
         <v>33</v>
@@ -4075,16 +4075,16 @@
         <v>1</v>
       </c>
       <c r="D112" t="n">
-        <v>1.67</v>
+        <v>1.93</v>
       </c>
       <c r="E112" t="n">
         <v>1.06</v>
       </c>
       <c r="F112" t="n">
-        <v>0.56</v>
+        <v>0.63</v>
       </c>
       <c r="G112" t="n">
-        <v>0.05</v>
+        <v>0.24</v>
       </c>
       <c r="H112" t="s">
         <v>33</v>
@@ -4107,16 +4107,16 @@
         <v>0</v>
       </c>
       <c r="D113" t="n">
-        <v>-0.61</v>
+        <v>-0.12</v>
       </c>
       <c r="E113" t="n">
-        <v>-0.61</v>
+        <v>-0.39</v>
       </c>
       <c r="F113" t="n">
-        <v>-0.59</v>
+        <v>-0.38</v>
       </c>
       <c r="G113" t="n">
-        <v>0.59</v>
+        <v>0.66</v>
       </c>
       <c r="H113" t="s">
         <v>33</v>
@@ -4139,16 +4139,16 @@
         <v>0</v>
       </c>
       <c r="D114" t="n">
-        <v>1.47</v>
+        <v>1.08</v>
       </c>
       <c r="E114" t="n">
-        <v>0.41</v>
+        <v>0.32</v>
       </c>
       <c r="F114" t="n">
-        <v>0.69</v>
+        <v>0.61</v>
       </c>
       <c r="G114" t="n">
-        <v>0.37</v>
+        <v>0.16</v>
       </c>
       <c r="H114" t="s">
         <v>33</v>
@@ -4171,16 +4171,16 @@
         <v>0</v>
       </c>
       <c r="D115" t="n">
-        <v>-1.8</v>
+        <v>-0.87</v>
       </c>
       <c r="E115" t="n">
-        <v>-1.13</v>
+        <v>-0.84</v>
       </c>
       <c r="F115" t="n">
-        <v>-0.99</v>
+        <v>-0.56</v>
       </c>
       <c r="G115" t="n">
-        <v>0.32</v>
+        <v>0.53</v>
       </c>
       <c r="H115" t="s">
         <v>33</v>
@@ -4203,16 +4203,16 @@
         <v>1</v>
       </c>
       <c r="D116" t="n">
-        <v>4.36</v>
+        <v>4.4</v>
       </c>
       <c r="E116" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="F116" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="G116" t="n">
-        <v>1.93</v>
+        <v>1.99</v>
       </c>
       <c r="H116" t="s">
         <v>33</v>
@@ -4235,16 +4235,16 @@
         <v>0</v>
       </c>
       <c r="D117" t="n">
-        <v>-2.95</v>
+        <v>-2.76</v>
       </c>
       <c r="E117" t="n">
-        <v>-1.05</v>
+        <v>-1.03</v>
       </c>
       <c r="F117" t="n">
-        <v>-1</v>
+        <v>-0.98</v>
       </c>
       <c r="G117" t="n">
-        <v>-0.9</v>
+        <v>-0.74</v>
       </c>
       <c r="H117" t="s">
         <v>33</v>
@@ -4267,16 +4267,16 @@
         <v>0</v>
       </c>
       <c r="D118" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="E118" t="n">
-        <v>0.85</v>
+        <v>0.84</v>
       </c>
       <c r="F118" t="n">
-        <v>0.74</v>
+        <v>0.73</v>
       </c>
       <c r="G118" t="n">
-        <v>-0.45</v>
+        <v>-0.46</v>
       </c>
       <c r="H118" t="s">
         <v>33</v>
@@ -4299,16 +4299,16 @@
         <v>0</v>
       </c>
       <c r="D119" t="n">
-        <v>-2.95</v>
+        <v>-3.02</v>
       </c>
       <c r="E119" t="n">
-        <v>-1.31</v>
+        <v>-1.33</v>
       </c>
       <c r="F119" t="n">
-        <v>-1.35</v>
+        <v>-1.37</v>
       </c>
       <c r="G119" t="n">
-        <v>-0.3</v>
+        <v>-0.31</v>
       </c>
       <c r="H119" t="s">
         <v>33</v>
@@ -4331,16 +4331,16 @@
         <v>0</v>
       </c>
       <c r="D120" t="n">
-        <v>0.59</v>
+        <v>0.49</v>
       </c>
       <c r="E120" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="F120" t="n">
-        <v>0.22</v>
+        <v>0.27</v>
       </c>
       <c r="G120" t="n">
-        <v>0.12</v>
+        <v>-0.07</v>
       </c>
       <c r="H120" t="s">
         <v>33</v>
@@ -4363,13 +4363,13 @@
         <v>0</v>
       </c>
       <c r="D121" t="n">
-        <v>-0.18</v>
+        <v>-0.21</v>
       </c>
       <c r="E121" t="n">
-        <v>0.07</v>
+        <v>0.06</v>
       </c>
       <c r="F121" t="n">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
       <c r="G121" t="n">
         <v>-0.4</v>
@@ -4395,10 +4395,10 @@
         <v>0</v>
       </c>
       <c r="D122" t="n">
-        <v>-5.65</v>
+        <v>-5.66</v>
       </c>
       <c r="E122" t="n">
-        <v>-1.96</v>
+        <v>-1.97</v>
       </c>
       <c r="F122" t="n">
         <v>-1.7</v>
@@ -4413,7 +4413,7 @@
         <v>5</v>
       </c>
       <c r="J122" t="n">
-        <v>0.000366112616240756</v>
+        <v>0.00040956749672346</v>
       </c>
     </row>
     <row r="123">
@@ -4427,16 +4427,16 @@
         <v>0</v>
       </c>
       <c r="D123" t="n">
-        <v>1.95</v>
+        <v>1.79</v>
       </c>
       <c r="E123" t="n">
-        <v>0.67</v>
+        <v>0.58</v>
       </c>
       <c r="F123" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="G123" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="H123" t="s">
         <v>33</v>
@@ -4445,7 +4445,7 @@
         <v>5</v>
       </c>
       <c r="J123" t="n">
-        <v>0.000366112616240756</v>
+        <v>0.00040956749672346</v>
       </c>
     </row>
     <row r="124">
@@ -4459,16 +4459,16 @@
         <v>0</v>
       </c>
       <c r="D124" t="n">
-        <v>-0.32</v>
+        <v>-0.26</v>
       </c>
       <c r="E124" t="n">
-        <v>-0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="F124" t="n">
-        <v>-0.4</v>
+        <v>-0.38</v>
       </c>
       <c r="G124" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="H124" t="s">
         <v>33</v>
@@ -4477,7 +4477,7 @@
         <v>5</v>
       </c>
       <c r="J124" t="n">
-        <v>0.000366112616240756</v>
+        <v>0.00040956749672346</v>
       </c>
     </row>
     <row r="125">
@@ -4491,13 +4491,13 @@
         <v>0</v>
       </c>
       <c r="D125" t="n">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="E125" t="n">
-        <v>0.43</v>
+        <v>0.49</v>
       </c>
       <c r="F125" t="n">
-        <v>0.47</v>
+        <v>0.49</v>
       </c>
       <c r="G125" t="n">
         <v>0.59</v>
@@ -4509,7 +4509,7 @@
         <v>5</v>
       </c>
       <c r="J125" t="n">
-        <v>0.000366112616240756</v>
+        <v>0.00040956749672346</v>
       </c>
     </row>
     <row r="126">
@@ -4523,16 +4523,16 @@
         <v>0</v>
       </c>
       <c r="D126" t="n">
-        <v>0.18</v>
+        <v>0.14</v>
       </c>
       <c r="E126" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="F126" t="n">
-        <v>-0.18</v>
+        <v>-0.21</v>
       </c>
       <c r="G126" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="H126" t="s">
         <v>33</v>
@@ -4541,7 +4541,7 @@
         <v>5</v>
       </c>
       <c r="J126" t="n">
-        <v>0.000366112616240756</v>
+        <v>0.00040956749672346</v>
       </c>
     </row>
     <row r="127">
@@ -4555,16 +4555,16 @@
         <v>1</v>
       </c>
       <c r="D127" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="E127" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="F127" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="G127" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="H127" t="s">
         <v>33</v>
@@ -4573,7 +4573,7 @@
         <v>5</v>
       </c>
       <c r="J127" t="n">
-        <v>0.000366112616240756</v>
+        <v>0.00040956749672346</v>
       </c>
     </row>
     <row r="128">
@@ -4587,16 +4587,16 @@
         <v>0</v>
       </c>
       <c r="D128" t="n">
-        <v>-3.48</v>
+        <v>-3.5</v>
       </c>
       <c r="E128" t="n">
-        <v>-1.88</v>
+        <v>-1.95</v>
       </c>
       <c r="F128" t="n">
-        <v>-1.93</v>
+        <v>-1.97</v>
       </c>
       <c r="G128" t="n">
-        <v>0.33</v>
+        <v>0.42</v>
       </c>
       <c r="H128" t="s">
         <v>33</v>
@@ -4605,7 +4605,7 @@
         <v>3</v>
       </c>
       <c r="J128" t="n">
-        <v>0.00202565833896016</v>
+        <v>0.00210231254379818</v>
       </c>
     </row>
     <row r="129">
@@ -4619,13 +4619,13 @@
         <v>0</v>
       </c>
       <c r="D129" t="n">
-        <v>0.56</v>
+        <v>0.62</v>
       </c>
       <c r="E129" t="n">
-        <v>0.19</v>
+        <v>0.25</v>
       </c>
       <c r="F129" t="n">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="G129"/>
       <c r="H129" t="s">
@@ -4635,7 +4635,7 @@
         <v>3</v>
       </c>
       <c r="J129" t="n">
-        <v>0.00202565833896016</v>
+        <v>0.00210231254379818</v>
       </c>
     </row>
     <row r="130">
@@ -4649,13 +4649,13 @@
         <v>0</v>
       </c>
       <c r="D130" t="n">
-        <v>-1.18</v>
+        <v>-1.11</v>
       </c>
       <c r="E130" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="F130" t="n">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="G130" t="n">
         <v>-1.78</v>
@@ -4667,7 +4667,7 @@
         <v>3</v>
       </c>
       <c r="J130" t="n">
-        <v>0.00202565833896016</v>
+        <v>0.00210231254379818</v>
       </c>
     </row>
     <row r="131">
@@ -4681,16 +4681,16 @@
         <v>0</v>
       </c>
       <c r="D131" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="E131" t="n">
-        <v>0.39</v>
+        <v>0.43</v>
       </c>
       <c r="F131" t="n">
-        <v>0.28</v>
+        <v>0.4</v>
       </c>
       <c r="G131" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="H131" t="s">
         <v>33</v>
@@ -4699,7 +4699,7 @@
         <v>3</v>
       </c>
       <c r="J131" t="n">
-        <v>0.00202565833896016</v>
+        <v>0.00210231254379818</v>
       </c>
     </row>
     <row r="132">
@@ -4713,16 +4713,16 @@
         <v>0</v>
       </c>
       <c r="D132" t="n">
-        <v>0.27</v>
+        <v>0.35</v>
       </c>
       <c r="E132" t="n">
-        <v>0.01</v>
+        <v>0.09</v>
       </c>
       <c r="F132" t="n">
-        <v>-0.09</v>
+        <v>-0.04</v>
       </c>
       <c r="G132" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="H132" t="s">
         <v>33</v>
@@ -4731,7 +4731,7 @@
         <v>3</v>
       </c>
       <c r="J132" t="n">
-        <v>0.00202565833896016</v>
+        <v>0.00210231254379818</v>
       </c>
     </row>
     <row r="133">
@@ -4745,16 +4745,16 @@
         <v>1</v>
       </c>
       <c r="D133" t="n">
-        <v>2.64</v>
+        <v>2.31</v>
       </c>
       <c r="E133" t="n">
-        <v>1.11</v>
+        <v>0.95</v>
       </c>
       <c r="F133" t="n">
-        <v>0.95</v>
+        <v>0.8</v>
       </c>
       <c r="G133" t="n">
-        <v>0.57</v>
+        <v>0.56</v>
       </c>
       <c r="H133" t="s">
         <v>33</v>
@@ -4763,7 +4763,7 @@
         <v>3</v>
       </c>
       <c r="J133" t="n">
-        <v>0.00202565833896016</v>
+        <v>0.00210231254379818</v>
       </c>
     </row>
     <row r="134">
@@ -4777,16 +4777,16 @@
         <v>0</v>
       </c>
       <c r="D134" t="n">
-        <v>0.82</v>
+        <v>0.84</v>
       </c>
       <c r="E134" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="F134" t="n">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="G134" t="n">
-        <v>0.11</v>
+        <v>0.15</v>
       </c>
       <c r="H134" t="s">
         <v>42</v>
@@ -4795,7 +4795,7 @@
         <v>18</v>
       </c>
       <c r="J134" t="n">
-        <v>0.0000198641512765476</v>
+        <v>0.0000201725650873416</v>
       </c>
     </row>
     <row r="135">
@@ -4809,16 +4809,16 @@
         <v>0</v>
       </c>
       <c r="D135" t="n">
-        <v>-2.14</v>
+        <v>-2.2</v>
       </c>
       <c r="E135" t="n">
-        <v>-1.66</v>
+        <v>-1.67</v>
       </c>
       <c r="F135" t="n">
         <v>-1.99</v>
       </c>
       <c r="G135" t="n">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="H135" t="s">
         <v>42</v>
@@ -4827,7 +4827,7 @@
         <v>18</v>
       </c>
       <c r="J135" t="n">
-        <v>0.0000198641512765476</v>
+        <v>0.0000201725650873416</v>
       </c>
     </row>
     <row r="136">
@@ -4841,16 +4841,16 @@
         <v>1</v>
       </c>
       <c r="D136" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="E136" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="F136" t="n">
         <v>0.52</v>
       </c>
       <c r="G136" t="n">
-        <v>-0.11</v>
+        <v>-0.13</v>
       </c>
       <c r="H136" t="s">
         <v>42</v>
@@ -4859,7 +4859,7 @@
         <v>18</v>
       </c>
       <c r="J136" t="n">
-        <v>0.0000198641512765476</v>
+        <v>0.0000201725650873416</v>
       </c>
     </row>
     <row r="137">
@@ -4873,16 +4873,16 @@
         <v>0</v>
       </c>
       <c r="D137" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="E137" t="n">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="F137" t="n">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="G137" t="n">
-        <v>-0.89</v>
+        <v>-0.91</v>
       </c>
       <c r="H137" t="s">
         <v>42</v>
@@ -4891,7 +4891,7 @@
         <v>18</v>
       </c>
       <c r="J137" t="n">
-        <v>0.0000198641512765476</v>
+        <v>0.0000201725650873416</v>
       </c>
     </row>
     <row r="138">
@@ -4905,16 +4905,16 @@
         <v>0</v>
       </c>
       <c r="D138" t="n">
-        <v>0.43</v>
+        <v>0.54</v>
       </c>
       <c r="E138" t="n">
-        <v>-0.15</v>
+        <v>-0.09</v>
       </c>
       <c r="F138" t="n">
-        <v>-0.04</v>
+        <v>-0.05</v>
       </c>
       <c r="G138" t="n">
-        <v>0.62</v>
+        <v>0.68</v>
       </c>
       <c r="H138" t="s">
         <v>42</v>
@@ -4923,7 +4923,7 @@
         <v>18</v>
       </c>
       <c r="J138" t="n">
-        <v>0.0000198641512765476</v>
+        <v>0.0000201725650873416</v>
       </c>
     </row>
     <row r="139">
@@ -4937,16 +4937,16 @@
         <v>0</v>
       </c>
       <c r="D139" t="n">
-        <v>-1.1</v>
+        <v>-1.13</v>
       </c>
       <c r="E139" t="n">
-        <v>-0.43</v>
+        <v>-0.45</v>
       </c>
       <c r="F139" t="n">
         <v>0.56</v>
       </c>
       <c r="G139" t="n">
-        <v>-1.23</v>
+        <v>-1.24</v>
       </c>
       <c r="H139" t="s">
         <v>42</v>
@@ -4955,7 +4955,7 @@
         <v>18</v>
       </c>
       <c r="J139" t="n">
-        <v>0.0000198641512765476</v>
+        <v>0.0000201725650873416</v>
       </c>
     </row>
     <row r="140">
@@ -4969,16 +4969,16 @@
         <v>0</v>
       </c>
       <c r="D140" t="n">
-        <v>-1.55</v>
+        <v>-1.49</v>
       </c>
       <c r="E140" t="n">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="F140" t="n">
-        <v>-0.06</v>
+        <v>-0.02</v>
       </c>
       <c r="G140" t="n">
-        <v>-1.66</v>
+        <v>-1.67</v>
       </c>
       <c r="H140" t="s">
         <v>42</v>
@@ -5001,16 +5001,16 @@
         <v>0</v>
       </c>
       <c r="D141" t="n">
-        <v>0.64</v>
+        <v>0.96</v>
       </c>
       <c r="E141" t="n">
-        <v>0.41</v>
+        <v>0.5</v>
       </c>
       <c r="F141" t="n">
-        <v>0.38</v>
+        <v>0.51</v>
       </c>
       <c r="G141" t="n">
-        <v>-0.15</v>
+        <v>-0.06</v>
       </c>
       <c r="H141" t="s">
         <v>42</v>
@@ -5033,16 +5033,16 @@
         <v>0</v>
       </c>
       <c r="D142" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="E142" t="n">
-        <v>-0.21</v>
+        <v>-0.22</v>
       </c>
       <c r="F142" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="G142" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="H142" t="s">
         <v>42</v>
@@ -5065,16 +5065,16 @@
         <v>1</v>
       </c>
       <c r="D143" t="n">
-        <v>2.31</v>
+        <v>2.03</v>
       </c>
       <c r="E143" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="F143" t="n">
-        <v>0.9</v>
+        <v>0.78</v>
       </c>
       <c r="G143" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="H143" t="s">
         <v>42</v>
@@ -5097,16 +5097,16 @@
         <v>0</v>
       </c>
       <c r="D144" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="E144" t="n">
-        <v>0.51</v>
+        <v>0.49</v>
       </c>
       <c r="F144" t="n">
-        <v>0.53</v>
+        <v>0.52</v>
       </c>
       <c r="G144" t="n">
-        <v>-0.26</v>
+        <v>-0.27</v>
       </c>
       <c r="H144" t="s">
         <v>42</v>
@@ -5129,16 +5129,16 @@
         <v>0</v>
       </c>
       <c r="D145" t="n">
-        <v>-2.42</v>
+        <v>-2.46</v>
       </c>
       <c r="E145" t="n">
-        <v>-1.87</v>
+        <v>-1.89</v>
       </c>
       <c r="F145" t="n">
-        <v>-1.93</v>
+        <v>-1.96</v>
       </c>
       <c r="G145" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="H145" t="s">
         <v>42</v>
@@ -5164,7 +5164,7 @@
         <v>4.78</v>
       </c>
       <c r="E146" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="F146" t="n">
         <v>1.78</v>
@@ -5179,7 +5179,7 @@
         <v>11</v>
       </c>
       <c r="J146" t="n">
-        <v>0.000225465278347135</v>
+        <v>0.000231034193060573</v>
       </c>
     </row>
     <row r="147">
@@ -5193,13 +5193,13 @@
         <v>0</v>
       </c>
       <c r="D147" t="n">
-        <v>-0.21</v>
+        <v>-0.23</v>
       </c>
       <c r="E147" t="n">
         <v>-0.15</v>
       </c>
       <c r="F147" t="n">
-        <v>-0.06</v>
+        <v>-0.07</v>
       </c>
       <c r="G147"/>
       <c r="H147" t="s">
@@ -5209,7 +5209,7 @@
         <v>11</v>
       </c>
       <c r="J147" t="n">
-        <v>0.000225465278347135</v>
+        <v>0.000231034193060573</v>
       </c>
     </row>
     <row r="148">
@@ -5223,13 +5223,13 @@
         <v>0</v>
       </c>
       <c r="D148" t="n">
-        <v>-0.05</v>
+        <v>-0.07</v>
       </c>
       <c r="E148" t="n">
-        <v>-0.07</v>
+        <v>-0.08</v>
       </c>
       <c r="F148" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="G148"/>
       <c r="H148" t="s">
@@ -5239,7 +5239,7 @@
         <v>11</v>
       </c>
       <c r="J148" t="n">
-        <v>0.000225465278347135</v>
+        <v>0.000231034193060573</v>
       </c>
     </row>
     <row r="149">
@@ -5253,7 +5253,7 @@
         <v>0</v>
       </c>
       <c r="D149" t="n">
-        <v>-1.8</v>
+        <v>-1.81</v>
       </c>
       <c r="E149" t="n">
         <v>-1.05</v>
@@ -5262,7 +5262,7 @@
         <v>-1.26</v>
       </c>
       <c r="G149" t="n">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
       <c r="H149" t="s">
         <v>42</v>
@@ -5271,7 +5271,7 @@
         <v>11</v>
       </c>
       <c r="J149" t="n">
-        <v>0.000225465278347135</v>
+        <v>0.000231034193060573</v>
       </c>
     </row>
     <row r="150">
@@ -5285,16 +5285,16 @@
         <v>0</v>
       </c>
       <c r="D150" t="n">
-        <v>-1.21</v>
+        <v>-1.19</v>
       </c>
       <c r="E150" t="n">
-        <v>-0.11</v>
+        <v>-0.09</v>
       </c>
       <c r="F150" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="G150" t="n">
-        <v>-1.12</v>
+        <v>-1.14</v>
       </c>
       <c r="H150" t="s">
         <v>42</v>
@@ -5303,7 +5303,7 @@
         <v>11</v>
       </c>
       <c r="J150" t="n">
-        <v>0.000225465278347135</v>
+        <v>0.000231034193060573</v>
       </c>
     </row>
     <row r="151">
@@ -5317,16 +5317,16 @@
         <v>0</v>
       </c>
       <c r="D151" t="n">
-        <v>-1.51</v>
+        <v>-1.5</v>
       </c>
       <c r="E151" t="n">
-        <v>-0.52</v>
+        <v>-0.53</v>
       </c>
       <c r="F151" t="n">
-        <v>-0.49</v>
+        <v>-0.51</v>
       </c>
       <c r="G151" t="n">
-        <v>-0.5</v>
+        <v>-0.46</v>
       </c>
       <c r="H151" t="s">
         <v>42</v>
@@ -5335,7 +5335,7 @@
         <v>11</v>
       </c>
       <c r="J151" t="n">
-        <v>0.000225465278347135</v>
+        <v>0.000231034193060573</v>
       </c>
     </row>
     <row r="152">
@@ -5349,16 +5349,16 @@
         <v>0</v>
       </c>
       <c r="D152" t="n">
-        <v>-1.77</v>
+        <v>-1.9</v>
       </c>
       <c r="E152" t="n">
-        <v>-0.8</v>
+        <v>-0.73</v>
       </c>
       <c r="F152" t="n">
-        <v>-0.91</v>
+        <v>-1.01</v>
       </c>
       <c r="G152" t="n">
-        <v>-0.06</v>
+        <v>-0.16</v>
       </c>
       <c r="H152" t="s">
         <v>42</v>
@@ -5381,13 +5381,13 @@
         <v>0</v>
       </c>
       <c r="D153" t="n">
-        <v>-1.43</v>
+        <v>-1.47</v>
       </c>
       <c r="E153" t="n">
-        <v>-0.64</v>
+        <v>-0.71</v>
       </c>
       <c r="F153" t="n">
-        <v>-0.79</v>
+        <v>-0.76</v>
       </c>
       <c r="G153"/>
       <c r="H153" t="s">
@@ -5411,16 +5411,16 @@
         <v>1</v>
       </c>
       <c r="D154" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="E154" t="n">
         <v>0.89</v>
       </c>
       <c r="F154" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="G154" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="H154" t="s">
         <v>42</v>
@@ -5443,13 +5443,13 @@
         <v>0</v>
       </c>
       <c r="D155" t="n">
-        <v>-1.46</v>
+        <v>-1.49</v>
       </c>
       <c r="E155" t="n">
-        <v>-0.72</v>
+        <v>-0.78</v>
       </c>
       <c r="F155" t="n">
-        <v>-0.74</v>
+        <v>-0.71</v>
       </c>
       <c r="G155"/>
       <c r="H155" t="s">
@@ -5473,16 +5473,16 @@
         <v>0</v>
       </c>
       <c r="D156" t="n">
-        <v>-1.5</v>
+        <v>-1.31</v>
       </c>
       <c r="E156" t="n">
-        <v>-0.32</v>
+        <v>-0.25</v>
       </c>
       <c r="F156" t="n">
-        <v>0.2</v>
+        <v>0.28</v>
       </c>
       <c r="G156" t="n">
-        <v>-1.39</v>
+        <v>-1.35</v>
       </c>
       <c r="H156" t="s">
         <v>42</v>
@@ -5505,16 +5505,16 @@
         <v>0</v>
       </c>
       <c r="D157" t="n">
-        <v>3.06</v>
+        <v>3.07</v>
       </c>
       <c r="E157" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="F157" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="G157" t="n">
-        <v>0.84</v>
+        <v>0.87</v>
       </c>
       <c r="H157" t="s">
         <v>42</v>
@@ -5534,28 +5534,28 @@
         <v>11</v>
       </c>
       <c r="C158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D158" t="n">
-        <v>3.89</v>
+        <v>-1.91</v>
       </c>
       <c r="E158" t="n">
-        <v>1.75</v>
+        <v>-1.02</v>
       </c>
       <c r="F158" t="n">
-        <v>1.52</v>
+        <v>-1.39</v>
       </c>
       <c r="G158" t="n">
-        <v>0.61</v>
+        <v>0.5</v>
       </c>
       <c r="H158" t="s">
         <v>42</v>
       </c>
       <c r="I158" t="n">
-        <v>14</v>
+        <v>71</v>
       </c>
       <c r="J158" t="n">
-        <v>0.00674698795180723</v>
+        <v>0.0529850746268657</v>
       </c>
     </row>
     <row r="159">
@@ -5569,23 +5569,23 @@
         <v>0</v>
       </c>
       <c r="D159" t="n">
-        <v>-0.29</v>
+        <v>1.59</v>
       </c>
       <c r="E159" t="n">
-        <v>-0.21</v>
+        <v>0.74</v>
       </c>
       <c r="F159" t="n">
-        <v>-0.08</v>
+        <v>0.85</v>
       </c>
       <c r="G159"/>
       <c r="H159" t="s">
         <v>42</v>
       </c>
       <c r="I159" t="n">
-        <v>14</v>
+        <v>71</v>
       </c>
       <c r="J159" t="n">
-        <v>0.00674698795180723</v>
+        <v>0.0529850746268657</v>
       </c>
     </row>
     <row r="160">
@@ -5599,23 +5599,25 @@
         <v>0</v>
       </c>
       <c r="D160" t="n">
-        <v>-0.33</v>
+        <v>0.52</v>
       </c>
       <c r="E160" t="n">
-        <v>-0.23</v>
+        <v>1.13</v>
       </c>
       <c r="F160" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="G160"/>
+        <v>1.17</v>
+      </c>
+      <c r="G160" t="n">
+        <v>-1.79</v>
+      </c>
       <c r="H160" t="s">
         <v>42</v>
       </c>
       <c r="I160" t="n">
-        <v>14</v>
+        <v>71</v>
       </c>
       <c r="J160" t="n">
-        <v>0.00674698795180723</v>
+        <v>0.0529850746268657</v>
       </c>
     </row>
     <row r="161">
@@ -5629,23 +5631,25 @@
         <v>0</v>
       </c>
       <c r="D161" t="n">
-        <v>-0.39</v>
+        <v>-0.38</v>
       </c>
       <c r="E161" t="n">
-        <v>-0.26</v>
+        <v>-0.57</v>
       </c>
       <c r="F161" t="n">
-        <v>-0.13</v>
-      </c>
-      <c r="G161"/>
+        <v>-0.25</v>
+      </c>
+      <c r="G161" t="n">
+        <v>0.43</v>
+      </c>
       <c r="H161" t="s">
         <v>42</v>
       </c>
       <c r="I161" t="n">
-        <v>14</v>
+        <v>71</v>
       </c>
       <c r="J161" t="n">
-        <v>0.00674698795180723</v>
+        <v>0.0529850746268657</v>
       </c>
     </row>
     <row r="162">
@@ -5656,28 +5660,28 @@
         <v>16</v>
       </c>
       <c r="C162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D162" t="n">
-        <v>-0.53</v>
+        <v>1.61</v>
       </c>
       <c r="E162" t="n">
-        <v>0.25</v>
+        <v>0.8</v>
       </c>
       <c r="F162" t="n">
-        <v>0.37</v>
+        <v>0.45</v>
       </c>
       <c r="G162" t="n">
-        <v>-1.15</v>
+        <v>0.35</v>
       </c>
       <c r="H162" t="s">
         <v>42</v>
       </c>
       <c r="I162" t="n">
-        <v>14</v>
+        <v>71</v>
       </c>
       <c r="J162" t="n">
-        <v>0.00674698795180723</v>
+        <v>0.0529850746268657</v>
       </c>
     </row>
     <row r="163">
@@ -5691,25 +5695,25 @@
         <v>0</v>
       </c>
       <c r="D163" t="n">
-        <v>-2.34</v>
+        <v>-1.43</v>
       </c>
       <c r="E163" t="n">
-        <v>-1.3</v>
+        <v>-1.09</v>
       </c>
       <c r="F163" t="n">
-        <v>-1.58</v>
+        <v>-0.84</v>
       </c>
       <c r="G163" t="n">
-        <v>0.54</v>
+        <v>0.49</v>
       </c>
       <c r="H163" t="s">
         <v>42</v>
       </c>
       <c r="I163" t="n">
-        <v>14</v>
+        <v>71</v>
       </c>
       <c r="J163" t="n">
-        <v>0.00674698795180723</v>
+        <v>0.0529850746268657</v>
       </c>
     </row>
     <row r="164">
@@ -5720,28 +5724,28 @@
         <v>11</v>
       </c>
       <c r="C164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D164" t="n">
-        <v>-1.25</v>
+        <v>3.95</v>
       </c>
       <c r="E164" t="n">
-        <v>-0.64</v>
+        <v>1.77</v>
       </c>
       <c r="F164" t="n">
-        <v>-1.17</v>
+        <v>1.59</v>
       </c>
       <c r="G164" t="n">
-        <v>0.56</v>
+        <v>0.59</v>
       </c>
       <c r="H164" t="s">
         <v>42</v>
       </c>
       <c r="I164" t="n">
-        <v>74</v>
+        <v>13</v>
       </c>
       <c r="J164" t="n">
-        <v>0.0541331382589612</v>
+        <v>0.0124760076775432</v>
       </c>
     </row>
     <row r="165">
@@ -5752,26 +5756,26 @@
         <v>13</v>
       </c>
       <c r="C165" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D165" t="n">
-        <v>1.72</v>
+        <v>-0.34</v>
       </c>
       <c r="E165" t="n">
-        <v>0.83</v>
+        <v>-0.23</v>
       </c>
       <c r="F165" t="n">
-        <v>0.89</v>
+        <v>-0.11</v>
       </c>
       <c r="G165"/>
       <c r="H165" t="s">
         <v>42</v>
       </c>
       <c r="I165" t="n">
-        <v>74</v>
+        <v>13</v>
       </c>
       <c r="J165" t="n">
-        <v>0.0541331382589612</v>
+        <v>0.0124760076775432</v>
       </c>
     </row>
     <row r="166">
@@ -5785,25 +5789,23 @@
         <v>0</v>
       </c>
       <c r="D166" t="n">
-        <v>0.65</v>
+        <v>-0.38</v>
       </c>
       <c r="E166" t="n">
-        <v>1.23</v>
+        <v>-0.25</v>
       </c>
       <c r="F166" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="G166" t="n">
-        <v>-1.77</v>
-      </c>
+        <v>-0.13</v>
+      </c>
+      <c r="G166"/>
       <c r="H166" t="s">
         <v>42</v>
       </c>
       <c r="I166" t="n">
-        <v>74</v>
+        <v>13</v>
       </c>
       <c r="J166" t="n">
-        <v>0.0541331382589612</v>
+        <v>0.0124760076775432</v>
       </c>
     </row>
     <row r="167">
@@ -5817,25 +5819,23 @@
         <v>0</v>
       </c>
       <c r="D167" t="n">
-        <v>-1.3</v>
+        <v>-0.46</v>
       </c>
       <c r="E167" t="n">
-        <v>-0.97</v>
+        <v>-0.29</v>
       </c>
       <c r="F167" t="n">
-        <v>-0.78</v>
-      </c>
-      <c r="G167" t="n">
-        <v>0.45</v>
-      </c>
+        <v>-0.17</v>
+      </c>
+      <c r="G167"/>
       <c r="H167" t="s">
         <v>42</v>
       </c>
       <c r="I167" t="n">
-        <v>74</v>
+        <v>13</v>
       </c>
       <c r="J167" t="n">
-        <v>0.0541331382589612</v>
+        <v>0.0124760076775432</v>
       </c>
     </row>
     <row r="168">
@@ -5849,25 +5849,25 @@
         <v>0</v>
       </c>
       <c r="D168" t="n">
-        <v>1.39</v>
+        <v>-0.55</v>
       </c>
       <c r="E168" t="n">
-        <v>0.59</v>
+        <v>0.26</v>
       </c>
       <c r="F168" t="n">
-        <v>0.57</v>
+        <v>0.34</v>
       </c>
       <c r="G168" t="n">
-        <v>0.23</v>
+        <v>-1.15</v>
       </c>
       <c r="H168" t="s">
         <v>42</v>
       </c>
       <c r="I168" t="n">
-        <v>74</v>
+        <v>13</v>
       </c>
       <c r="J168" t="n">
-        <v>0.0541331382589612</v>
+        <v>0.0124760076775432</v>
       </c>
     </row>
     <row r="169">
@@ -5881,25 +5881,25 @@
         <v>0</v>
       </c>
       <c r="D169" t="n">
-        <v>-1.21</v>
+        <v>-2.22</v>
       </c>
       <c r="E169" t="n">
-        <v>-1.04</v>
+        <v>-1.26</v>
       </c>
       <c r="F169" t="n">
-        <v>-0.71</v>
+        <v>-1.52</v>
       </c>
       <c r="G169" t="n">
-        <v>0.54</v>
+        <v>0.56</v>
       </c>
       <c r="H169" t="s">
         <v>42</v>
       </c>
       <c r="I169" t="n">
-        <v>74</v>
+        <v>13</v>
       </c>
       <c r="J169" t="n">
-        <v>0.0541331382589612</v>
+        <v>0.0124760076775432</v>
       </c>
     </row>
     <row r="170">
@@ -5913,25 +5913,25 @@
         <v>0</v>
       </c>
       <c r="D170" t="n">
-        <v>-0.32</v>
+        <v>-0.14</v>
       </c>
       <c r="E170" t="n">
         <v>0.26</v>
       </c>
       <c r="F170" t="n">
-        <v>0.47</v>
+        <v>0.54</v>
       </c>
       <c r="G170" t="n">
-        <v>-1.04</v>
+        <v>-0.93</v>
       </c>
       <c r="H170" t="s">
         <v>49</v>
       </c>
       <c r="I170" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J170" t="n">
-        <v>0.0000402007020047588</v>
+        <v>0.0000401227497285243</v>
       </c>
     </row>
     <row r="171">
@@ -5945,25 +5945,25 @@
         <v>0</v>
       </c>
       <c r="D171" t="n">
-        <v>0.26</v>
+        <v>0.17</v>
       </c>
       <c r="E171" t="n">
-        <v>0.52</v>
+        <v>0.56</v>
       </c>
       <c r="F171" t="n">
-        <v>0.1</v>
+        <v>0.02</v>
       </c>
       <c r="G171" t="n">
-        <v>-0.36</v>
+        <v>-0.42</v>
       </c>
       <c r="H171" t="s">
         <v>49</v>
       </c>
       <c r="I171" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J171" t="n">
-        <v>0.0000402007020047588</v>
+        <v>0.0000401227497285243</v>
       </c>
     </row>
     <row r="172">
@@ -5977,25 +5977,25 @@
         <v>0</v>
       </c>
       <c r="D172" t="n">
-        <v>0.87</v>
+        <v>0.89</v>
       </c>
       <c r="E172" t="n">
-        <v>-0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="F172" t="n">
-        <v>-0.3</v>
+        <v>-0.29</v>
       </c>
       <c r="G172" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="H172" t="s">
         <v>49</v>
       </c>
       <c r="I172" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J172" t="n">
-        <v>0.0000402007020047588</v>
+        <v>0.0000401227497285243</v>
       </c>
     </row>
     <row r="173">
@@ -6009,25 +6009,25 @@
         <v>0</v>
       </c>
       <c r="D173" t="n">
-        <v>0.91</v>
+        <v>0.89</v>
       </c>
       <c r="E173" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="F173" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="G173" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="H173" t="s">
         <v>49</v>
       </c>
       <c r="I173" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J173" t="n">
-        <v>0.0000402007020047588</v>
+        <v>0.0000401227497285243</v>
       </c>
     </row>
     <row r="174">
@@ -6041,25 +6041,25 @@
         <v>1</v>
       </c>
       <c r="D174" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="E174" t="n">
-        <v>0.57</v>
+        <v>0.56</v>
       </c>
       <c r="F174" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="G174" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="H174" t="s">
         <v>49</v>
       </c>
       <c r="I174" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J174" t="n">
-        <v>0.0000402007020047588</v>
+        <v>0.0000401227497285243</v>
       </c>
     </row>
     <row r="175">
@@ -6073,25 +6073,25 @@
         <v>0</v>
       </c>
       <c r="D175" t="n">
-        <v>-4.73</v>
+        <v>-4.79</v>
       </c>
       <c r="E175" t="n">
         <v>-1.98</v>
       </c>
       <c r="F175" t="n">
-        <v>-1.73</v>
+        <v>-1.72</v>
       </c>
       <c r="G175" t="n">
-        <v>-1.02</v>
+        <v>-1.09</v>
       </c>
       <c r="H175" t="s">
         <v>49</v>
       </c>
       <c r="I175" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J175" t="n">
-        <v>0.0000402007020047588</v>
+        <v>0.0000401227497285243</v>
       </c>
     </row>
     <row r="176">
@@ -6108,7 +6108,7 @@
         <v>1.49</v>
       </c>
       <c r="E176" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="F176" t="n">
         <v>1.71</v>
@@ -6120,10 +6120,10 @@
         <v>49</v>
       </c>
       <c r="I176" t="n">
-        <v>809</v>
+        <v>769</v>
       </c>
       <c r="J176" t="n">
-        <v>0.0166296661733268</v>
+        <v>0.0163248843034858</v>
       </c>
     </row>
     <row r="177">
@@ -6137,25 +6137,25 @@
         <v>0</v>
       </c>
       <c r="D177" t="n">
-        <v>-0.08</v>
+        <v>0.13</v>
       </c>
       <c r="E177" t="n">
-        <v>-0.2</v>
+        <v>-0.12</v>
       </c>
       <c r="F177" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G177" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="H177" t="s">
         <v>49</v>
       </c>
       <c r="I177" t="n">
-        <v>809</v>
+        <v>769</v>
       </c>
       <c r="J177" t="n">
-        <v>0.0166296661733268</v>
+        <v>0.0163248843034858</v>
       </c>
     </row>
     <row r="178">
@@ -6169,25 +6169,25 @@
         <v>0</v>
       </c>
       <c r="D178" t="n">
-        <v>-1.05</v>
+        <v>-1.07</v>
       </c>
       <c r="E178" t="n">
-        <v>-0.6</v>
+        <v>-0.61</v>
       </c>
       <c r="F178" t="n">
-        <v>-0.92</v>
+        <v>-0.94</v>
       </c>
       <c r="G178" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="H178" t="s">
         <v>49</v>
       </c>
       <c r="I178" t="n">
-        <v>809</v>
+        <v>769</v>
       </c>
       <c r="J178" t="n">
-        <v>0.0166296661733268</v>
+        <v>0.0163248843034858</v>
       </c>
     </row>
     <row r="179">
@@ -6201,25 +6201,25 @@
         <v>0</v>
       </c>
       <c r="D179" t="n">
-        <v>-1.49</v>
+        <v>-1.5</v>
       </c>
       <c r="E179" t="n">
-        <v>-0.77</v>
+        <v>-0.78</v>
       </c>
       <c r="F179" t="n">
-        <v>-0.7</v>
+        <v>-0.71</v>
       </c>
       <c r="G179" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="H179" t="s">
         <v>49</v>
       </c>
       <c r="I179" t="n">
-        <v>809</v>
+        <v>769</v>
       </c>
       <c r="J179" t="n">
-        <v>0.0166296661733268</v>
+        <v>0.0163248843034858</v>
       </c>
     </row>
     <row r="180">
@@ -6233,25 +6233,25 @@
         <v>1</v>
       </c>
       <c r="D180" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="E180" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="F180" t="n">
-        <v>0.56</v>
+        <v>0.5</v>
       </c>
       <c r="G180" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="H180" t="s">
         <v>49</v>
       </c>
       <c r="I180" t="n">
-        <v>809</v>
+        <v>769</v>
       </c>
       <c r="J180" t="n">
-        <v>0.0166296661733268</v>
+        <v>0.0163248843034858</v>
       </c>
     </row>
     <row r="181">
@@ -6265,13 +6265,13 @@
         <v>0</v>
       </c>
       <c r="D181" t="n">
-        <v>-0.52</v>
+        <v>-0.55</v>
       </c>
       <c r="E181" t="n">
-        <v>-0.81</v>
+        <v>-0.82</v>
       </c>
       <c r="F181" t="n">
-        <v>-0.65</v>
+        <v>-0.66</v>
       </c>
       <c r="G181" t="n">
         <v>0.93</v>
@@ -6280,10 +6280,10 @@
         <v>49</v>
       </c>
       <c r="I181" t="n">
-        <v>809</v>
+        <v>769</v>
       </c>
       <c r="J181" t="n">
-        <v>0.0166296661733268</v>
+        <v>0.0163248843034858</v>
       </c>
     </row>
     <row r="182">
@@ -6315,7 +6315,7 @@
         <v>3</v>
       </c>
       <c r="J182" t="n">
-        <v>0.0000713707950706571</v>
+        <v>0.0000730549129428954</v>
       </c>
     </row>
     <row r="183">
@@ -6329,16 +6329,16 @@
         <v>0</v>
       </c>
       <c r="D183" t="n">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="E183" t="n">
-        <v>0.24</v>
+        <v>0.3</v>
       </c>
       <c r="F183" t="n">
-        <v>0.37</v>
+        <v>0.44</v>
       </c>
       <c r="G183" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="H183" t="s">
         <v>49</v>
@@ -6347,7 +6347,7 @@
         <v>3</v>
       </c>
       <c r="J183" t="n">
-        <v>0.0000713707950706571</v>
+        <v>0.0000730549129428954</v>
       </c>
     </row>
     <row r="184">
@@ -6361,13 +6361,13 @@
         <v>1</v>
       </c>
       <c r="D184" t="n">
-        <v>3.36</v>
+        <v>3.31</v>
       </c>
       <c r="E184" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="F184" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="G184" t="n">
         <v>0.89</v>
@@ -6379,7 +6379,7 @@
         <v>3</v>
       </c>
       <c r="J184" t="n">
-        <v>0.0000713707950706571</v>
+        <v>0.0000730549129428954</v>
       </c>
     </row>
     <row r="185">
@@ -6402,7 +6402,7 @@
         <v>-0.28</v>
       </c>
       <c r="G185" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="H185" t="s">
         <v>49</v>
@@ -6411,7 +6411,7 @@
         <v>3</v>
       </c>
       <c r="J185" t="n">
-        <v>0.0000713707950706571</v>
+        <v>0.0000730549129428954</v>
       </c>
     </row>
     <row r="186">
@@ -6425,13 +6425,13 @@
         <v>0</v>
       </c>
       <c r="D186" t="n">
-        <v>1.02</v>
+        <v>0.95</v>
       </c>
       <c r="E186" t="n">
-        <v>0.3</v>
+        <v>0.26</v>
       </c>
       <c r="F186" t="n">
-        <v>0.43</v>
+        <v>0.39</v>
       </c>
       <c r="G186" t="n">
         <v>0.29</v>
@@ -6443,7 +6443,7 @@
         <v>3</v>
       </c>
       <c r="J186" t="n">
-        <v>0.0000713707950706571</v>
+        <v>0.0000730549129428954</v>
       </c>
     </row>
     <row r="187">
@@ -6457,13 +6457,13 @@
         <v>0</v>
       </c>
       <c r="D187" t="n">
-        <v>-3.32</v>
+        <v>-3.35</v>
       </c>
       <c r="E187" t="n">
-        <v>-1.66</v>
+        <v>-1.67</v>
       </c>
       <c r="F187" t="n">
-        <v>-1.83</v>
+        <v>-1.84</v>
       </c>
       <c r="G187" t="n">
         <v>0.17</v>
@@ -6475,7 +6475,7 @@
         <v>3</v>
       </c>
       <c r="J187" t="n">
-        <v>0.0000713707950706571</v>
+        <v>0.0000730549129428954</v>
       </c>
     </row>
     <row r="188">
@@ -6489,16 +6489,16 @@
         <v>1</v>
       </c>
       <c r="D188" t="n">
-        <v>2.55</v>
+        <v>2.85</v>
       </c>
       <c r="E188" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="F188" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="G188" t="n">
-        <v>-0.47</v>
+        <v>-0.22</v>
       </c>
       <c r="H188" t="s">
         <v>49</v>
@@ -6507,7 +6507,7 @@
         <v>2</v>
       </c>
       <c r="J188" t="n">
-        <v>0.0000491654170456501</v>
+        <v>0.0000493254741411202</v>
       </c>
     </row>
     <row r="189">
@@ -6521,16 +6521,16 @@
         <v>0</v>
       </c>
       <c r="D189" t="n">
-        <v>-0.86</v>
+        <v>-0.94</v>
       </c>
       <c r="E189" t="n">
-        <v>-0.34</v>
+        <v>-0.36</v>
       </c>
       <c r="F189" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="G189" t="n">
-        <v>-0.69</v>
+        <v>-0.73</v>
       </c>
       <c r="H189" t="s">
         <v>49</v>
@@ -6539,7 +6539,7 @@
         <v>2</v>
       </c>
       <c r="J189" t="n">
-        <v>0.0000491654170456501</v>
+        <v>0.0000493254741411202</v>
       </c>
     </row>
     <row r="190">
@@ -6553,16 +6553,16 @@
         <v>0</v>
       </c>
       <c r="D190" t="n">
-        <v>-0.2</v>
+        <v>-0.18</v>
       </c>
       <c r="E190" t="n">
-        <v>-0.9</v>
+        <v>-0.87</v>
       </c>
       <c r="F190" t="n">
-        <v>-0.37</v>
+        <v>-0.35</v>
       </c>
       <c r="G190" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H190" t="s">
         <v>49</v>
@@ -6571,7 +6571,7 @@
         <v>2</v>
       </c>
       <c r="J190" t="n">
-        <v>0.0000491654170456501</v>
+        <v>0.0000493254741411202</v>
       </c>
     </row>
     <row r="191">
@@ -6585,16 +6585,16 @@
         <v>0</v>
       </c>
       <c r="D191" t="n">
-        <v>-0.39</v>
+        <v>-0.29</v>
       </c>
       <c r="E191" t="n">
-        <v>-0.08</v>
+        <v>-0.05</v>
       </c>
       <c r="F191" t="n">
-        <v>0.44</v>
+        <v>0.46</v>
       </c>
       <c r="G191" t="n">
-        <v>-0.75</v>
+        <v>-0.71</v>
       </c>
       <c r="H191" t="s">
         <v>49</v>
@@ -6603,7 +6603,7 @@
         <v>2</v>
       </c>
       <c r="J191" t="n">
-        <v>0.0000491654170456501</v>
+        <v>0.0000493254741411202</v>
       </c>
     </row>
     <row r="192">
@@ -6617,16 +6617,16 @@
         <v>0</v>
       </c>
       <c r="D192" t="n">
-        <v>-0.14</v>
+        <v>-0.5</v>
       </c>
       <c r="E192" t="n">
-        <v>0.04</v>
+        <v>-0.04</v>
       </c>
       <c r="F192" t="n">
-        <v>0.45</v>
+        <v>0.39</v>
       </c>
       <c r="G192" t="n">
-        <v>-0.63</v>
+        <v>-0.84</v>
       </c>
       <c r="H192" t="s">
         <v>49</v>
@@ -6635,7 +6635,7 @@
         <v>2</v>
       </c>
       <c r="J192" t="n">
-        <v>0.0000491654170456501</v>
+        <v>0.0000493254741411202</v>
       </c>
     </row>
     <row r="193">
@@ -6649,16 +6649,16 @@
         <v>0</v>
       </c>
       <c r="D193" t="n">
-        <v>-0.95</v>
+        <v>-0.94</v>
       </c>
       <c r="E193" t="n">
-        <v>-0.64</v>
+        <v>-0.61</v>
       </c>
       <c r="F193" t="n">
         <v>-1.79</v>
       </c>
       <c r="G193" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="H193" t="s">
         <v>49</v>
@@ -6667,7 +6667,7 @@
         <v>2</v>
       </c>
       <c r="J193" t="n">
-        <v>0.0000491654170456501</v>
+        <v>0.0000493254741411202</v>
       </c>
     </row>
     <row r="194">
@@ -6681,16 +6681,16 @@
         <v>0</v>
       </c>
       <c r="D194" t="n">
-        <v>-0.27</v>
+        <v>-0.41</v>
       </c>
       <c r="E194" t="n">
-        <v>0.53</v>
+        <v>0.44</v>
       </c>
       <c r="F194" t="n">
-        <v>0.56</v>
+        <v>0.51</v>
       </c>
       <c r="G194" t="n">
-        <v>-1.36</v>
+        <v>-1.37</v>
       </c>
       <c r="H194" t="s">
         <v>49</v>
@@ -6699,7 +6699,7 @@
         <v>1</v>
       </c>
       <c r="J194" t="n">
-        <v>0.0000275862068965517</v>
+        <v>0.000028246193825382</v>
       </c>
     </row>
     <row r="195">
@@ -6713,13 +6713,13 @@
         <v>0</v>
       </c>
       <c r="D195" t="n">
-        <v>-3.21</v>
+        <v>-2.7</v>
       </c>
       <c r="E195" t="n">
-        <v>-1.27</v>
+        <v>-1.04</v>
       </c>
       <c r="F195" t="n">
-        <v>-0.76</v>
+        <v>-0.48</v>
       </c>
       <c r="G195" t="n">
         <v>-1.18</v>
@@ -6731,7 +6731,7 @@
         <v>1</v>
       </c>
       <c r="J195" t="n">
-        <v>0.0000275862068965517</v>
+        <v>0.000028246193825382</v>
       </c>
     </row>
     <row r="196">
@@ -6745,16 +6745,16 @@
         <v>1</v>
       </c>
       <c r="D196" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="E196" t="n">
         <v>0.72</v>
       </c>
       <c r="F196" t="n">
-        <v>0.58</v>
+        <v>0.53</v>
       </c>
       <c r="G196" t="n">
-        <v>0.93</v>
+        <v>0.95</v>
       </c>
       <c r="H196" t="s">
         <v>49</v>
@@ -6763,7 +6763,7 @@
         <v>1</v>
       </c>
       <c r="J196" t="n">
-        <v>0.0000275862068965517</v>
+        <v>0.000028246193825382</v>
       </c>
     </row>
     <row r="197">
@@ -6777,16 +6777,16 @@
         <v>0</v>
       </c>
       <c r="D197" t="n">
-        <v>2.01</v>
+        <v>1.94</v>
       </c>
       <c r="E197" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="F197" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="G197" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="H197" t="s">
         <v>49</v>
@@ -6795,7 +6795,7 @@
         <v>1</v>
       </c>
       <c r="J197" t="n">
-        <v>0.0000275862068965517</v>
+        <v>0.000028246193825382</v>
       </c>
     </row>
     <row r="198">
@@ -6809,16 +6809,16 @@
         <v>0</v>
       </c>
       <c r="D198" t="n">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="E198" t="n">
-        <v>0.61</v>
+        <v>0.65</v>
       </c>
       <c r="F198" t="n">
         <v>0.62</v>
       </c>
       <c r="G198" t="n">
-        <v>0.41</v>
+        <v>0.45</v>
       </c>
       <c r="H198" t="s">
         <v>49</v>
@@ -6827,7 +6827,7 @@
         <v>1</v>
       </c>
       <c r="J198" t="n">
-        <v>0.0000275862068965517</v>
+        <v>0.000028246193825382</v>
       </c>
     </row>
     <row r="199">
@@ -6841,16 +6841,16 @@
         <v>0</v>
       </c>
       <c r="D199" t="n">
-        <v>-2.39</v>
+        <v>-2.75</v>
       </c>
       <c r="E199" t="n">
-        <v>-1.3</v>
+        <v>-1.5</v>
       </c>
       <c r="F199" t="n">
-        <v>-1.7</v>
+        <v>-1.84</v>
       </c>
       <c r="G199" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="H199" t="s">
         <v>49</v>
@@ -6859,7 +6859,7 @@
         <v>1</v>
       </c>
       <c r="J199" t="n">
-        <v>0.0000275862068965517</v>
+        <v>0.000028246193825382</v>
       </c>
     </row>
     <row r="200">
@@ -6873,13 +6873,13 @@
         <v>0</v>
       </c>
       <c r="D200" t="n">
-        <v>-1.62</v>
+        <v>-2.03</v>
       </c>
       <c r="E200" t="n">
-        <v>0.21</v>
+        <v>0.05</v>
       </c>
       <c r="F200" t="n">
-        <v>0.11</v>
+        <v>-0.14</v>
       </c>
       <c r="G200" t="n">
         <v>-1.94</v>
@@ -6891,7 +6891,7 @@
         <v>1</v>
       </c>
       <c r="J200" t="n">
-        <v>0.000116157509582995</v>
+        <v>0.00012045290291496</v>
       </c>
     </row>
     <row r="201">
@@ -6905,16 +6905,16 @@
         <v>1</v>
       </c>
       <c r="D201" t="n">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="E201" t="n">
-        <v>0.51</v>
+        <v>0.56</v>
       </c>
       <c r="F201" t="n">
-        <v>0.56</v>
+        <v>0.61</v>
       </c>
       <c r="G201" t="n">
-        <v>0.9</v>
+        <v>0.84</v>
       </c>
       <c r="H201" t="s">
         <v>49</v>
@@ -6923,7 +6923,7 @@
         <v>1</v>
       </c>
       <c r="J201" t="n">
-        <v>0.000116157509582995</v>
+        <v>0.00012045290291496</v>
       </c>
     </row>
     <row r="202">
@@ -6937,16 +6937,16 @@
         <v>0</v>
       </c>
       <c r="D202" t="n">
-        <v>0.98</v>
+        <v>1.13</v>
       </c>
       <c r="E202" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="F202" t="n">
-        <v>0.41</v>
+        <v>0.47</v>
       </c>
       <c r="G202" t="n">
-        <v>0.16</v>
+        <v>0.22</v>
       </c>
       <c r="H202" t="s">
         <v>49</v>
@@ -6955,7 +6955,7 @@
         <v>1</v>
       </c>
       <c r="J202" t="n">
-        <v>0.000116157509582995</v>
+        <v>0.00012045290291496</v>
       </c>
     </row>
     <row r="203">
@@ -6969,16 +6969,16 @@
         <v>0</v>
       </c>
       <c r="D203" t="n">
-        <v>1.11</v>
+        <v>0.92</v>
       </c>
       <c r="E203" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="F203" t="n">
-        <v>0.39</v>
+        <v>0.43</v>
       </c>
       <c r="G203" t="n">
-        <v>0.31</v>
+        <v>0.09</v>
       </c>
       <c r="H203" t="s">
         <v>49</v>
@@ -6987,7 +6987,7 @@
         <v>1</v>
       </c>
       <c r="J203" t="n">
-        <v>0.000116157509582995</v>
+        <v>0.00012045290291496</v>
       </c>
     </row>
     <row r="204">
@@ -7001,16 +7001,16 @@
         <v>0</v>
       </c>
       <c r="D204" t="n">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="E204" t="n">
-        <v>0.49</v>
+        <v>0.55</v>
       </c>
       <c r="F204" t="n">
-        <v>0.54</v>
+        <v>0.6</v>
       </c>
       <c r="G204" t="n">
-        <v>0.54</v>
+        <v>0.68</v>
       </c>
       <c r="H204" t="s">
         <v>49</v>
@@ -7019,7 +7019,7 @@
         <v>1</v>
       </c>
       <c r="J204" t="n">
-        <v>0.000116157509582995</v>
+        <v>0.00012045290291496</v>
       </c>
     </row>
     <row r="205">
@@ -7033,16 +7033,16 @@
         <v>0</v>
       </c>
       <c r="D205" t="n">
-        <v>-4.01</v>
+        <v>-3.85</v>
       </c>
       <c r="E205" t="n">
-        <v>-2.03</v>
+        <v>-2.01</v>
       </c>
       <c r="F205" t="n">
-        <v>-2.01</v>
+        <v>-1.96</v>
       </c>
       <c r="G205" t="n">
-        <v>0.04</v>
+        <v>0.11</v>
       </c>
       <c r="H205" t="s">
         <v>49</v>
@@ -7051,7 +7051,7 @@
         <v>1</v>
       </c>
       <c r="J205" t="n">
-        <v>0.000116157509582995</v>
+        <v>0.00012045290291496</v>
       </c>
     </row>
     <row r="206">
@@ -7065,16 +7065,16 @@
         <v>1</v>
       </c>
       <c r="D206" t="n">
-        <v>2</v>
+        <v>2.39</v>
       </c>
       <c r="E206" t="n">
-        <v>0.98</v>
+        <v>1.6</v>
       </c>
       <c r="F206" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="G206" t="n">
-        <v>0.7</v>
+        <v>0.39</v>
       </c>
       <c r="H206" t="s">
         <v>49</v>
@@ -7097,13 +7097,13 @@
         <v>0</v>
       </c>
       <c r="D207" t="n">
-        <v>0.82</v>
+        <v>0.38</v>
       </c>
       <c r="E207" t="n">
-        <v>0.35</v>
+        <v>-0.03</v>
       </c>
       <c r="F207" t="n">
-        <v>0.46</v>
+        <v>0.41</v>
       </c>
       <c r="G207"/>
       <c r="H207" t="s">
@@ -7127,13 +7127,13 @@
         <v>0</v>
       </c>
       <c r="D208" t="n">
-        <v>0.83</v>
+        <v>0.38</v>
       </c>
       <c r="E208" t="n">
-        <v>0.36</v>
+        <v>-0.03</v>
       </c>
       <c r="F208" t="n">
-        <v>0.46</v>
+        <v>0.41</v>
       </c>
       <c r="G208"/>
       <c r="H208" t="s">
@@ -7157,17 +7157,15 @@
         <v>0</v>
       </c>
       <c r="D209" t="n">
-        <v>-0.58</v>
+        <v>0.36</v>
       </c>
       <c r="E209" t="n">
-        <v>0.3</v>
+        <v>-0.04</v>
       </c>
       <c r="F209" t="n">
         <v>0.41</v>
       </c>
-      <c r="G209" t="n">
-        <v>-1.3</v>
-      </c>
+      <c r="G209"/>
       <c r="H209" t="s">
         <v>49</v>
       </c>
@@ -7189,16 +7187,16 @@
         <v>0</v>
       </c>
       <c r="D210" t="n">
-        <v>0.02</v>
+        <v>-0.66</v>
       </c>
       <c r="E210" t="n">
-        <v>-0.08</v>
+        <v>0.07</v>
       </c>
       <c r="F210" t="n">
-        <v>0.37</v>
+        <v>0.41</v>
       </c>
       <c r="G210" t="n">
-        <v>-0.27</v>
+        <v>-1.14</v>
       </c>
       <c r="H210" t="s">
         <v>49</v>
@@ -7221,16 +7219,16 @@
         <v>0</v>
       </c>
       <c r="D211" t="n">
-        <v>-3.08</v>
+        <v>-2.86</v>
       </c>
       <c r="E211" t="n">
-        <v>-1.92</v>
+        <v>-1.56</v>
       </c>
       <c r="F211" t="n">
         <v>-2.04</v>
       </c>
       <c r="G211" t="n">
-        <v>0.87</v>
+        <v>0.75</v>
       </c>
       <c r="H211" t="s">
         <v>49</v>
@@ -7253,16 +7251,16 @@
         <v>0</v>
       </c>
       <c r="D212" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="E212" t="n">
-        <v>0.32</v>
+        <v>0.36</v>
       </c>
       <c r="F212" t="n">
-        <v>0.4</v>
+        <v>0.42</v>
       </c>
       <c r="G212" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="H212" t="s">
         <v>49</v>
@@ -7271,7 +7269,7 @@
         <v>1</v>
       </c>
       <c r="J212" t="n">
-        <v>0.000208811860513677</v>
+        <v>0.000212856534695615</v>
       </c>
     </row>
     <row r="213">
@@ -7285,16 +7283,16 @@
         <v>0</v>
       </c>
       <c r="D213" t="n">
-        <v>1.62</v>
+        <v>1.46</v>
       </c>
       <c r="E213" t="n">
-        <v>0.58</v>
+        <v>0.49</v>
       </c>
       <c r="F213" t="n">
-        <v>0.59</v>
+        <v>0.56</v>
       </c>
       <c r="G213" t="n">
-        <v>0.46</v>
+        <v>0.42</v>
       </c>
       <c r="H213" t="s">
         <v>49</v>
@@ -7303,7 +7301,7 @@
         <v>1</v>
       </c>
       <c r="J213" t="n">
-        <v>0.000208811860513677</v>
+        <v>0.000212856534695615</v>
       </c>
     </row>
     <row r="214">
@@ -7320,13 +7318,13 @@
         <v>0.31</v>
       </c>
       <c r="E214" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="F214" t="n">
         <v>0</v>
       </c>
       <c r="G214" t="n">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="H214" t="s">
         <v>49</v>
@@ -7335,7 +7333,7 @@
         <v>1</v>
       </c>
       <c r="J214" t="n">
-        <v>0.000208811860513677</v>
+        <v>0.000212856534695615</v>
       </c>
     </row>
     <row r="215">
@@ -7349,16 +7347,16 @@
         <v>1</v>
       </c>
       <c r="D215" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="E215" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="F215" t="n">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
       <c r="G215" t="n">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="H215" t="s">
         <v>49</v>
@@ -7367,7 +7365,7 @@
         <v>1</v>
       </c>
       <c r="J215" t="n">
-        <v>0.000208811860513677</v>
+        <v>0.000212856534695615</v>
       </c>
     </row>
     <row r="216">
@@ -7381,16 +7379,16 @@
         <v>0</v>
       </c>
       <c r="D216" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="E216" t="n">
-        <v>0.47</v>
+        <v>0.49</v>
       </c>
       <c r="F216" t="n">
-        <v>0.43</v>
+        <v>0.46</v>
       </c>
       <c r="G216" t="n">
-        <v>0.31</v>
+        <v>0.35</v>
       </c>
       <c r="H216" t="s">
         <v>49</v>
@@ -7399,7 +7397,7 @@
         <v>1</v>
       </c>
       <c r="J216" t="n">
-        <v>0.000208811860513677</v>
+        <v>0.000212856534695615</v>
       </c>
     </row>
     <row r="217">
@@ -7419,7 +7417,7 @@
         <v>-1.99</v>
       </c>
       <c r="F217" t="n">
-        <v>-1.99</v>
+        <v>-2</v>
       </c>
       <c r="G217" t="n">
         <v>-2.04</v>
@@ -7431,7 +7429,7 @@
         <v>1</v>
       </c>
       <c r="J217" t="n">
-        <v>0.000208811860513677</v>
+        <v>0.000212856534695615</v>
       </c>
     </row>
     <row r="218">
@@ -7445,16 +7443,16 @@
         <v>1</v>
       </c>
       <c r="D218" t="n">
-        <v>1.65</v>
+        <v>2.48</v>
       </c>
       <c r="E218" t="n">
-        <v>0.67</v>
+        <v>1.59</v>
       </c>
       <c r="F218" t="n">
-        <v>0.43</v>
+        <v>0.48</v>
       </c>
       <c r="G218" t="n">
-        <v>0.55</v>
+        <v>0.41</v>
       </c>
       <c r="H218" t="s">
         <v>49</v>
@@ -7463,7 +7461,7 @@
         <v>35</v>
       </c>
       <c r="J218" t="n">
-        <v>0.00951345474313672</v>
+        <v>0.00952640174197061</v>
       </c>
     </row>
     <row r="219">
@@ -7477,15 +7475,17 @@
         <v>0</v>
       </c>
       <c r="D219" t="n">
-        <v>0.87</v>
+        <v>-1.95</v>
       </c>
       <c r="E219" t="n">
-        <v>0.47</v>
+        <v>-0.29</v>
       </c>
       <c r="F219" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G219"/>
+        <v>0.38</v>
+      </c>
+      <c r="G219" t="n">
+        <v>-2.04</v>
+      </c>
       <c r="H219" t="s">
         <v>49</v>
       </c>
@@ -7493,7 +7493,7 @@
         <v>35</v>
       </c>
       <c r="J219" t="n">
-        <v>0.00951345474313672</v>
+        <v>0.00952640174197061</v>
       </c>
     </row>
     <row r="220">
@@ -7507,16 +7507,16 @@
         <v>0</v>
       </c>
       <c r="D220" t="n">
-        <v>-0.18</v>
+        <v>0.39</v>
       </c>
       <c r="E220" t="n">
-        <v>0.24</v>
+        <v>-0.41</v>
       </c>
       <c r="F220" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="G220" t="n">
         <v>0.41</v>
-      </c>
-      <c r="G220" t="n">
-        <v>-0.83</v>
       </c>
       <c r="H220" t="s">
         <v>49</v>
@@ -7525,7 +7525,7 @@
         <v>35</v>
       </c>
       <c r="J220" t="n">
-        <v>0.00951345474313672</v>
+        <v>0.00952640174197061</v>
       </c>
     </row>
     <row r="221">
@@ -7539,16 +7539,16 @@
         <v>0</v>
       </c>
       <c r="D221" t="n">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="E221" t="n">
-        <v>0.57</v>
+        <v>0.12</v>
       </c>
       <c r="F221" t="n">
         <v>0.39</v>
       </c>
       <c r="G221" t="n">
-        <v>-0.01</v>
+        <v>0.41</v>
       </c>
       <c r="H221" t="s">
         <v>49</v>
@@ -7557,7 +7557,7 @@
         <v>35</v>
       </c>
       <c r="J221" t="n">
-        <v>0.00951345474313672</v>
+        <v>0.00952640174197061</v>
       </c>
     </row>
     <row r="222">
@@ -7571,16 +7571,16 @@
         <v>0</v>
       </c>
       <c r="D222" t="n">
-        <v>-0.63</v>
+        <v>1.23</v>
       </c>
       <c r="E222" t="n">
-        <v>0.03</v>
+        <v>0.41</v>
       </c>
       <c r="F222" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G222" t="n">
         <v>0.41</v>
-      </c>
-      <c r="G222" t="n">
-        <v>-1.07</v>
       </c>
       <c r="H222" t="s">
         <v>49</v>
@@ -7589,7 +7589,7 @@
         <v>35</v>
       </c>
       <c r="J222" t="n">
-        <v>0.00951345474313672</v>
+        <v>0.00952640174197061</v>
       </c>
     </row>
     <row r="223">
@@ -7603,16 +7603,16 @@
         <v>0</v>
       </c>
       <c r="D223" t="n">
-        <v>-2.66</v>
+        <v>-3.06</v>
       </c>
       <c r="E223" t="n">
-        <v>-1.99</v>
+        <v>-1.42</v>
       </c>
       <c r="F223" t="n">
         <v>-2.04</v>
       </c>
       <c r="G223" t="n">
-        <v>1.37</v>
+        <v>0.41</v>
       </c>
       <c r="H223" t="s">
         <v>49</v>
@@ -7621,7 +7621,7 @@
         <v>35</v>
       </c>
       <c r="J223" t="n">
-        <v>0.00951345474313672</v>
+        <v>0.00952640174197061</v>
       </c>
     </row>
   </sheetData>

--- a/Outcome/Appendix/figure_data/fig6.xlsx
+++ b/Outcome/Appendix/figure_data/fig6.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
   <si>
     <t xml:space="preserve">disease</t>
   </si>
@@ -89,9 +89,6 @@
     <t xml:space="preserve">TBM</t>
   </si>
   <si>
-    <t xml:space="preserve">Leprosy</t>
-  </si>
-  <si>
     <t xml:space="preserve">Dengue fever</t>
   </si>
   <si>
@@ -111,9 +108,6 @@
   </si>
   <si>
     <t xml:space="preserve">Streptococcus suis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EM</t>
   </si>
   <si>
     <t xml:space="preserve">Gonorrhoea</t>
@@ -158,12 +152,6 @@
     <t xml:space="preserve">Rubella</t>
   </si>
   <si>
-    <t xml:space="preserve">Other tetanus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pertussis</t>
-  </si>
-  <si>
     <t xml:space="preserve">HFMD</t>
   </si>
   <si>
@@ -186,12 +174,6 @@
   </si>
   <si>
     <t xml:space="preserve">Liver fluke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paratyphoid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cholera</t>
   </si>
 </sst>
 </file>
@@ -1931,37 +1913,37 @@
         <v>25</v>
       </c>
       <c r="B38" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C38" t="n">
-        <v>86.11</v>
+        <v>199.08</v>
       </c>
       <c r="D38" t="n">
-        <v>1.95</v>
+        <v>4465.21</v>
       </c>
       <c r="E38" t="n">
-        <v>3.73</v>
+        <v>5.03</v>
       </c>
       <c r="F38" t="n">
-        <v>0.29</v>
+        <v>0.94</v>
       </c>
       <c r="G38" t="n">
-        <v>1.64</v>
+        <v>-0.41</v>
       </c>
       <c r="H38" t="n">
-        <v>1.62</v>
+        <v>-0.05</v>
       </c>
       <c r="I38" t="n">
-        <v>0.22</v>
+        <v>0.33</v>
       </c>
       <c r="J38" t="n">
-        <v>3.48</v>
+        <v>-0.13</v>
       </c>
       <c r="K38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L38" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
     </row>
     <row r="39">
@@ -1969,37 +1951,37 @@
         <v>25</v>
       </c>
       <c r="B39" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C39" t="n">
-        <v>132.27</v>
+        <v>199.38</v>
       </c>
       <c r="D39" t="n">
-        <v>4.03</v>
+        <v>8610.71</v>
       </c>
       <c r="E39" t="n">
-        <v>3.57</v>
+        <v>3.43</v>
       </c>
       <c r="F39" t="n">
-        <v>0.28</v>
+        <v>0.91</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.85</v>
+        <v>-0.41</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.67</v>
+        <v>-1.5</v>
       </c>
       <c r="I39" t="n">
-        <v>0.27</v>
+        <v>0.44</v>
       </c>
       <c r="J39" t="n">
-        <v>-1.25</v>
+        <v>-1.47</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
     </row>
     <row r="40">
@@ -2007,37 +1989,37 @@
         <v>25</v>
       </c>
       <c r="B40" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C40" t="n">
-        <v>118.07</v>
+        <v>11.03</v>
       </c>
       <c r="D40" t="n">
-        <v>3.52</v>
+        <v>1.19</v>
       </c>
       <c r="E40" t="n">
-        <v>9.82</v>
+        <v>3.55</v>
       </c>
       <c r="F40" t="n">
-        <v>0.01</v>
+        <v>0.67</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.08</v>
+        <v>2.04</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.12</v>
+        <v>1.51</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.97</v>
+        <v>0.44</v>
       </c>
       <c r="J40" t="n">
-        <v>-2.17</v>
+        <v>3.98</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
     </row>
     <row r="41">
@@ -2045,37 +2027,37 @@
         <v>25</v>
       </c>
       <c r="B41" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C41" t="n">
-        <v>138.6</v>
+        <v>198.76</v>
       </c>
       <c r="D41" t="n">
-        <v>4.63</v>
+        <v>2804.24</v>
       </c>
       <c r="E41" t="n">
-        <v>3.57</v>
+        <v>37.76</v>
       </c>
       <c r="F41" t="n">
-        <v>0.29</v>
+        <v>0.01</v>
       </c>
       <c r="G41" t="n">
-        <v>-1.19</v>
+        <v>-0.4</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.33</v>
+        <v>0.53</v>
       </c>
       <c r="I41" t="n">
-        <v>0.28</v>
+        <v>-2.04</v>
       </c>
       <c r="J41" t="n">
-        <v>-2.25</v>
+        <v>-1.92</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
     </row>
     <row r="42">
@@ -2083,37 +2065,37 @@
         <v>25</v>
       </c>
       <c r="B42" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C42" t="n">
-        <v>114.56</v>
+        <v>199.13</v>
       </c>
       <c r="D42" t="n">
-        <v>3.27</v>
+        <v>5609.73</v>
       </c>
       <c r="E42" t="n">
-        <v>3.56</v>
+        <v>3.85</v>
       </c>
       <c r="F42" t="n">
-        <v>0.03</v>
+        <v>0.87</v>
       </c>
       <c r="G42" t="n">
-        <v>0.11</v>
+        <v>-0.41</v>
       </c>
       <c r="H42" t="n">
-        <v>0.16</v>
+        <v>-0.45</v>
       </c>
       <c r="I42" t="n">
-        <v>0.28</v>
+        <v>0.41</v>
       </c>
       <c r="J42" t="n">
-        <v>0.54</v>
+        <v>-0.45</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
     </row>
     <row r="43">
@@ -2121,265 +2103,265 @@
         <v>25</v>
       </c>
       <c r="B43" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C43" t="n">
-        <v>109.71</v>
+        <v>199.01</v>
       </c>
       <c r="D43" t="n">
-        <v>3.1</v>
+        <v>4418.99</v>
       </c>
       <c r="E43" t="n">
-        <v>1.76</v>
+        <v>3.82</v>
       </c>
       <c r="F43" t="n">
-        <v>0.05</v>
+        <v>0.87</v>
       </c>
       <c r="G43" t="n">
-        <v>0.37</v>
+        <v>-0.41</v>
       </c>
       <c r="H43" t="n">
-        <v>0.35</v>
+        <v>-0.04</v>
       </c>
       <c r="I43" t="n">
-        <v>0.92</v>
+        <v>0.42</v>
       </c>
       <c r="J43" t="n">
-        <v>1.64</v>
+        <v>-0.03</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
       </c>
       <c r="L43" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B44" t="s">
         <v>18</v>
       </c>
       <c r="C44" t="n">
-        <v>199.08</v>
+        <v>183.51</v>
       </c>
       <c r="D44" t="n">
-        <v>4465.21</v>
+        <v>128.04</v>
       </c>
       <c r="E44" t="n">
-        <v>5.03</v>
+        <v>4.01</v>
       </c>
       <c r="F44" t="n">
-        <v>0.94</v>
+        <v>0.84</v>
       </c>
       <c r="G44" t="n">
         <v>-0.41</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.05</v>
+        <v>-0.34</v>
       </c>
       <c r="I44" t="n">
-        <v>0.33</v>
+        <v>-0.16</v>
       </c>
       <c r="J44" t="n">
-        <v>-0.13</v>
+        <v>-0.91</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
+        <v>27</v>
+      </c>
+      <c r="B45" t="s">
+        <v>19</v>
+      </c>
+      <c r="C45" t="n">
+        <v>183.06</v>
+      </c>
+      <c r="D45" t="n">
+        <v>132.09</v>
+      </c>
+      <c r="E45" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="G45" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="H45" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="J45" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="s">
         <v>26</v>
-      </c>
-      <c r="B45" t="s">
-        <v>13</v>
-      </c>
-      <c r="C45" t="n">
-        <v>199.38</v>
-      </c>
-      <c r="D45" t="n">
-        <v>8610.71</v>
-      </c>
-      <c r="E45" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="F45" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="G45" t="n">
-        <v>-0.41</v>
-      </c>
-      <c r="H45" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="I45" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="J45" t="n">
-        <v>-1.47</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
+        <v>27</v>
+      </c>
+      <c r="B46" t="s">
+        <v>17</v>
+      </c>
+      <c r="C46" t="n">
+        <v>181.22</v>
+      </c>
+      <c r="D46" t="n">
+        <v>115.45</v>
+      </c>
+      <c r="E46" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="G46" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="H46" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="J46" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="s">
         <v>26</v>
-      </c>
-      <c r="B46" t="s">
-        <v>16</v>
-      </c>
-      <c r="C46" t="n">
-        <v>11.03</v>
-      </c>
-      <c r="D46" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="E46" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="F46" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="G46" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="H46" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="I46" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="J46" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="K46" t="n">
-        <v>1</v>
-      </c>
-      <c r="L46" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
+        <v>27</v>
+      </c>
+      <c r="B47" t="s">
+        <v>16</v>
+      </c>
+      <c r="C47" t="n">
+        <v>6.24</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E47" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G47" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="H47" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="I47" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="J47" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="K47" t="n">
+        <v>1</v>
+      </c>
+      <c r="L47" t="s">
         <v>26</v>
-      </c>
-      <c r="B47" t="s">
-        <v>15</v>
-      </c>
-      <c r="C47" t="n">
-        <v>198.76</v>
-      </c>
-      <c r="D47" t="n">
-        <v>2804.24</v>
-      </c>
-      <c r="E47" t="n">
-        <v>37.76</v>
-      </c>
-      <c r="F47" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G47" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="H47" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="I47" t="n">
-        <v>-2.04</v>
-      </c>
-      <c r="J47" t="n">
-        <v>-1.92</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0</v>
-      </c>
-      <c r="L47" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
+        <v>27</v>
+      </c>
+      <c r="B48" t="s">
+        <v>15</v>
+      </c>
+      <c r="C48" t="n">
+        <v>184.25</v>
+      </c>
+      <c r="D48" t="n">
+        <v>121.93</v>
+      </c>
+      <c r="E48" t="n">
+        <v>6.51</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G48" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="H48" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="I48" t="n">
+        <v>-1.65</v>
+      </c>
+      <c r="J48" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="s">
         <v>26</v>
-      </c>
-      <c r="B48" t="s">
-        <v>19</v>
-      </c>
-      <c r="C48" t="n">
-        <v>199.13</v>
-      </c>
-      <c r="D48" t="n">
-        <v>5609.73</v>
-      </c>
-      <c r="E48" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="F48" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="G48" t="n">
-        <v>-0.41</v>
-      </c>
-      <c r="H48" t="n">
-        <v>-0.45</v>
-      </c>
-      <c r="I48" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="J48" t="n">
-        <v>-0.45</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
+        <v>27</v>
+      </c>
+      <c r="B49" t="s">
+        <v>13</v>
+      </c>
+      <c r="C49" t="n">
+        <v>185.92</v>
+      </c>
+      <c r="D49" t="n">
+        <v>158.28</v>
+      </c>
+      <c r="E49" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="G49" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="H49" t="n">
+        <v>-0.88</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="J49" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="s">
         <v>26</v>
-      </c>
-      <c r="B49" t="s">
-        <v>17</v>
-      </c>
-      <c r="C49" t="n">
-        <v>199.01</v>
-      </c>
-      <c r="D49" t="n">
-        <v>4418.99</v>
-      </c>
-      <c r="E49" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="F49" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="G49" t="n">
-        <v>-0.41</v>
-      </c>
-      <c r="H49" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="I49" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="J49" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="50">
@@ -2390,34 +2372,34 @@
         <v>18</v>
       </c>
       <c r="C50" t="n">
-        <v>183.51</v>
+        <v>196.32</v>
       </c>
       <c r="D50" t="n">
-        <v>128.04</v>
+        <v>827.69</v>
       </c>
       <c r="E50" t="n">
-        <v>4.01</v>
+        <v>5.96</v>
       </c>
       <c r="F50" t="n">
-        <v>0.84</v>
+        <v>0.87</v>
       </c>
       <c r="G50" t="n">
         <v>-0.41</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.34</v>
+        <v>-0.4</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.16</v>
+        <v>-0.33</v>
       </c>
       <c r="J50" t="n">
-        <v>-0.91</v>
+        <v>-1.14</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
       </c>
       <c r="L50" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="51">
@@ -2428,34 +2410,34 @@
         <v>19</v>
       </c>
       <c r="C51" t="n">
-        <v>183.06</v>
+        <v>196.23</v>
       </c>
       <c r="D51" t="n">
-        <v>132.09</v>
+        <v>827.9</v>
       </c>
       <c r="E51" t="n">
-        <v>3.35</v>
+        <v>5.25</v>
       </c>
       <c r="F51" t="n">
-        <v>0.79</v>
+        <v>0.9</v>
       </c>
       <c r="G51" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="H51" t="n">
         <v>-0.4</v>
       </c>
-      <c r="H51" t="n">
-        <v>-0.41</v>
-      </c>
       <c r="I51" t="n">
-        <v>0.23</v>
+        <v>-0.04</v>
       </c>
       <c r="J51" t="n">
-        <v>-0.58</v>
+        <v>-0.85</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
       </c>
       <c r="L51" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="52">
@@ -2463,37 +2445,37 @@
         <v>28</v>
       </c>
       <c r="B52" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C52" t="n">
-        <v>181.22</v>
+        <v>1.95</v>
       </c>
       <c r="D52" t="n">
-        <v>115.45</v>
+        <v>0.18</v>
       </c>
       <c r="E52" t="n">
-        <v>3.59</v>
+        <v>0.62</v>
       </c>
       <c r="F52" t="n">
-        <v>0.82</v>
+        <v>0.88</v>
       </c>
       <c r="G52" t="n">
-        <v>-0.38</v>
+        <v>2.04</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.11</v>
+        <v>2.04</v>
       </c>
       <c r="I52" t="n">
-        <v>0.09</v>
+        <v>1.85</v>
       </c>
       <c r="J52" t="n">
-        <v>-0.4</v>
+        <v>5.93</v>
       </c>
       <c r="K52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L52" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="53">
@@ -2501,37 +2483,37 @@
         <v>28</v>
       </c>
       <c r="B53" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C53" t="n">
-        <v>6.24</v>
+        <v>196.42</v>
       </c>
       <c r="D53" t="n">
-        <v>0.35</v>
+        <v>869.31</v>
       </c>
       <c r="E53" t="n">
-        <v>1.25</v>
+        <v>5.44</v>
       </c>
       <c r="F53" t="n">
         <v>0.88</v>
       </c>
       <c r="G53" t="n">
-        <v>2.04</v>
+        <v>-0.41</v>
       </c>
       <c r="H53" t="n">
-        <v>1.97</v>
+        <v>-0.53</v>
       </c>
       <c r="I53" t="n">
-        <v>1.48</v>
+        <v>-0.12</v>
       </c>
       <c r="J53" t="n">
-        <v>5.49</v>
+        <v>-1.06</v>
       </c>
       <c r="K53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L53" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="54">
@@ -2539,37 +2521,37 @@
         <v>28</v>
       </c>
       <c r="B54" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C54" t="n">
-        <v>184.25</v>
+        <v>196.2</v>
       </c>
       <c r="D54" t="n">
-        <v>121.93</v>
+        <v>807.32</v>
       </c>
       <c r="E54" t="n">
-        <v>6.51</v>
+        <v>5.54</v>
       </c>
       <c r="F54" t="n">
-        <v>0.8</v>
+        <v>0.89</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.42</v>
+        <v>-0.41</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.23</v>
+        <v>-0.34</v>
       </c>
       <c r="I54" t="n">
-        <v>-1.65</v>
+        <v>-0.16</v>
       </c>
       <c r="J54" t="n">
-        <v>-2.3</v>
+        <v>-0.91</v>
       </c>
       <c r="K54" t="n">
         <v>0</v>
       </c>
       <c r="L54" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="55">
@@ -2577,37 +2559,37 @@
         <v>28</v>
       </c>
       <c r="B55" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C55" t="n">
-        <v>185.92</v>
+        <v>196.4</v>
       </c>
       <c r="D55" t="n">
-        <v>158.28</v>
+        <v>811.44</v>
       </c>
       <c r="E55" t="n">
-        <v>3.7</v>
+        <v>8.09</v>
       </c>
       <c r="F55" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.44</v>
+        <v>-0.41</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.88</v>
+        <v>-0.36</v>
       </c>
       <c r="I55" t="n">
-        <v>0.02</v>
+        <v>-1.2</v>
       </c>
       <c r="J55" t="n">
-        <v>-1.3</v>
+        <v>-1.97</v>
       </c>
       <c r="K55" t="n">
         <v>0</v>
       </c>
       <c r="L55" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="56">
@@ -2615,37 +2597,37 @@
         <v>29</v>
       </c>
       <c r="B56" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C56" t="n">
-        <v>196.32</v>
+        <v>184.86</v>
       </c>
       <c r="D56" t="n">
-        <v>827.69</v>
+        <v>329.62</v>
       </c>
       <c r="E56" t="n">
-        <v>5.96</v>
+        <v>4.28</v>
       </c>
       <c r="F56" t="n">
-        <v>0.87</v>
+        <v>0.01</v>
       </c>
       <c r="G56" t="n">
-        <v>-0.41</v>
+        <v>-0.24</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.4</v>
+        <v>0.59</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.33</v>
+        <v>0.42</v>
       </c>
       <c r="J56" t="n">
-        <v>-1.14</v>
+        <v>0.77</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
       </c>
       <c r="L56" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="57">
@@ -2653,37 +2635,37 @@
         <v>29</v>
       </c>
       <c r="B57" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C57" t="n">
-        <v>196.23</v>
+        <v>199.63</v>
       </c>
       <c r="D57" t="n">
-        <v>827.9</v>
+        <v>9767.13</v>
       </c>
       <c r="E57" t="n">
-        <v>5.25</v>
+        <v>5.7</v>
       </c>
       <c r="F57" t="n">
-        <v>0.9</v>
+        <v>0.18</v>
       </c>
       <c r="G57" t="n">
-        <v>-0.41</v>
+        <v>-0.47</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.4</v>
+        <v>-2</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.04</v>
+        <v>-0.35</v>
       </c>
       <c r="J57" t="n">
-        <v>-0.85</v>
+        <v>-2.81</v>
       </c>
       <c r="K57" t="n">
         <v>0</v>
       </c>
       <c r="L57" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="58">
@@ -2691,37 +2673,37 @@
         <v>29</v>
       </c>
       <c r="B58" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C58" t="n">
-        <v>1.95</v>
+        <v>198.36</v>
       </c>
       <c r="D58" t="n">
-        <v>0.18</v>
+        <v>1750.27</v>
       </c>
       <c r="E58" t="n">
-        <v>0.62</v>
+        <v>7.45</v>
       </c>
       <c r="F58" t="n">
-        <v>0.88</v>
+        <v>0.32</v>
       </c>
       <c r="G58" t="n">
-        <v>2.04</v>
+        <v>-0.45</v>
       </c>
       <c r="H58" t="n">
-        <v>2.04</v>
+        <v>0.2</v>
       </c>
       <c r="I58" t="n">
-        <v>1.85</v>
+        <v>-1.29</v>
       </c>
       <c r="J58" t="n">
-        <v>5.93</v>
+        <v>-1.53</v>
       </c>
       <c r="K58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L58" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="59">
@@ -2729,37 +2711,37 @@
         <v>29</v>
       </c>
       <c r="B59" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C59" t="n">
-        <v>196.42</v>
+        <v>197.56</v>
       </c>
       <c r="D59" t="n">
-        <v>869.31</v>
+        <v>1740.04</v>
       </c>
       <c r="E59" t="n">
-        <v>5.44</v>
+        <v>2.42</v>
       </c>
       <c r="F59" t="n">
-        <v>0.88</v>
+        <v>0.55</v>
       </c>
       <c r="G59" t="n">
-        <v>-0.41</v>
+        <v>-0.44</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.53</v>
+        <v>0.2</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.12</v>
+        <v>1.42</v>
       </c>
       <c r="J59" t="n">
-        <v>-1.06</v>
+        <v>1.19</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>
       </c>
       <c r="L59" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="60">
@@ -2767,37 +2749,37 @@
         <v>29</v>
       </c>
       <c r="B60" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C60" t="n">
-        <v>196.2</v>
+        <v>41.83</v>
       </c>
       <c r="D60" t="n">
-        <v>807.32</v>
+        <v>4.13</v>
       </c>
       <c r="E60" t="n">
-        <v>5.54</v>
+        <v>5.43</v>
       </c>
       <c r="F60" t="n">
-        <v>0.89</v>
+        <v>0.4</v>
       </c>
       <c r="G60" t="n">
-        <v>-0.41</v>
+        <v>2.03</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.34</v>
+        <v>0.68</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.16</v>
+        <v>-0.2</v>
       </c>
       <c r="J60" t="n">
-        <v>-0.91</v>
+        <v>2.51</v>
       </c>
       <c r="K60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L60" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="61">
@@ -2805,37 +2787,31 @@
         <v>29</v>
       </c>
       <c r="B61" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C61" t="n">
-        <v>196.4</v>
+        <v>197.95</v>
       </c>
       <c r="D61" t="n">
-        <v>811.44</v>
-      </c>
-      <c r="E61" t="n">
-        <v>8.09</v>
-      </c>
-      <c r="F61" t="n">
-        <v>0.71</v>
-      </c>
+        <v>1324.55</v>
+      </c>
+      <c r="E61"/>
+      <c r="F61"/>
       <c r="G61" t="n">
-        <v>-0.41</v>
+        <v>-0.44</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.36</v>
-      </c>
-      <c r="I61" t="n">
-        <v>-1.2</v>
-      </c>
+        <v>0.32</v>
+      </c>
+      <c r="I61"/>
       <c r="J61" t="n">
-        <v>-1.97</v>
+        <v>-0.12</v>
       </c>
       <c r="K61" t="n">
         <v>0</v>
       </c>
       <c r="L61" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="62">
@@ -2843,37 +2819,37 @@
         <v>30</v>
       </c>
       <c r="B62" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C62" t="n">
-        <v>184.86</v>
+        <v>189.76</v>
       </c>
       <c r="D62" t="n">
-        <v>329.62</v>
+        <v>241.98</v>
       </c>
       <c r="E62" t="n">
-        <v>4.28</v>
+        <v>4.38</v>
       </c>
       <c r="F62" t="n">
-        <v>0.01</v>
+        <v>0.61</v>
       </c>
       <c r="G62" t="n">
-        <v>-0.24</v>
+        <v>-0.4</v>
       </c>
       <c r="H62" t="n">
-        <v>0.59</v>
+        <v>-0.37</v>
       </c>
       <c r="I62" t="n">
-        <v>0.42</v>
+        <v>-0.22</v>
       </c>
       <c r="J62" t="n">
-        <v>0.77</v>
+        <v>-0.99</v>
       </c>
       <c r="K62" t="n">
         <v>0</v>
       </c>
       <c r="L62" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="63">
@@ -2881,37 +2857,37 @@
         <v>30</v>
       </c>
       <c r="B63" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C63" t="n">
-        <v>199.63</v>
+        <v>189.69</v>
       </c>
       <c r="D63" t="n">
-        <v>9767.13</v>
+        <v>241.81</v>
       </c>
       <c r="E63" t="n">
-        <v>5.7</v>
+        <v>4.28</v>
       </c>
       <c r="F63" t="n">
-        <v>0.18</v>
+        <v>0.58</v>
       </c>
       <c r="G63" t="n">
-        <v>-0.47</v>
+        <v>-0.4</v>
       </c>
       <c r="H63" t="n">
-        <v>-2</v>
+        <v>-0.37</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.35</v>
+        <v>-0.15</v>
       </c>
       <c r="J63" t="n">
-        <v>-2.81</v>
+        <v>-0.92</v>
       </c>
       <c r="K63" t="n">
         <v>0</v>
       </c>
       <c r="L63" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="64">
@@ -2919,37 +2895,37 @@
         <v>30</v>
       </c>
       <c r="B64" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C64" t="n">
-        <v>198.36</v>
+        <v>190.81</v>
       </c>
       <c r="D64" t="n">
-        <v>1750.27</v>
+        <v>260.45</v>
       </c>
       <c r="E64" t="n">
-        <v>7.45</v>
+        <v>5.11</v>
       </c>
       <c r="F64" t="n">
-        <v>0.32</v>
+        <v>0.61</v>
       </c>
       <c r="G64" t="n">
-        <v>-0.45</v>
+        <v>-0.42</v>
       </c>
       <c r="H64" t="n">
-        <v>0.2</v>
+        <v>-0.56</v>
       </c>
       <c r="I64" t="n">
-        <v>-1.29</v>
+        <v>-0.72</v>
       </c>
       <c r="J64" t="n">
-        <v>-1.53</v>
+        <v>-1.69</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
       </c>
       <c r="L64" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="65">
@@ -2957,37 +2933,37 @@
         <v>30</v>
       </c>
       <c r="B65" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C65" t="n">
-        <v>197.56</v>
+        <v>4.98</v>
       </c>
       <c r="D65" t="n">
-        <v>1740.04</v>
+        <v>0.32</v>
       </c>
       <c r="E65" t="n">
-        <v>2.42</v>
+        <v>1.18</v>
       </c>
       <c r="F65" t="n">
-        <v>0.55</v>
+        <v>0.6</v>
       </c>
       <c r="G65" t="n">
-        <v>-0.44</v>
+        <v>2.04</v>
       </c>
       <c r="H65" t="n">
-        <v>0.2</v>
+        <v>2.04</v>
       </c>
       <c r="I65" t="n">
-        <v>1.42</v>
+        <v>2</v>
       </c>
       <c r="J65" t="n">
-        <v>1.19</v>
+        <v>6.07</v>
       </c>
       <c r="K65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L65" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="66">
@@ -2995,37 +2971,37 @@
         <v>30</v>
       </c>
       <c r="B66" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C66" t="n">
-        <v>41.83</v>
+        <v>189.83</v>
       </c>
       <c r="D66" t="n">
-        <v>4.13</v>
+        <v>238.48</v>
       </c>
       <c r="E66" t="n">
-        <v>5.43</v>
+        <v>4.66</v>
       </c>
       <c r="F66" t="n">
-        <v>0.4</v>
+        <v>0.59</v>
       </c>
       <c r="G66" t="n">
-        <v>2.03</v>
+        <v>-0.41</v>
       </c>
       <c r="H66" t="n">
-        <v>0.68</v>
+        <v>-0.34</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.2</v>
+        <v>-0.41</v>
       </c>
       <c r="J66" t="n">
-        <v>2.51</v>
+        <v>-1.15</v>
       </c>
       <c r="K66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L66" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="67">
@@ -3033,31 +3009,37 @@
         <v>30</v>
       </c>
       <c r="B67" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C67" t="n">
-        <v>197.95</v>
+        <v>190.02</v>
       </c>
       <c r="D67" t="n">
-        <v>1324.55</v>
-      </c>
-      <c r="E67"/>
-      <c r="F67"/>
+        <v>244.86</v>
+      </c>
+      <c r="E67" t="n">
+        <v>4.79</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0.61</v>
+      </c>
       <c r="G67" t="n">
-        <v>-0.44</v>
+        <v>-0.41</v>
       </c>
       <c r="H67" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="I67"/>
+        <v>-0.4</v>
+      </c>
+      <c r="I67" t="n">
+        <v>-0.5</v>
+      </c>
       <c r="J67" t="n">
-        <v>-0.12</v>
+        <v>-1.31</v>
       </c>
       <c r="K67" t="n">
         <v>0</v>
       </c>
       <c r="L67" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="68">
@@ -3068,34 +3050,34 @@
         <v>13</v>
       </c>
       <c r="C68" t="n">
-        <v>189.76</v>
+        <v>152.92</v>
       </c>
       <c r="D68" t="n">
-        <v>241.98</v>
+        <v>25.72</v>
       </c>
       <c r="E68" t="n">
-        <v>4.38</v>
+        <v>4.15</v>
       </c>
       <c r="F68" t="n">
-        <v>0.61</v>
+        <v>0.89</v>
       </c>
       <c r="G68" t="n">
         <v>-0.4</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.37</v>
+        <v>-0.39</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.22</v>
+        <v>-0.45</v>
       </c>
       <c r="J68" t="n">
-        <v>-0.99</v>
+        <v>-1.23</v>
       </c>
       <c r="K68" t="n">
         <v>0</v>
       </c>
       <c r="L68" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="69">
@@ -3103,37 +3085,37 @@
         <v>31</v>
       </c>
       <c r="B69" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C69" t="n">
-        <v>189.69</v>
+        <v>156.44</v>
       </c>
       <c r="D69" t="n">
-        <v>241.81</v>
+        <v>28.31</v>
       </c>
       <c r="E69" t="n">
-        <v>4.28</v>
+        <v>4.11</v>
       </c>
       <c r="F69" t="n">
-        <v>0.58</v>
+        <v>0.88</v>
       </c>
       <c r="G69" t="n">
-        <v>-0.4</v>
+        <v>-0.46</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.37</v>
+        <v>-0.63</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.15</v>
+        <v>-0.42</v>
       </c>
       <c r="J69" t="n">
-        <v>-0.92</v>
+        <v>-1.51</v>
       </c>
       <c r="K69" t="n">
         <v>0</v>
       </c>
       <c r="L69" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="70">
@@ -3141,37 +3123,37 @@
         <v>31</v>
       </c>
       <c r="B70" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C70" t="n">
-        <v>190.81</v>
+        <v>153.45</v>
       </c>
       <c r="D70" t="n">
-        <v>260.45</v>
+        <v>25.37</v>
       </c>
       <c r="E70" t="n">
-        <v>5.11</v>
+        <v>4.21</v>
       </c>
       <c r="F70" t="n">
-        <v>0.61</v>
+        <v>0.91</v>
       </c>
       <c r="G70" t="n">
-        <v>-0.42</v>
+        <v>-0.41</v>
       </c>
       <c r="H70" t="n">
-        <v>-0.56</v>
+        <v>-0.35</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.72</v>
+        <v>-0.49</v>
       </c>
       <c r="J70" t="n">
-        <v>-1.69</v>
+        <v>-1.25</v>
       </c>
       <c r="K70" t="n">
         <v>0</v>
       </c>
       <c r="L70" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="71">
@@ -3179,37 +3161,37 @@
         <v>31</v>
       </c>
       <c r="B71" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C71" t="n">
-        <v>4.98</v>
+        <v>152.75</v>
       </c>
       <c r="D71" t="n">
-        <v>0.32</v>
+        <v>25.55</v>
       </c>
       <c r="E71" t="n">
-        <v>1.18</v>
+        <v>3.97</v>
       </c>
       <c r="F71" t="n">
-        <v>0.6</v>
+        <v>0.91</v>
       </c>
       <c r="G71" t="n">
-        <v>2.04</v>
+        <v>-0.39</v>
       </c>
       <c r="H71" t="n">
-        <v>2.04</v>
+        <v>-0.37</v>
       </c>
       <c r="I71" t="n">
-        <v>2</v>
+        <v>-0.31</v>
       </c>
       <c r="J71" t="n">
-        <v>6.07</v>
+        <v>-1.08</v>
       </c>
       <c r="K71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L71" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="72">
@@ -3217,37 +3199,37 @@
         <v>31</v>
       </c>
       <c r="B72" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C72" t="n">
-        <v>189.83</v>
+        <v>5.19</v>
       </c>
       <c r="D72" t="n">
-        <v>238.48</v>
+        <v>0.24</v>
       </c>
       <c r="E72" t="n">
-        <v>4.66</v>
+        <v>0.8</v>
       </c>
       <c r="F72" t="n">
-        <v>0.59</v>
+        <v>0.87</v>
       </c>
       <c r="G72" t="n">
-        <v>-0.41</v>
+        <v>2.04</v>
       </c>
       <c r="H72" t="n">
-        <v>-0.34</v>
+        <v>2.03</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.41</v>
+        <v>2.04</v>
       </c>
       <c r="J72" t="n">
-        <v>-1.15</v>
+        <v>6.1</v>
       </c>
       <c r="K72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L72" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="73">
@@ -3255,37 +3237,37 @@
         <v>31</v>
       </c>
       <c r="B73" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C73" t="n">
-        <v>190.02</v>
+        <v>152.32</v>
       </c>
       <c r="D73" t="n">
-        <v>244.86</v>
+        <v>24.59</v>
       </c>
       <c r="E73" t="n">
-        <v>4.79</v>
+        <v>4.03</v>
       </c>
       <c r="F73" t="n">
-        <v>0.61</v>
+        <v>0.76</v>
       </c>
       <c r="G73" t="n">
-        <v>-0.41</v>
+        <v>-0.39</v>
       </c>
       <c r="H73" t="n">
-        <v>-0.4</v>
+        <v>-0.28</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.5</v>
+        <v>-0.36</v>
       </c>
       <c r="J73" t="n">
-        <v>-1.31</v>
+        <v>-1.03</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
       </c>
       <c r="L73" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="74">
@@ -3293,37 +3275,37 @@
         <v>32</v>
       </c>
       <c r="B74" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C74" t="n">
-        <v>152.92</v>
+        <v>196.97</v>
       </c>
       <c r="D74" t="n">
-        <v>25.72</v>
+        <v>872.94</v>
       </c>
       <c r="E74" t="n">
-        <v>4.15</v>
+        <v>19.3</v>
       </c>
       <c r="F74" t="n">
-        <v>0.89</v>
+        <v>0.56</v>
       </c>
       <c r="G74" t="n">
-        <v>-0.4</v>
+        <v>-0.41</v>
       </c>
       <c r="H74" t="n">
-        <v>-0.39</v>
+        <v>-0.42</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.45</v>
+        <v>0.05</v>
       </c>
       <c r="J74" t="n">
-        <v>-1.23</v>
+        <v>-0.77</v>
       </c>
       <c r="K74" t="n">
         <v>0</v>
       </c>
       <c r="L74" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
     </row>
     <row r="75">
@@ -3334,34 +3316,34 @@
         <v>17</v>
       </c>
       <c r="C75" t="n">
-        <v>156.44</v>
+        <v>197.08</v>
       </c>
       <c r="D75" t="n">
-        <v>28.31</v>
+        <v>907.87</v>
       </c>
       <c r="E75" t="n">
-        <v>4.11</v>
+        <v>17.37</v>
       </c>
       <c r="F75" t="n">
-        <v>0.88</v>
+        <v>0.55</v>
       </c>
       <c r="G75" t="n">
-        <v>-0.46</v>
+        <v>-0.41</v>
       </c>
       <c r="H75" t="n">
-        <v>-0.63</v>
+        <v>-0.51</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.42</v>
+        <v>0.17</v>
       </c>
       <c r="J75" t="n">
-        <v>-1.51</v>
+        <v>-0.76</v>
       </c>
       <c r="K75" t="n">
         <v>0</v>
       </c>
       <c r="L75" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
     </row>
     <row r="76">
@@ -3369,37 +3351,37 @@
         <v>32</v>
       </c>
       <c r="B76" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C76" t="n">
-        <v>153.45</v>
+        <v>197</v>
       </c>
       <c r="D76" t="n">
-        <v>25.37</v>
+        <v>887.09</v>
       </c>
       <c r="E76" t="n">
-        <v>4.21</v>
+        <v>16.39</v>
       </c>
       <c r="F76" t="n">
-        <v>0.91</v>
+        <v>0.58</v>
       </c>
       <c r="G76" t="n">
         <v>-0.41</v>
       </c>
       <c r="H76" t="n">
-        <v>-0.35</v>
+        <v>-0.46</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.49</v>
+        <v>0.22</v>
       </c>
       <c r="J76" t="n">
-        <v>-1.25</v>
+        <v>-0.64</v>
       </c>
       <c r="K76" t="n">
         <v>0</v>
       </c>
       <c r="L76" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
     </row>
     <row r="77">
@@ -3407,37 +3389,37 @@
         <v>32</v>
       </c>
       <c r="B77" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C77" t="n">
-        <v>152.75</v>
+        <v>1.97</v>
       </c>
       <c r="D77" t="n">
-        <v>25.55</v>
+        <v>0.15</v>
       </c>
       <c r="E77" t="n">
-        <v>3.97</v>
+        <v>2.39</v>
       </c>
       <c r="F77" t="n">
-        <v>0.91</v>
+        <v>0.52</v>
       </c>
       <c r="G77" t="n">
-        <v>-0.39</v>
+        <v>2.04</v>
       </c>
       <c r="H77" t="n">
-        <v>-0.37</v>
+        <v>2.03</v>
       </c>
       <c r="I77" t="n">
-        <v>-0.31</v>
+        <v>1.04</v>
       </c>
       <c r="J77" t="n">
-        <v>-1.08</v>
+        <v>5.12</v>
       </c>
       <c r="K77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L77" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
     </row>
     <row r="78">
@@ -3445,37 +3427,37 @@
         <v>32</v>
       </c>
       <c r="B78" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C78" t="n">
-        <v>5.19</v>
+        <v>196.77</v>
       </c>
       <c r="D78" t="n">
-        <v>0.24</v>
+        <v>815.36</v>
       </c>
       <c r="E78" t="n">
-        <v>0.8</v>
+        <v>53.02</v>
       </c>
       <c r="F78" t="n">
-        <v>0.87</v>
+        <v>0.51</v>
       </c>
       <c r="G78" t="n">
-        <v>2.04</v>
+        <v>-0.41</v>
       </c>
       <c r="H78" t="n">
-        <v>2.03</v>
+        <v>-0.25</v>
       </c>
       <c r="I78" t="n">
-        <v>2.04</v>
+        <v>-1.91</v>
       </c>
       <c r="J78" t="n">
-        <v>6.1</v>
+        <v>-2.57</v>
       </c>
       <c r="K78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L78" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
     </row>
     <row r="79">
@@ -3483,493 +3465,493 @@
         <v>32</v>
       </c>
       <c r="B79" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C79" t="n">
-        <v>152.32</v>
+        <v>196.93</v>
       </c>
       <c r="D79" t="n">
-        <v>24.59</v>
+        <v>865.25</v>
       </c>
       <c r="E79" t="n">
-        <v>4.03</v>
+        <v>12.98</v>
       </c>
       <c r="F79" t="n">
-        <v>0.76</v>
+        <v>0.47</v>
       </c>
       <c r="G79" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="H79" t="n">
         <v>-0.39</v>
       </c>
-      <c r="H79" t="n">
-        <v>-0.28</v>
-      </c>
       <c r="I79" t="n">
-        <v>-0.36</v>
+        <v>0.42</v>
       </c>
       <c r="J79" t="n">
-        <v>-1.03</v>
+        <v>-0.38</v>
       </c>
       <c r="K79" t="n">
         <v>0</v>
       </c>
       <c r="L79" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
+        <v>34</v>
+      </c>
+      <c r="B80" t="s">
+        <v>16</v>
+      </c>
+      <c r="C80" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="D80" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="G80" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="H80" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="I80" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="J80" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="K80" t="n">
+        <v>1</v>
+      </c>
+      <c r="L80" t="s">
         <v>33</v>
-      </c>
-      <c r="B80" t="s">
-        <v>17</v>
-      </c>
-      <c r="C80" t="n">
-        <v>147.99</v>
-      </c>
-      <c r="D80" t="n">
-        <v>13.41</v>
-      </c>
-      <c r="E80" t="n">
-        <v>15.65</v>
-      </c>
-      <c r="F80" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="G80" t="n">
-        <v>-0.36</v>
-      </c>
-      <c r="H80" t="n">
-        <v>-0.15</v>
-      </c>
-      <c r="I80" t="n">
-        <v>-1.91</v>
-      </c>
-      <c r="J80" t="n">
-        <v>-2.42</v>
-      </c>
-      <c r="K80" t="n">
-        <v>0</v>
-      </c>
-      <c r="L80" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
+        <v>34</v>
+      </c>
+      <c r="B81" t="s">
+        <v>17</v>
+      </c>
+      <c r="C81" t="n">
+        <v>196.02</v>
+      </c>
+      <c r="D81" t="n">
+        <v>643.65</v>
+      </c>
+      <c r="E81" t="n">
+        <v>10.42</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="G81" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="H81" t="n">
+        <v>-0.54</v>
+      </c>
+      <c r="I81" t="n">
+        <v>-0.52</v>
+      </c>
+      <c r="J81" t="n">
+        <v>-1.48</v>
+      </c>
+      <c r="K81" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" t="s">
         <v>33</v>
-      </c>
-      <c r="B81" t="s">
-        <v>16</v>
-      </c>
-      <c r="C81" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="D81" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="E81" t="n">
-        <v>4.68</v>
-      </c>
-      <c r="F81" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="G81" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="H81" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="I81" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="J81" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="K81" t="n">
-        <v>1</v>
-      </c>
-      <c r="L81" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
+        <v>34</v>
+      </c>
+      <c r="B82" t="s">
+        <v>19</v>
+      </c>
+      <c r="C82" t="n">
+        <v>195.65</v>
+      </c>
+      <c r="D82" t="n">
+        <v>589.18</v>
+      </c>
+      <c r="E82" t="n">
+        <v>11.15</v>
+      </c>
+      <c r="F82" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G82" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="H82" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="I82" t="n">
+        <v>-0.71</v>
+      </c>
+      <c r="J82" t="n">
+        <v>-1.44</v>
+      </c>
+      <c r="K82" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" t="s">
         <v>33</v>
-      </c>
-      <c r="B82" t="s">
-        <v>18</v>
-      </c>
-      <c r="C82" t="n">
-        <v>150.63</v>
-      </c>
-      <c r="D82" t="n">
-        <v>14.51</v>
-      </c>
-      <c r="E82" t="n">
-        <v>7.67</v>
-      </c>
-      <c r="F82" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="G82" t="n">
-        <v>-0.41</v>
-      </c>
-      <c r="H82" t="n">
-        <v>-0.34</v>
-      </c>
-      <c r="I82" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="J82" t="n">
-        <v>-0.87</v>
-      </c>
-      <c r="K82" t="n">
-        <v>0</v>
-      </c>
-      <c r="L82" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
+        <v>34</v>
+      </c>
+      <c r="B83" t="s">
+        <v>15</v>
+      </c>
+      <c r="C83" t="n">
+        <v>195.73</v>
+      </c>
+      <c r="D83" t="n">
+        <v>597.76</v>
+      </c>
+      <c r="E83" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="F83" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G83" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="H83" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="I83" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="J83" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="K83" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" t="s">
         <v>33</v>
-      </c>
-      <c r="B83" t="s">
-        <v>19</v>
-      </c>
-      <c r="C83" t="n">
-        <v>151.62</v>
-      </c>
-      <c r="D83" t="n">
-        <v>15.19</v>
-      </c>
-      <c r="E83" t="n">
-        <v>6.62</v>
-      </c>
-      <c r="F83" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G83" t="n">
-        <v>-0.43</v>
-      </c>
-      <c r="H83" t="n">
-        <v>-0.45</v>
-      </c>
-      <c r="I83" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="J83" t="n">
-        <v>-0.77</v>
-      </c>
-      <c r="K83" t="n">
-        <v>0</v>
-      </c>
-      <c r="L83" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B84" t="s">
         <v>13</v>
       </c>
       <c r="C84" t="n">
-        <v>153.53</v>
+        <v>195.79</v>
       </c>
       <c r="D84" t="n">
-        <v>16.17</v>
+        <v>609.88</v>
       </c>
       <c r="E84" t="n">
-        <v>4.94</v>
+        <v>9.71</v>
       </c>
       <c r="F84" t="n">
-        <v>0.15</v>
+        <v>0.85</v>
       </c>
       <c r="G84" t="n">
-        <v>-0.47</v>
+        <v>-0.41</v>
       </c>
       <c r="H84" t="n">
-        <v>-0.62</v>
+        <v>-0.41</v>
       </c>
       <c r="I84" t="n">
-        <v>0.49</v>
+        <v>-0.34</v>
       </c>
       <c r="J84" t="n">
-        <v>-0.6</v>
+        <v>-1.16</v>
       </c>
       <c r="K84" t="n">
         <v>0</v>
       </c>
       <c r="L84" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
+        <v>34</v>
+      </c>
+      <c r="B85" t="s">
+        <v>18</v>
+      </c>
+      <c r="C85" t="n">
+        <v>195.79</v>
+      </c>
+      <c r="D85" t="n">
+        <v>608.7</v>
+      </c>
+      <c r="E85" t="n">
+        <v>10.34</v>
+      </c>
+      <c r="F85" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G85" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="H85" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="I85" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="J85" t="n">
+        <v>-1.31</v>
+      </c>
+      <c r="K85" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" t="s">
         <v>33</v>
-      </c>
-      <c r="B85" t="s">
-        <v>15</v>
-      </c>
-      <c r="C85" t="n">
-        <v>149.08</v>
-      </c>
-      <c r="D85" t="n">
-        <v>15.21</v>
-      </c>
-      <c r="E85" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="F85" t="n">
-        <v>0</v>
-      </c>
-      <c r="G85" t="n">
-        <v>-0.38</v>
-      </c>
-      <c r="H85" t="n">
-        <v>-0.46</v>
-      </c>
-      <c r="I85" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="J85" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="K85" t="n">
-        <v>0</v>
-      </c>
-      <c r="L85" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B86" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C86" t="n">
-        <v>196.97</v>
+        <v>196.34</v>
       </c>
       <c r="D86" t="n">
-        <v>872.94</v>
+        <v>745.44</v>
       </c>
       <c r="E86" t="n">
-        <v>19.3</v>
+        <v>8.24</v>
       </c>
       <c r="F86" t="n">
-        <v>0.56</v>
+        <v>0.5</v>
       </c>
       <c r="G86" t="n">
         <v>-0.41</v>
       </c>
       <c r="H86" t="n">
-        <v>-0.42</v>
+        <v>-0.37</v>
       </c>
       <c r="I86" t="n">
-        <v>0.05</v>
+        <v>-0.19</v>
       </c>
       <c r="J86" t="n">
-        <v>-0.77</v>
+        <v>-0.97</v>
       </c>
       <c r="K86" t="n">
         <v>0</v>
       </c>
       <c r="L86" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B87" t="s">
         <v>17</v>
       </c>
       <c r="C87" t="n">
-        <v>197.08</v>
+        <v>196.35</v>
       </c>
       <c r="D87" t="n">
-        <v>907.87</v>
+        <v>724.06</v>
       </c>
       <c r="E87" t="n">
-        <v>17.37</v>
+        <v>9.29</v>
       </c>
       <c r="F87" t="n">
-        <v>0.55</v>
+        <v>0.79</v>
       </c>
       <c r="G87" t="n">
         <v>-0.41</v>
       </c>
       <c r="H87" t="n">
-        <v>-0.51</v>
+        <v>-0.3</v>
       </c>
       <c r="I87" t="n">
-        <v>0.17</v>
+        <v>-0.5</v>
       </c>
       <c r="J87" t="n">
-        <v>-0.76</v>
+        <v>-1.21</v>
       </c>
       <c r="K87" t="n">
         <v>0</v>
       </c>
       <c r="L87" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B88" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C88" t="n">
-        <v>197</v>
+        <v>196.37</v>
       </c>
       <c r="D88" t="n">
-        <v>887.09</v>
+        <v>728.38</v>
       </c>
       <c r="E88" t="n">
-        <v>16.39</v>
+        <v>11.1</v>
       </c>
       <c r="F88" t="n">
-        <v>0.58</v>
+        <v>0.5</v>
       </c>
       <c r="G88" t="n">
         <v>-0.41</v>
       </c>
       <c r="H88" t="n">
-        <v>-0.46</v>
+        <v>-0.32</v>
       </c>
       <c r="I88" t="n">
-        <v>0.22</v>
+        <v>-1.03</v>
       </c>
       <c r="J88" t="n">
-        <v>-0.64</v>
+        <v>-1.75</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
       </c>
       <c r="L88" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B89" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C89" t="n">
-        <v>1.97</v>
+        <v>196.06</v>
       </c>
       <c r="D89" t="n">
-        <v>0.15</v>
+        <v>690.55</v>
       </c>
       <c r="E89" t="n">
-        <v>2.39</v>
+        <v>8.45</v>
       </c>
       <c r="F89" t="n">
-        <v>0.52</v>
+        <v>0.56</v>
       </c>
       <c r="G89" t="n">
-        <v>2.04</v>
+        <v>-0.4</v>
       </c>
       <c r="H89" t="n">
-        <v>2.03</v>
+        <v>-0.2</v>
       </c>
       <c r="I89" t="n">
-        <v>1.04</v>
+        <v>-0.25</v>
       </c>
       <c r="J89" t="n">
-        <v>5.12</v>
+        <v>-0.85</v>
       </c>
       <c r="K89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L89" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B90" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C90" t="n">
-        <v>196.77</v>
+        <v>1.99</v>
       </c>
       <c r="D90" t="n">
-        <v>815.36</v>
+        <v>0.16</v>
       </c>
       <c r="E90" t="n">
-        <v>53.02</v>
+        <v>1.13</v>
       </c>
       <c r="F90" t="n">
-        <v>0.51</v>
+        <v>0.47</v>
       </c>
       <c r="G90" t="n">
-        <v>-0.41</v>
+        <v>2.04</v>
       </c>
       <c r="H90" t="n">
-        <v>-0.25</v>
+        <v>1.99</v>
       </c>
       <c r="I90" t="n">
-        <v>-1.91</v>
+        <v>1.89</v>
       </c>
       <c r="J90" t="n">
-        <v>-2.57</v>
+        <v>5.93</v>
       </c>
       <c r="K90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L90" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B91" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C91" t="n">
-        <v>196.93</v>
+        <v>196.97</v>
       </c>
       <c r="D91" t="n">
-        <v>865.25</v>
+        <v>883.59</v>
       </c>
       <c r="E91" t="n">
-        <v>12.98</v>
+        <v>7.31</v>
       </c>
       <c r="F91" t="n">
-        <v>0.47</v>
+        <v>0.27</v>
       </c>
       <c r="G91" t="n">
-        <v>-0.41</v>
+        <v>-0.42</v>
       </c>
       <c r="H91" t="n">
-        <v>-0.39</v>
+        <v>-0.81</v>
       </c>
       <c r="I91" t="n">
-        <v>0.42</v>
+        <v>0.08</v>
       </c>
       <c r="J91" t="n">
-        <v>-0.38</v>
+        <v>-1.14</v>
       </c>
       <c r="K91" t="n">
         <v>0</v>
       </c>
       <c r="L91" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="92">
@@ -3980,34 +3962,34 @@
         <v>16</v>
       </c>
       <c r="C92" t="n">
-        <v>1.11</v>
+        <v>1.45</v>
       </c>
       <c r="D92" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="E92" t="n">
-        <v>0.65</v>
+        <v>0.92</v>
       </c>
       <c r="F92" t="n">
-        <v>0.78</v>
+        <v>0.68</v>
       </c>
       <c r="G92" t="n">
         <v>2.04</v>
       </c>
       <c r="H92" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="I92" t="n">
-        <v>1.96</v>
+        <v>1.54</v>
       </c>
       <c r="J92" t="n">
-        <v>6.04</v>
+        <v>5.62</v>
       </c>
       <c r="K92" t="n">
         <v>1</v>
       </c>
       <c r="L92" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="93">
@@ -4018,34 +4000,34 @@
         <v>17</v>
       </c>
       <c r="C93" t="n">
-        <v>196.02</v>
+        <v>194.03</v>
       </c>
       <c r="D93" t="n">
-        <v>643.65</v>
+        <v>388.37</v>
       </c>
       <c r="E93" t="n">
-        <v>10.42</v>
+        <v>10.08</v>
       </c>
       <c r="F93" t="n">
-        <v>0.82</v>
+        <v>0.7</v>
       </c>
       <c r="G93" t="n">
         <v>-0.41</v>
       </c>
       <c r="H93" t="n">
-        <v>-0.54</v>
+        <v>-0.59</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.52</v>
+        <v>0.08</v>
       </c>
       <c r="J93" t="n">
-        <v>-1.48</v>
+        <v>-0.92</v>
       </c>
       <c r="K93" t="n">
         <v>0</v>
       </c>
       <c r="L93" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="94">
@@ -4056,34 +4038,34 @@
         <v>19</v>
       </c>
       <c r="C94" t="n">
-        <v>195.65</v>
+        <v>193.46</v>
       </c>
       <c r="D94" t="n">
-        <v>589.18</v>
+        <v>354.51</v>
       </c>
       <c r="E94" t="n">
-        <v>11.15</v>
+        <v>8.62</v>
       </c>
       <c r="F94" t="n">
-        <v>0.8</v>
+        <v>0.56</v>
       </c>
       <c r="G94" t="n">
         <v>-0.41</v>
       </c>
       <c r="H94" t="n">
-        <v>-0.32</v>
+        <v>-0.36</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.71</v>
+        <v>0.31</v>
       </c>
       <c r="J94" t="n">
-        <v>-1.44</v>
+        <v>-0.46</v>
       </c>
       <c r="K94" t="n">
         <v>0</v>
       </c>
       <c r="L94" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="95">
@@ -4094,34 +4076,34 @@
         <v>15</v>
       </c>
       <c r="C95" t="n">
-        <v>195.73</v>
+        <v>193.41</v>
       </c>
       <c r="D95" t="n">
-        <v>597.76</v>
+        <v>345.97</v>
       </c>
       <c r="E95" t="n">
-        <v>7.9</v>
+        <v>20.22</v>
       </c>
       <c r="F95" t="n">
-        <v>0.75</v>
+        <v>0.81</v>
       </c>
       <c r="G95" t="n">
         <v>-0.41</v>
       </c>
       <c r="H95" t="n">
-        <v>-0.36</v>
+        <v>-0.3</v>
       </c>
       <c r="I95" t="n">
-        <v>0.12</v>
+        <v>-1.55</v>
       </c>
       <c r="J95" t="n">
-        <v>-0.65</v>
+        <v>-2.25</v>
       </c>
       <c r="K95" t="n">
         <v>0</v>
       </c>
       <c r="L95" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="96">
@@ -4129,28 +4111,28 @@
         <v>36</v>
       </c>
       <c r="B96" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C96" t="n">
-        <v>195.79</v>
+        <v>193.61</v>
       </c>
       <c r="D96" t="n">
-        <v>609.88</v>
+        <v>360.05</v>
       </c>
       <c r="E96" t="n">
-        <v>9.71</v>
+        <v>12.8</v>
       </c>
       <c r="F96" t="n">
-        <v>0.85</v>
+        <v>0.7</v>
       </c>
       <c r="G96" t="n">
         <v>-0.41</v>
       </c>
       <c r="H96" t="n">
-        <v>-0.41</v>
+        <v>-0.4</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.34</v>
+        <v>-0.36</v>
       </c>
       <c r="J96" t="n">
         <v>-1.16</v>
@@ -4159,7 +4141,7 @@
         <v>0</v>
       </c>
       <c r="L96" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="97">
@@ -4167,37 +4149,37 @@
         <v>36</v>
       </c>
       <c r="B97" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C97" t="n">
-        <v>195.79</v>
+        <v>193.5</v>
       </c>
       <c r="D97" t="n">
-        <v>608.7</v>
+        <v>357.88</v>
       </c>
       <c r="E97" t="n">
-        <v>10.34</v>
+        <v>10.74</v>
       </c>
       <c r="F97" t="n">
-        <v>0.84</v>
+        <v>0.7</v>
       </c>
       <c r="G97" t="n">
         <v>-0.41</v>
       </c>
       <c r="H97" t="n">
-        <v>-0.4</v>
+        <v>-0.38</v>
       </c>
       <c r="I97" t="n">
-        <v>-0.5</v>
+        <v>-0.03</v>
       </c>
       <c r="J97" t="n">
-        <v>-1.31</v>
+        <v>-0.82</v>
       </c>
       <c r="K97" t="n">
         <v>0</v>
       </c>
       <c r="L97" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="98">
@@ -4205,37 +4187,37 @@
         <v>37</v>
       </c>
       <c r="B98" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C98" t="n">
-        <v>196.34</v>
+        <v>188.08</v>
       </c>
       <c r="D98" t="n">
-        <v>745.44</v>
+        <v>162.09</v>
       </c>
       <c r="E98" t="n">
-        <v>8.24</v>
+        <v>49.18</v>
       </c>
       <c r="F98" t="n">
-        <v>0.5</v>
+        <v>0.04</v>
       </c>
       <c r="G98" t="n">
-        <v>-0.41</v>
+        <v>-0.4</v>
       </c>
       <c r="H98" t="n">
-        <v>-0.37</v>
+        <v>-0.31</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.19</v>
+        <v>-1.84</v>
       </c>
       <c r="J98" t="n">
-        <v>-0.97</v>
+        <v>-2.55</v>
       </c>
       <c r="K98" t="n">
         <v>0</v>
       </c>
       <c r="L98" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="99">
@@ -4243,37 +4225,37 @@
         <v>37</v>
       </c>
       <c r="B99" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C99" t="n">
-        <v>196.35</v>
+        <v>188.5</v>
       </c>
       <c r="D99" t="n">
-        <v>724.06</v>
+        <v>169.25</v>
       </c>
       <c r="E99" t="n">
-        <v>9.29</v>
+        <v>16.56</v>
       </c>
       <c r="F99" t="n">
-        <v>0.79</v>
+        <v>0.03</v>
       </c>
       <c r="G99" t="n">
         <v>-0.41</v>
       </c>
       <c r="H99" t="n">
-        <v>-0.3</v>
+        <v>-0.41</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.5</v>
+        <v>0.12</v>
       </c>
       <c r="J99" t="n">
-        <v>-1.21</v>
+        <v>-0.7</v>
       </c>
       <c r="K99" t="n">
         <v>0</v>
       </c>
       <c r="L99" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="100">
@@ -4281,37 +4263,37 @@
         <v>37</v>
       </c>
       <c r="B100" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C100" t="n">
-        <v>196.37</v>
+        <v>2.77</v>
       </c>
       <c r="D100" t="n">
-        <v>728.38</v>
+        <v>0.15</v>
       </c>
       <c r="E100" t="n">
-        <v>11.1</v>
+        <v>1.6</v>
       </c>
       <c r="F100" t="n">
-        <v>0.5</v>
+        <v>0.04</v>
       </c>
       <c r="G100" t="n">
-        <v>-0.41</v>
+        <v>2.04</v>
       </c>
       <c r="H100" t="n">
-        <v>-0.32</v>
+        <v>2.03</v>
       </c>
       <c r="I100" t="n">
-        <v>-1.03</v>
+        <v>1.02</v>
       </c>
       <c r="J100" t="n">
-        <v>-1.75</v>
+        <v>5.09</v>
       </c>
       <c r="K100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L100" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="101">
@@ -4322,34 +4304,34 @@
         <v>19</v>
       </c>
       <c r="C101" t="n">
-        <v>196.06</v>
+        <v>189.02</v>
       </c>
       <c r="D101" t="n">
-        <v>690.55</v>
+        <v>179.08</v>
       </c>
       <c r="E101" t="n">
-        <v>8.45</v>
+        <v>10.05</v>
       </c>
       <c r="F101" t="n">
-        <v>0.56</v>
+        <v>0.05</v>
       </c>
       <c r="G101" t="n">
-        <v>-0.4</v>
+        <v>-0.42</v>
       </c>
       <c r="H101" t="n">
-        <v>-0.2</v>
+        <v>-0.55</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.25</v>
+        <v>0.51</v>
       </c>
       <c r="J101" t="n">
-        <v>-0.85</v>
+        <v>-0.46</v>
       </c>
       <c r="K101" t="n">
         <v>0</v>
       </c>
       <c r="L101" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="102">
@@ -4357,37 +4339,37 @@
         <v>37</v>
       </c>
       <c r="B102" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C102" t="n">
-        <v>1.99</v>
+        <v>188.83</v>
       </c>
       <c r="D102" t="n">
-        <v>0.16</v>
+        <v>175.72</v>
       </c>
       <c r="E102" t="n">
-        <v>1.13</v>
+        <v>10.73</v>
       </c>
       <c r="F102" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G102" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="H102" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="I102" t="n">
         <v>0.47</v>
       </c>
-      <c r="G102" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="H102" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="I102" t="n">
-        <v>1.89</v>
-      </c>
       <c r="J102" t="n">
-        <v>5.93</v>
+        <v>-0.45</v>
       </c>
       <c r="K102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L102" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="103">
@@ -4395,37 +4377,37 @@
         <v>37</v>
       </c>
       <c r="B103" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C103" t="n">
-        <v>196.97</v>
+        <v>187.78</v>
       </c>
       <c r="D103" t="n">
-        <v>883.59</v>
+        <v>158.5</v>
       </c>
       <c r="E103" t="n">
-        <v>7.31</v>
+        <v>23.09</v>
       </c>
       <c r="F103" t="n">
-        <v>0.27</v>
+        <v>0.02</v>
       </c>
       <c r="G103" t="n">
-        <v>-0.42</v>
+        <v>-0.4</v>
       </c>
       <c r="H103" t="n">
-        <v>-0.81</v>
+        <v>-0.26</v>
       </c>
       <c r="I103" t="n">
-        <v>0.08</v>
+        <v>-0.27</v>
       </c>
       <c r="J103" t="n">
-        <v>-1.14</v>
+        <v>-0.93</v>
       </c>
       <c r="K103" t="n">
         <v>0</v>
       </c>
       <c r="L103" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="104">
@@ -4433,37 +4415,37 @@
         <v>38</v>
       </c>
       <c r="B104" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C104" t="n">
-        <v>1.45</v>
+        <v>184.96</v>
       </c>
       <c r="D104" t="n">
-        <v>0.09</v>
+        <v>115.51</v>
       </c>
       <c r="E104" t="n">
-        <v>0.92</v>
+        <v>21.38</v>
       </c>
       <c r="F104" t="n">
-        <v>0.68</v>
+        <v>0.15</v>
       </c>
       <c r="G104" t="n">
-        <v>2.04</v>
+        <v>-0.41</v>
       </c>
       <c r="H104" t="n">
-        <v>2.03</v>
+        <v>-0.38</v>
       </c>
       <c r="I104" t="n">
-        <v>1.54</v>
+        <v>-0.58</v>
       </c>
       <c r="J104" t="n">
-        <v>5.62</v>
+        <v>-1.37</v>
       </c>
       <c r="K104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L104" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="105">
@@ -4471,37 +4453,37 @@
         <v>38</v>
       </c>
       <c r="B105" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C105" t="n">
-        <v>194.03</v>
+        <v>185.78</v>
       </c>
       <c r="D105" t="n">
-        <v>388.37</v>
+        <v>123.3</v>
       </c>
       <c r="E105" t="n">
-        <v>10.08</v>
+        <v>14.66</v>
       </c>
       <c r="F105" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="G105" t="n">
-        <v>-0.41</v>
+        <v>-0.42</v>
       </c>
       <c r="H105" t="n">
-        <v>-0.59</v>
+        <v>-0.54</v>
       </c>
       <c r="I105" t="n">
-        <v>0.08</v>
+        <v>0.13</v>
       </c>
       <c r="J105" t="n">
-        <v>-0.92</v>
+        <v>-0.83</v>
       </c>
       <c r="K105" t="n">
         <v>0</v>
       </c>
       <c r="L105" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="106">
@@ -4509,37 +4491,37 @@
         <v>38</v>
       </c>
       <c r="B106" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C106" t="n">
-        <v>193.46</v>
+        <v>3.37</v>
       </c>
       <c r="D106" t="n">
-        <v>354.51</v>
+        <v>0.18</v>
       </c>
       <c r="E106" t="n">
-        <v>8.62</v>
+        <v>2.75</v>
       </c>
       <c r="F106" t="n">
-        <v>0.56</v>
+        <v>0.13</v>
       </c>
       <c r="G106" t="n">
-        <v>-0.41</v>
+        <v>2.04</v>
       </c>
       <c r="H106" t="n">
-        <v>-0.36</v>
+        <v>2.02</v>
       </c>
       <c r="I106" t="n">
-        <v>0.31</v>
+        <v>1.41</v>
       </c>
       <c r="J106" t="n">
-        <v>-0.46</v>
+        <v>5.47</v>
       </c>
       <c r="K106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L106" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="107">
@@ -4547,37 +4529,37 @@
         <v>38</v>
       </c>
       <c r="B107" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C107" t="n">
-        <v>193.41</v>
+        <v>184.57</v>
       </c>
       <c r="D107" t="n">
-        <v>345.97</v>
+        <v>112.26</v>
       </c>
       <c r="E107" t="n">
-        <v>20.22</v>
+        <v>30.54</v>
       </c>
       <c r="F107" t="n">
-        <v>0.81</v>
+        <v>0.01</v>
       </c>
       <c r="G107" t="n">
-        <v>-0.41</v>
+        <v>-0.4</v>
       </c>
       <c r="H107" t="n">
-        <v>-0.3</v>
+        <v>-0.31</v>
       </c>
       <c r="I107" t="n">
-        <v>-1.55</v>
+        <v>-1.56</v>
       </c>
       <c r="J107" t="n">
-        <v>-2.25</v>
+        <v>-2.28</v>
       </c>
       <c r="K107" t="n">
         <v>0</v>
       </c>
       <c r="L107" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="108">
@@ -4585,37 +4567,37 @@
         <v>38</v>
       </c>
       <c r="B108" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C108" t="n">
-        <v>193.61</v>
+        <v>183.67</v>
       </c>
       <c r="D108" t="n">
-        <v>360.05</v>
+        <v>105.66</v>
       </c>
       <c r="E108" t="n">
-        <v>12.8</v>
+        <v>14.35</v>
       </c>
       <c r="F108" t="n">
-        <v>0.7</v>
+        <v>0.12</v>
       </c>
       <c r="G108" t="n">
-        <v>-0.41</v>
+        <v>-0.39</v>
       </c>
       <c r="H108" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="I108" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="J108" t="n">
         <v>-0.4</v>
       </c>
-      <c r="I108" t="n">
-        <v>-0.36</v>
-      </c>
-      <c r="J108" t="n">
-        <v>-1.16</v>
-      </c>
       <c r="K108" t="n">
         <v>0</v>
       </c>
       <c r="L108" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="109">
@@ -4623,37 +4605,37 @@
         <v>38</v>
       </c>
       <c r="B109" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C109" t="n">
-        <v>193.5</v>
+        <v>186.12</v>
       </c>
       <c r="D109" t="n">
-        <v>357.88</v>
+        <v>126.53</v>
       </c>
       <c r="E109" t="n">
-        <v>10.74</v>
+        <v>11.85</v>
       </c>
       <c r="F109" t="n">
-        <v>0.7</v>
+        <v>0.19</v>
       </c>
       <c r="G109" t="n">
-        <v>-0.41</v>
+        <v>-0.42</v>
       </c>
       <c r="H109" t="n">
-        <v>-0.38</v>
+        <v>-0.61</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.03</v>
+        <v>0.44</v>
       </c>
       <c r="J109" t="n">
-        <v>-0.82</v>
+        <v>-0.6</v>
       </c>
       <c r="K109" t="n">
         <v>0</v>
       </c>
       <c r="L109" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="110">
@@ -4661,37 +4643,37 @@
         <v>39</v>
       </c>
       <c r="B110" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C110" t="n">
-        <v>188.08</v>
+        <v>160.61</v>
       </c>
       <c r="D110" t="n">
-        <v>162.09</v>
+        <v>30.56</v>
       </c>
       <c r="E110" t="n">
-        <v>49.18</v>
+        <v>6.69</v>
       </c>
       <c r="F110" t="n">
-        <v>0.04</v>
+        <v>0.61</v>
       </c>
       <c r="G110" t="n">
-        <v>-0.4</v>
+        <v>-0.51</v>
       </c>
       <c r="H110" t="n">
-        <v>-0.31</v>
+        <v>-0.68</v>
       </c>
       <c r="I110" t="n">
-        <v>-1.84</v>
+        <v>-0.85</v>
       </c>
       <c r="J110" t="n">
-        <v>-2.55</v>
+        <v>-2.04</v>
       </c>
       <c r="K110" t="n">
         <v>0</v>
       </c>
       <c r="L110" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="111">
@@ -4699,37 +4681,37 @@
         <v>39</v>
       </c>
       <c r="B111" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C111" t="n">
-        <v>188.5</v>
+        <v>129.11</v>
       </c>
       <c r="D111" t="n">
-        <v>169.25</v>
+        <v>14.41</v>
       </c>
       <c r="E111" t="n">
-        <v>16.56</v>
+        <v>3.33</v>
       </c>
       <c r="F111" t="n">
-        <v>0.03</v>
+        <v>0.12</v>
       </c>
       <c r="G111" t="n">
-        <v>-0.41</v>
+        <v>0</v>
       </c>
       <c r="H111" t="n">
-        <v>-0.41</v>
+        <v>0.62</v>
       </c>
       <c r="I111" t="n">
-        <v>0.12</v>
+        <v>0.95</v>
       </c>
       <c r="J111" t="n">
-        <v>-0.7</v>
+        <v>1.58</v>
       </c>
       <c r="K111" t="n">
         <v>0</v>
       </c>
       <c r="L111" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="112">
@@ -4737,37 +4719,37 @@
         <v>39</v>
       </c>
       <c r="B112" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C112" t="n">
-        <v>2.77</v>
+        <v>163.25</v>
       </c>
       <c r="D112" t="n">
-        <v>0.15</v>
+        <v>32.17</v>
       </c>
       <c r="E112" t="n">
-        <v>1.6</v>
+        <v>5.99</v>
       </c>
       <c r="F112" t="n">
-        <v>0.04</v>
+        <v>0.57</v>
       </c>
       <c r="G112" t="n">
-        <v>2.04</v>
+        <v>-0.56</v>
       </c>
       <c r="H112" t="n">
-        <v>2.03</v>
+        <v>-0.81</v>
       </c>
       <c r="I112" t="n">
-        <v>1.02</v>
+        <v>-0.47</v>
       </c>
       <c r="J112" t="n">
-        <v>5.09</v>
+        <v>-1.84</v>
       </c>
       <c r="K112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L112" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="113">
@@ -4778,34 +4760,34 @@
         <v>19</v>
       </c>
       <c r="C113" t="n">
-        <v>189.02</v>
+        <v>159.46</v>
       </c>
       <c r="D113" t="n">
-        <v>179.08</v>
+        <v>29.08</v>
       </c>
       <c r="E113" t="n">
-        <v>10.05</v>
+        <v>6.01</v>
       </c>
       <c r="F113" t="n">
-        <v>0.05</v>
+        <v>0.55</v>
       </c>
       <c r="G113" t="n">
-        <v>-0.42</v>
+        <v>-0.49</v>
       </c>
       <c r="H113" t="n">
-        <v>-0.55</v>
+        <v>-0.56</v>
       </c>
       <c r="I113" t="n">
-        <v>0.51</v>
+        <v>-0.48</v>
       </c>
       <c r="J113" t="n">
-        <v>-0.46</v>
+        <v>-1.54</v>
       </c>
       <c r="K113" t="n">
         <v>0</v>
       </c>
       <c r="L113" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="114">
@@ -4813,37 +4795,37 @@
         <v>39</v>
       </c>
       <c r="B114" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C114" t="n">
-        <v>188.83</v>
+        <v>155.98</v>
       </c>
       <c r="D114" t="n">
-        <v>175.72</v>
+        <v>26.23</v>
       </c>
       <c r="E114" t="n">
-        <v>10.73</v>
+        <v>6.41</v>
       </c>
       <c r="F114" t="n">
-        <v>0.02</v>
+        <v>0.44</v>
       </c>
       <c r="G114" t="n">
-        <v>-0.41</v>
+        <v>-0.44</v>
       </c>
       <c r="H114" t="n">
-        <v>-0.5</v>
+        <v>-0.33</v>
       </c>
       <c r="I114" t="n">
-        <v>0.47</v>
+        <v>-0.7</v>
       </c>
       <c r="J114" t="n">
-        <v>-0.45</v>
+        <v>-1.47</v>
       </c>
       <c r="K114" t="n">
         <v>0</v>
       </c>
       <c r="L114" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="115">
@@ -4851,37 +4833,37 @@
         <v>39</v>
       </c>
       <c r="B115" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C115" t="n">
-        <v>187.78</v>
+        <v>8.03</v>
       </c>
       <c r="D115" t="n">
-        <v>158.5</v>
+        <v>0.34</v>
       </c>
       <c r="E115" t="n">
-        <v>23.09</v>
+        <v>2.21</v>
       </c>
       <c r="F115" t="n">
-        <v>0.02</v>
+        <v>0.6</v>
       </c>
       <c r="G115" t="n">
-        <v>-0.4</v>
+        <v>2</v>
       </c>
       <c r="H115" t="n">
-        <v>-0.26</v>
+        <v>1.75</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.27</v>
+        <v>1.55</v>
       </c>
       <c r="J115" t="n">
-        <v>-0.93</v>
+        <v>5.31</v>
       </c>
       <c r="K115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L115" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="116">
@@ -4889,37 +4871,37 @@
         <v>40</v>
       </c>
       <c r="B116" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C116" t="n">
-        <v>184.96</v>
+        <v>111.86</v>
       </c>
       <c r="D116" t="n">
-        <v>115.51</v>
+        <v>1.88</v>
       </c>
       <c r="E116" t="n">
-        <v>21.38</v>
+        <v>0.99</v>
       </c>
       <c r="F116" t="n">
-        <v>0.15</v>
+        <v>0.01</v>
       </c>
       <c r="G116" t="n">
-        <v>-0.41</v>
+        <v>-1.64</v>
       </c>
       <c r="H116" t="n">
-        <v>-0.38</v>
+        <v>0.99</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.58</v>
+        <v>0.49</v>
       </c>
       <c r="J116" t="n">
-        <v>-1.37</v>
+        <v>-0.16</v>
       </c>
       <c r="K116" t="n">
         <v>0</v>
       </c>
       <c r="L116" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="117">
@@ -4927,37 +4909,37 @@
         <v>40</v>
       </c>
       <c r="B117" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C117" t="n">
-        <v>185.78</v>
+        <v>78.57</v>
       </c>
       <c r="D117" t="n">
-        <v>123.3</v>
+        <v>2.18</v>
       </c>
       <c r="E117" t="n">
-        <v>14.66</v>
+        <v>3.02</v>
       </c>
       <c r="F117" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="G117" t="n">
-        <v>-0.42</v>
+        <v>0.72</v>
       </c>
       <c r="H117" t="n">
-        <v>-0.54</v>
+        <v>0.38</v>
       </c>
       <c r="I117" t="n">
-        <v>0.13</v>
+        <v>0.39</v>
       </c>
       <c r="J117" t="n">
-        <v>-0.83</v>
+        <v>1.49</v>
       </c>
       <c r="K117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L117" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="118">
@@ -4968,34 +4950,34 @@
         <v>16</v>
       </c>
       <c r="C118" t="n">
-        <v>3.37</v>
+        <v>81.52</v>
       </c>
       <c r="D118" t="n">
-        <v>0.18</v>
+        <v>2.23</v>
       </c>
       <c r="E118" t="n">
-        <v>2.75</v>
+        <v>1.74</v>
       </c>
       <c r="F118" t="n">
-        <v>0.13</v>
+        <v>0.03</v>
       </c>
       <c r="G118" t="n">
-        <v>2.04</v>
+        <v>0.51</v>
       </c>
       <c r="H118" t="n">
-        <v>2.02</v>
+        <v>0.26</v>
       </c>
       <c r="I118" t="n">
-        <v>1.41</v>
+        <v>0.45</v>
       </c>
       <c r="J118" t="n">
-        <v>5.47</v>
+        <v>1.22</v>
       </c>
       <c r="K118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L118" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="119">
@@ -5003,37 +4985,37 @@
         <v>40</v>
       </c>
       <c r="B119" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C119" t="n">
-        <v>184.57</v>
+        <v>100.59</v>
       </c>
       <c r="D119" t="n">
-        <v>112.26</v>
+        <v>3.31</v>
       </c>
       <c r="E119" t="n">
-        <v>30.54</v>
+        <v>1.58</v>
       </c>
       <c r="F119" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="G119" t="n">
-        <v>-0.4</v>
+        <v>-0.84</v>
       </c>
       <c r="H119" t="n">
-        <v>-0.31</v>
+        <v>-1.93</v>
       </c>
       <c r="I119" t="n">
-        <v>-1.56</v>
+        <v>0.46</v>
       </c>
       <c r="J119" t="n">
-        <v>-2.28</v>
+        <v>-2.31</v>
       </c>
       <c r="K119" t="n">
         <v>0</v>
       </c>
       <c r="L119" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="120">
@@ -5041,37 +5023,31 @@
         <v>40</v>
       </c>
       <c r="B120" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C120" t="n">
-        <v>183.67</v>
+        <v>77.34</v>
       </c>
       <c r="D120" t="n">
-        <v>105.66</v>
-      </c>
-      <c r="E120" t="n">
-        <v>14.35</v>
-      </c>
-      <c r="F120" t="n">
-        <v>0.12</v>
-      </c>
+        <v>2.21</v>
+      </c>
+      <c r="E120"/>
+      <c r="F120"/>
       <c r="G120" t="n">
-        <v>-0.39</v>
+        <v>0.81</v>
       </c>
       <c r="H120" t="n">
-        <v>-0.18</v>
-      </c>
-      <c r="I120" t="n">
-        <v>0.17</v>
-      </c>
+        <v>0.31</v>
+      </c>
+      <c r="I120"/>
       <c r="J120" t="n">
-        <v>-0.4</v>
+        <v>1.11</v>
       </c>
       <c r="K120" t="n">
         <v>0</v>
       </c>
       <c r="L120" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="121">
@@ -5079,37 +5055,37 @@
         <v>40</v>
       </c>
       <c r="B121" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C121" t="n">
-        <v>186.12</v>
+        <v>82.59</v>
       </c>
       <c r="D121" t="n">
-        <v>126.53</v>
+        <v>2.37</v>
       </c>
       <c r="E121" t="n">
-        <v>11.85</v>
+        <v>50.11</v>
       </c>
       <c r="F121" t="n">
-        <v>0.19</v>
+        <v>0</v>
       </c>
       <c r="G121" t="n">
-        <v>-0.42</v>
+        <v>0.44</v>
       </c>
       <c r="H121" t="n">
-        <v>-0.61</v>
+        <v>-0.01</v>
       </c>
       <c r="I121" t="n">
-        <v>0.44</v>
+        <v>-1.79</v>
       </c>
       <c r="J121" t="n">
-        <v>-0.6</v>
+        <v>-1.36</v>
       </c>
       <c r="K121" t="n">
         <v>0</v>
       </c>
       <c r="L121" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="122">
@@ -5117,37 +5093,37 @@
         <v>41</v>
       </c>
       <c r="B122" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C122" t="n">
-        <v>160.61</v>
+        <v>199.21</v>
       </c>
       <c r="D122" t="n">
-        <v>30.56</v>
+        <v>6709.39</v>
       </c>
       <c r="E122" t="n">
-        <v>6.69</v>
+        <v>3.66</v>
       </c>
       <c r="F122" t="n">
-        <v>0.61</v>
+        <v>0.94</v>
       </c>
       <c r="G122" t="n">
-        <v>-0.51</v>
+        <v>-0.41</v>
       </c>
       <c r="H122" t="n">
-        <v>-0.68</v>
+        <v>-0.47</v>
       </c>
       <c r="I122" t="n">
-        <v>-0.85</v>
+        <v>-0.07</v>
       </c>
       <c r="J122" t="n">
-        <v>-2.04</v>
+        <v>-0.94</v>
       </c>
       <c r="K122" t="n">
         <v>0</v>
       </c>
       <c r="L122" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
     </row>
     <row r="123">
@@ -5155,37 +5131,37 @@
         <v>41</v>
       </c>
       <c r="B123" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C123" t="n">
-        <v>129.11</v>
+        <v>199.27</v>
       </c>
       <c r="D123" t="n">
-        <v>14.41</v>
+        <v>6870.42</v>
       </c>
       <c r="E123" t="n">
-        <v>3.33</v>
+        <v>4.02</v>
       </c>
       <c r="F123" t="n">
-        <v>0.12</v>
+        <v>0.95</v>
       </c>
       <c r="G123" t="n">
-        <v>0</v>
+        <v>-0.41</v>
       </c>
       <c r="H123" t="n">
-        <v>0.62</v>
+        <v>-0.53</v>
       </c>
       <c r="I123" t="n">
-        <v>0.95</v>
+        <v>-0.49</v>
       </c>
       <c r="J123" t="n">
-        <v>1.58</v>
+        <v>-1.43</v>
       </c>
       <c r="K123" t="n">
         <v>0</v>
       </c>
       <c r="L123" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
     </row>
     <row r="124">
@@ -5196,34 +5172,34 @@
         <v>17</v>
       </c>
       <c r="C124" t="n">
-        <v>163.25</v>
+        <v>199.21</v>
       </c>
       <c r="D124" t="n">
-        <v>32.17</v>
+        <v>6047.4</v>
       </c>
       <c r="E124" t="n">
-        <v>5.99</v>
+        <v>4.21</v>
       </c>
       <c r="F124" t="n">
-        <v>0.57</v>
+        <v>0.95</v>
       </c>
       <c r="G124" t="n">
-        <v>-0.56</v>
+        <v>-0.41</v>
       </c>
       <c r="H124" t="n">
-        <v>-0.81</v>
+        <v>-0.22</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.47</v>
+        <v>-0.71</v>
       </c>
       <c r="J124" t="n">
-        <v>-1.84</v>
+        <v>-1.34</v>
       </c>
       <c r="K124" t="n">
         <v>0</v>
       </c>
       <c r="L124" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
     </row>
     <row r="125">
@@ -5231,37 +5207,37 @@
         <v>41</v>
       </c>
       <c r="B125" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C125" t="n">
-        <v>159.46</v>
+        <v>4.29</v>
       </c>
       <c r="D125" t="n">
-        <v>29.08</v>
+        <v>0.42</v>
       </c>
       <c r="E125" t="n">
-        <v>6.01</v>
+        <v>1.87</v>
       </c>
       <c r="F125" t="n">
-        <v>0.55</v>
+        <v>0.95</v>
       </c>
       <c r="G125" t="n">
-        <v>-0.49</v>
+        <v>2.04</v>
       </c>
       <c r="H125" t="n">
-        <v>-0.56</v>
+        <v>2.03</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.48</v>
+        <v>1.99</v>
       </c>
       <c r="J125" t="n">
-        <v>-1.54</v>
+        <v>6.06</v>
       </c>
       <c r="K125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L125" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
     </row>
     <row r="126">
@@ -5272,34 +5248,34 @@
         <v>18</v>
       </c>
       <c r="C126" t="n">
-        <v>155.98</v>
+        <v>199.24</v>
       </c>
       <c r="D126" t="n">
-        <v>26.23</v>
+        <v>6469.43</v>
       </c>
       <c r="E126" t="n">
-        <v>6.41</v>
+        <v>4.03</v>
       </c>
       <c r="F126" t="n">
-        <v>0.44</v>
+        <v>0.94</v>
       </c>
       <c r="G126" t="n">
-        <v>-0.44</v>
+        <v>-0.41</v>
       </c>
       <c r="H126" t="n">
-        <v>-0.33</v>
+        <v>-0.38</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.7</v>
+        <v>-0.5</v>
       </c>
       <c r="J126" t="n">
-        <v>-1.47</v>
+        <v>-1.28</v>
       </c>
       <c r="K126" t="n">
         <v>0</v>
       </c>
       <c r="L126" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
     </row>
     <row r="127">
@@ -5307,487 +5283,487 @@
         <v>41</v>
       </c>
       <c r="B127" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C127" t="n">
-        <v>8.03</v>
+        <v>199.25</v>
       </c>
       <c r="D127" t="n">
-        <v>0.34</v>
+        <v>6639.28</v>
       </c>
       <c r="E127" t="n">
-        <v>2.21</v>
+        <v>3.79</v>
       </c>
       <c r="F127" t="n">
-        <v>0.6</v>
+        <v>0.91</v>
       </c>
       <c r="G127" t="n">
-        <v>2</v>
+        <v>-0.41</v>
       </c>
       <c r="H127" t="n">
-        <v>1.75</v>
+        <v>-0.44</v>
       </c>
       <c r="I127" t="n">
-        <v>1.55</v>
+        <v>-0.22</v>
       </c>
       <c r="J127" t="n">
-        <v>5.31</v>
+        <v>-1.07</v>
       </c>
       <c r="K127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L127" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s">
+        <v>43</v>
+      </c>
+      <c r="B128" t="s">
+        <v>13</v>
+      </c>
+      <c r="C128" t="n">
+        <v>187.78</v>
+      </c>
+      <c r="D128" t="n">
+        <v>167.02</v>
+      </c>
+      <c r="E128" t="n">
+        <v>11.37</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="G128" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="H128" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="J128" t="n">
+        <v>-0.88</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0</v>
+      </c>
+      <c r="L128" t="s">
         <v>42</v>
-      </c>
-      <c r="B128" t="s">
-        <v>15</v>
-      </c>
-      <c r="C128" t="n">
-        <v>111.86</v>
-      </c>
-      <c r="D128" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="E128" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="F128" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G128" t="n">
-        <v>-1.64</v>
-      </c>
-      <c r="H128" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="I128" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="J128" t="n">
-        <v>-0.16</v>
-      </c>
-      <c r="K128" t="n">
-        <v>0</v>
-      </c>
-      <c r="L128" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s">
+        <v>43</v>
+      </c>
+      <c r="B129" t="s">
+        <v>15</v>
+      </c>
+      <c r="C129" t="n">
+        <v>186.85</v>
+      </c>
+      <c r="D129" t="n">
+        <v>152.09</v>
+      </c>
+      <c r="E129" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G129" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="H129" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="I129" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="J129" t="n">
+        <v>-2.44</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0</v>
+      </c>
+      <c r="L129" t="s">
         <v>42</v>
-      </c>
-      <c r="B129" t="s">
-        <v>18</v>
-      </c>
-      <c r="C129" t="n">
-        <v>78.57</v>
-      </c>
-      <c r="D129" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="E129" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="F129" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="G129" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="H129" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="I129" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="J129" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="K129" t="n">
-        <v>1</v>
-      </c>
-      <c r="L129" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
+        <v>43</v>
+      </c>
+      <c r="B130" t="s">
+        <v>19</v>
+      </c>
+      <c r="C130" t="n">
+        <v>186.89</v>
+      </c>
+      <c r="D130" t="n">
+        <v>156.31</v>
+      </c>
+      <c r="E130" t="n">
+        <v>11.81</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="G130" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="H130" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="J130" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0</v>
+      </c>
+      <c r="L130" t="s">
         <v>42</v>
-      </c>
-      <c r="B130" t="s">
-        <v>16</v>
-      </c>
-      <c r="C130" t="n">
-        <v>81.52</v>
-      </c>
-      <c r="D130" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="E130" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="F130" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="G130" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="H130" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="I130" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="J130" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="K130" t="n">
-        <v>0</v>
-      </c>
-      <c r="L130" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s">
+        <v>43</v>
+      </c>
+      <c r="B131" t="s">
+        <v>17</v>
+      </c>
+      <c r="C131" t="n">
+        <v>186.75</v>
+      </c>
+      <c r="D131" t="n">
+        <v>155.88</v>
+      </c>
+      <c r="E131" t="n">
+        <v>7.88</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="G131" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="H131" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="J131" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0</v>
+      </c>
+      <c r="L131" t="s">
         <v>42</v>
-      </c>
-      <c r="B131" t="s">
-        <v>19</v>
-      </c>
-      <c r="C131" t="n">
-        <v>100.59</v>
-      </c>
-      <c r="D131" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="E131" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="F131" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="G131" t="n">
-        <v>-0.84</v>
-      </c>
-      <c r="H131" t="n">
-        <v>-1.93</v>
-      </c>
-      <c r="I131" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="J131" t="n">
-        <v>-2.31</v>
-      </c>
-      <c r="K131" t="n">
-        <v>0</v>
-      </c>
-      <c r="L131" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s">
+        <v>43</v>
+      </c>
+      <c r="B132" t="s">
+        <v>16</v>
+      </c>
+      <c r="C132" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="E132" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="G132" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="H132" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="I132" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J132" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="K132" t="n">
+        <v>1</v>
+      </c>
+      <c r="L132" t="s">
         <v>42</v>
-      </c>
-      <c r="B132" t="s">
-        <v>13</v>
-      </c>
-      <c r="C132" t="n">
-        <v>77.34</v>
-      </c>
-      <c r="D132" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="E132"/>
-      <c r="F132"/>
-      <c r="G132" t="n">
-        <v>0.81</v>
-      </c>
-      <c r="H132" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="I132"/>
-      <c r="J132" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="K132" t="n">
-        <v>0</v>
-      </c>
-      <c r="L132" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s">
+        <v>43</v>
+      </c>
+      <c r="B133" t="s">
+        <v>18</v>
+      </c>
+      <c r="C133" t="n">
+        <v>187.15</v>
+      </c>
+      <c r="D133" t="n">
+        <v>158.2</v>
+      </c>
+      <c r="E133" t="n">
+        <v>13.65</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="G133" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="H133" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="I133" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="J133" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0</v>
+      </c>
+      <c r="L133" t="s">
         <v>42</v>
-      </c>
-      <c r="B133" t="s">
-        <v>17</v>
-      </c>
-      <c r="C133" t="n">
-        <v>82.59</v>
-      </c>
-      <c r="D133" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="E133" t="n">
-        <v>50.11</v>
-      </c>
-      <c r="F133" t="n">
-        <v>0</v>
-      </c>
-      <c r="G133" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="H133" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="I133" t="n">
-        <v>-1.79</v>
-      </c>
-      <c r="J133" t="n">
-        <v>-1.36</v>
-      </c>
-      <c r="K133" t="n">
-        <v>0</v>
-      </c>
-      <c r="L133" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B134" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C134" t="n">
-        <v>199.21</v>
+        <v>196.97</v>
       </c>
       <c r="D134" t="n">
-        <v>6709.39</v>
-      </c>
-      <c r="E134" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="F134" t="n">
-        <v>0.94</v>
-      </c>
+        <v>799.85</v>
+      </c>
+      <c r="E134"/>
+      <c r="F134"/>
       <c r="G134" t="n">
         <v>-0.41</v>
       </c>
       <c r="H134" t="n">
-        <v>-0.47</v>
-      </c>
-      <c r="I134" t="n">
-        <v>-0.07</v>
-      </c>
+        <v>-0.27</v>
+      </c>
+      <c r="I134"/>
       <c r="J134" t="n">
-        <v>-0.94</v>
+        <v>-0.68</v>
       </c>
       <c r="K134" t="n">
         <v>0</v>
       </c>
       <c r="L134" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B135" t="s">
         <v>13</v>
       </c>
       <c r="C135" t="n">
-        <v>199.27</v>
+        <v>197.64</v>
       </c>
       <c r="D135" t="n">
-        <v>6870.42</v>
+        <v>1052.06</v>
       </c>
       <c r="E135" t="n">
-        <v>4.02</v>
+        <v>12.78</v>
       </c>
       <c r="F135" t="n">
-        <v>0.95</v>
+        <v>0.33</v>
       </c>
       <c r="G135" t="n">
-        <v>-0.41</v>
+        <v>-0.42</v>
       </c>
       <c r="H135" t="n">
-        <v>-0.53</v>
+        <v>-0.91</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.49</v>
+        <v>0.36</v>
       </c>
       <c r="J135" t="n">
-        <v>-1.43</v>
+        <v>-0.97</v>
       </c>
       <c r="K135" t="n">
         <v>0</v>
       </c>
       <c r="L135" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B136" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C136" t="n">
-        <v>199.21</v>
+        <v>194.99</v>
       </c>
       <c r="D136" t="n">
-        <v>6047.4</v>
+        <v>483.69</v>
       </c>
       <c r="E136" t="n">
-        <v>4.21</v>
+        <v>14.44</v>
       </c>
       <c r="F136" t="n">
-        <v>0.95</v>
+        <v>0.03</v>
       </c>
       <c r="G136" t="n">
-        <v>-0.41</v>
+        <v>-0.38</v>
       </c>
       <c r="H136" t="n">
-        <v>-0.22</v>
+        <v>0.54</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.71</v>
+        <v>0.07</v>
       </c>
       <c r="J136" t="n">
-        <v>-1.34</v>
+        <v>0.22</v>
       </c>
       <c r="K136" t="n">
         <v>0</v>
       </c>
       <c r="L136" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B137" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C137" t="n">
-        <v>4.29</v>
+        <v>197.1</v>
       </c>
       <c r="D137" t="n">
-        <v>0.42</v>
+        <v>840.55</v>
       </c>
       <c r="E137" t="n">
-        <v>1.87</v>
+        <v>24.49</v>
       </c>
       <c r="F137" t="n">
-        <v>0.95</v>
+        <v>0.11</v>
       </c>
       <c r="G137" t="n">
-        <v>2.04</v>
+        <v>-0.41</v>
       </c>
       <c r="H137" t="n">
-        <v>2.03</v>
+        <v>-0.37</v>
       </c>
       <c r="I137" t="n">
-        <v>1.99</v>
+        <v>-1.71</v>
       </c>
       <c r="J137" t="n">
-        <v>6.06</v>
+        <v>-2.5</v>
       </c>
       <c r="K137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L137" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B138" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C138" t="n">
-        <v>199.24</v>
+        <v>23.47</v>
       </c>
       <c r="D138" t="n">
-        <v>6469.43</v>
+        <v>1.73</v>
       </c>
       <c r="E138" t="n">
-        <v>4.03</v>
+        <v>12.48</v>
       </c>
       <c r="F138" t="n">
-        <v>0.94</v>
+        <v>0.5</v>
       </c>
       <c r="G138" t="n">
-        <v>-0.41</v>
+        <v>2.04</v>
       </c>
       <c r="H138" t="n">
-        <v>-0.38</v>
+        <v>1.77</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.5</v>
+        <v>0.41</v>
       </c>
       <c r="J138" t="n">
-        <v>-1.28</v>
+        <v>4.22</v>
       </c>
       <c r="K138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L138" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B139" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C139" t="n">
-        <v>199.25</v>
+        <v>197.48</v>
       </c>
       <c r="D139" t="n">
-        <v>6639.28</v>
+        <v>983.57</v>
       </c>
       <c r="E139" t="n">
-        <v>3.79</v>
+        <v>9.87</v>
       </c>
       <c r="F139" t="n">
-        <v>0.91</v>
+        <v>0.15</v>
       </c>
       <c r="G139" t="n">
-        <v>-0.41</v>
+        <v>-0.42</v>
       </c>
       <c r="H139" t="n">
-        <v>-0.44</v>
+        <v>-0.74</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.22</v>
+        <v>0.87</v>
       </c>
       <c r="J139" t="n">
-        <v>-1.07</v>
+        <v>-0.28</v>
       </c>
       <c r="K139" t="n">
         <v>0</v>
       </c>
       <c r="L139" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="140">
@@ -5795,37 +5771,37 @@
         <v>45</v>
       </c>
       <c r="B140" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C140" t="n">
-        <v>187.78</v>
+        <v>165.96</v>
       </c>
       <c r="D140" t="n">
-        <v>167.02</v>
+        <v>34.85</v>
       </c>
       <c r="E140" t="n">
-        <v>11.37</v>
+        <v>18.17</v>
       </c>
       <c r="F140" t="n">
-        <v>0.44</v>
+        <v>0.02</v>
       </c>
       <c r="G140" t="n">
-        <v>-0.42</v>
+        <v>-0.44</v>
       </c>
       <c r="H140" t="n">
-        <v>-0.55</v>
+        <v>-0.59</v>
       </c>
       <c r="I140" t="n">
-        <v>0.08</v>
+        <v>-0.69</v>
       </c>
       <c r="J140" t="n">
-        <v>-0.88</v>
+        <v>-1.72</v>
       </c>
       <c r="K140" t="n">
         <v>0</v>
       </c>
       <c r="L140" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="141">
@@ -5833,37 +5809,37 @@
         <v>45</v>
       </c>
       <c r="B141" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C141" t="n">
-        <v>186.85</v>
+        <v>164.7</v>
       </c>
       <c r="D141" t="n">
-        <v>152.09</v>
+        <v>32.55</v>
       </c>
       <c r="E141" t="n">
-        <v>22.7</v>
+        <v>22.76</v>
       </c>
       <c r="F141" t="n">
-        <v>0.5</v>
+        <v>0.18</v>
       </c>
       <c r="G141" t="n">
-        <v>-0.41</v>
+        <v>-0.42</v>
       </c>
       <c r="H141" t="n">
-        <v>-0.32</v>
+        <v>-0.42</v>
       </c>
       <c r="I141" t="n">
-        <v>-1.71</v>
+        <v>-1.25</v>
       </c>
       <c r="J141" t="n">
-        <v>-2.44</v>
+        <v>-2.08</v>
       </c>
       <c r="K141" t="n">
         <v>0</v>
       </c>
       <c r="L141" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="142">
@@ -5871,37 +5847,37 @@
         <v>45</v>
       </c>
       <c r="B142" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C142" t="n">
-        <v>186.89</v>
+        <v>10.65</v>
       </c>
       <c r="D142" t="n">
-        <v>156.31</v>
+        <v>0.44</v>
       </c>
       <c r="E142" t="n">
-        <v>11.81</v>
+        <v>1.77</v>
       </c>
       <c r="F142" t="n">
-        <v>0.23</v>
+        <v>0.36</v>
       </c>
       <c r="G142" t="n">
-        <v>-0.41</v>
+        <v>2.04</v>
       </c>
       <c r="H142" t="n">
-        <v>-0.38</v>
+        <v>2.02</v>
       </c>
       <c r="I142" t="n">
-        <v>0.02</v>
+        <v>1.29</v>
       </c>
       <c r="J142" t="n">
-        <v>-0.77</v>
+        <v>5.35</v>
       </c>
       <c r="K142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L142" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="143">
@@ -5909,37 +5885,37 @@
         <v>45</v>
       </c>
       <c r="B143" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C143" t="n">
-        <v>186.75</v>
+        <v>164.94</v>
       </c>
       <c r="D143" t="n">
-        <v>155.88</v>
+        <v>33.33</v>
       </c>
       <c r="E143" t="n">
-        <v>7.88</v>
+        <v>8.1</v>
       </c>
       <c r="F143" t="n">
-        <v>0.55</v>
+        <v>0.17</v>
       </c>
       <c r="G143" t="n">
-        <v>-0.4</v>
+        <v>-0.42</v>
       </c>
       <c r="H143" t="n">
-        <v>-0.38</v>
+        <v>-0.48</v>
       </c>
       <c r="I143" t="n">
-        <v>0.64</v>
+        <v>0.52</v>
       </c>
       <c r="J143" t="n">
-        <v>-0.14</v>
+        <v>-0.37</v>
       </c>
       <c r="K143" t="n">
         <v>0</v>
       </c>
       <c r="L143" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="144">
@@ -5947,37 +5923,31 @@
         <v>45</v>
       </c>
       <c r="B144" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C144" t="n">
-        <v>6.7</v>
+        <v>161.33</v>
       </c>
       <c r="D144" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="E144" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="F144" t="n">
-        <v>0.36</v>
-      </c>
+        <v>29.02</v>
+      </c>
+      <c r="E144"/>
+      <c r="F144"/>
       <c r="G144" t="n">
-        <v>2.04</v>
+        <v>-0.36</v>
       </c>
       <c r="H144" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="I144" t="n">
-        <v>1.25</v>
-      </c>
+        <v>-0.15</v>
+      </c>
+      <c r="I144"/>
       <c r="J144" t="n">
-        <v>5.33</v>
+        <v>-0.51</v>
       </c>
       <c r="K144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L144" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="145">
@@ -5985,37 +5955,37 @@
         <v>45</v>
       </c>
       <c r="B145" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C145" t="n">
-        <v>187.15</v>
+        <v>164.27</v>
       </c>
       <c r="D145" t="n">
-        <v>158.2</v>
+        <v>32.16</v>
       </c>
       <c r="E145" t="n">
-        <v>13.65</v>
+        <v>11.34</v>
       </c>
       <c r="F145" t="n">
-        <v>0.47</v>
+        <v>0.19</v>
       </c>
       <c r="G145" t="n">
         <v>-0.41</v>
       </c>
       <c r="H145" t="n">
-        <v>-0.41</v>
+        <v>-0.39</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.28</v>
+        <v>0.13</v>
       </c>
       <c r="J145" t="n">
-        <v>-1.1</v>
+        <v>-0.66</v>
       </c>
       <c r="K145" t="n">
         <v>0</v>
       </c>
       <c r="L145" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="146">
@@ -6023,31 +5993,37 @@
         <v>46</v>
       </c>
       <c r="B146" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C146" t="n">
-        <v>196.97</v>
+        <v>199.23</v>
       </c>
       <c r="D146" t="n">
-        <v>799.85</v>
-      </c>
-      <c r="E146"/>
-      <c r="F146"/>
+        <v>6085.52</v>
+      </c>
+      <c r="E146" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="F146" t="n">
+        <v>0.79</v>
+      </c>
       <c r="G146" t="n">
         <v>-0.41</v>
       </c>
       <c r="H146" t="n">
-        <v>-0.27</v>
-      </c>
-      <c r="I146"/>
+        <v>-0.1</v>
+      </c>
+      <c r="I146" t="n">
+        <v>0.02</v>
+      </c>
       <c r="J146" t="n">
-        <v>-0.68</v>
+        <v>-0.48</v>
       </c>
       <c r="K146" t="n">
         <v>0</v>
       </c>
       <c r="L146" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="147">
@@ -6055,37 +6031,37 @@
         <v>46</v>
       </c>
       <c r="B147" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C147" t="n">
-        <v>197.64</v>
+        <v>6.91</v>
       </c>
       <c r="D147" t="n">
-        <v>1052.06</v>
+        <v>0.71</v>
       </c>
       <c r="E147" t="n">
-        <v>12.78</v>
+        <v>1.5</v>
       </c>
       <c r="F147" t="n">
-        <v>0.33</v>
+        <v>0.54</v>
       </c>
       <c r="G147" t="n">
-        <v>-0.42</v>
+        <v>2.04</v>
       </c>
       <c r="H147" t="n">
-        <v>-0.91</v>
+        <v>1.64</v>
       </c>
       <c r="I147" t="n">
-        <v>0.36</v>
+        <v>1.41</v>
       </c>
       <c r="J147" t="n">
-        <v>-0.97</v>
+        <v>5.09</v>
       </c>
       <c r="K147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L147" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="148">
@@ -6093,37 +6069,37 @@
         <v>46</v>
       </c>
       <c r="B148" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C148" t="n">
-        <v>194.99</v>
+        <v>199.49</v>
       </c>
       <c r="D148" t="n">
-        <v>483.69</v>
+        <v>11011.09</v>
       </c>
       <c r="E148" t="n">
-        <v>14.44</v>
+        <v>2.44</v>
       </c>
       <c r="F148" t="n">
-        <v>0.03</v>
+        <v>0.82</v>
       </c>
       <c r="G148" t="n">
-        <v>-0.38</v>
+        <v>-0.41</v>
       </c>
       <c r="H148" t="n">
-        <v>0.54</v>
+        <v>-1.5</v>
       </c>
       <c r="I148" t="n">
-        <v>0.07</v>
+        <v>0.51</v>
       </c>
       <c r="J148" t="n">
-        <v>0.22</v>
+        <v>-1.4</v>
       </c>
       <c r="K148" t="n">
         <v>0</v>
       </c>
       <c r="L148" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="149">
@@ -6134,34 +6110,34 @@
         <v>18</v>
       </c>
       <c r="C149" t="n">
-        <v>197.1</v>
+        <v>199.3</v>
       </c>
       <c r="D149" t="n">
-        <v>840.55</v>
+        <v>6457.06</v>
       </c>
       <c r="E149" t="n">
-        <v>24.49</v>
+        <v>3.16</v>
       </c>
       <c r="F149" t="n">
-        <v>0.11</v>
+        <v>0.9</v>
       </c>
       <c r="G149" t="n">
         <v>-0.41</v>
       </c>
       <c r="H149" t="n">
-        <v>-0.37</v>
+        <v>-0.2</v>
       </c>
       <c r="I149" t="n">
-        <v>-1.71</v>
+        <v>-0.17</v>
       </c>
       <c r="J149" t="n">
-        <v>-2.5</v>
+        <v>-0.78</v>
       </c>
       <c r="K149" t="n">
         <v>0</v>
       </c>
       <c r="L149" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="150">
@@ -6169,37 +6145,37 @@
         <v>46</v>
       </c>
       <c r="B150" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C150" t="n">
-        <v>23.47</v>
+        <v>199.15</v>
       </c>
       <c r="D150" t="n">
-        <v>1.73</v>
+        <v>5270.76</v>
       </c>
       <c r="E150" t="n">
-        <v>12.48</v>
+        <v>3.12</v>
       </c>
       <c r="F150" t="n">
-        <v>0.5</v>
+        <v>0.83</v>
       </c>
       <c r="G150" t="n">
-        <v>2.04</v>
+        <v>-0.41</v>
       </c>
       <c r="H150" t="n">
-        <v>1.77</v>
+        <v>0.14</v>
       </c>
       <c r="I150" t="n">
-        <v>0.41</v>
+        <v>-0.14</v>
       </c>
       <c r="J150" t="n">
-        <v>4.22</v>
+        <v>-0.4</v>
       </c>
       <c r="K150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L150" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="151">
@@ -6207,241 +6183,247 @@
         <v>46</v>
       </c>
       <c r="B151" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C151" t="n">
-        <v>197.48</v>
+        <v>199.3</v>
       </c>
       <c r="D151" t="n">
-        <v>983.57</v>
+        <v>5680.61</v>
       </c>
       <c r="E151" t="n">
-        <v>9.87</v>
+        <v>4.7</v>
       </c>
       <c r="F151" t="n">
-        <v>0.15</v>
+        <v>0.83</v>
       </c>
       <c r="G151" t="n">
-        <v>-0.42</v>
+        <v>-0.41</v>
       </c>
       <c r="H151" t="n">
-        <v>-0.74</v>
+        <v>0.02</v>
       </c>
       <c r="I151" t="n">
-        <v>0.87</v>
+        <v>-1.64</v>
       </c>
       <c r="J151" t="n">
-        <v>-0.28</v>
+        <v>-2.03</v>
       </c>
       <c r="K151" t="n">
         <v>0</v>
       </c>
       <c r="L151" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="s">
+        <v>48</v>
+      </c>
+      <c r="B152" t="s">
+        <v>17</v>
+      </c>
+      <c r="C152" t="n">
+        <v>188.34</v>
+      </c>
+      <c r="D152" t="n">
+        <v>188.45</v>
+      </c>
+      <c r="E152" t="n">
+        <v>5.69</v>
+      </c>
+      <c r="F152" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="G152" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="H152" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="I152" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J152" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="K152" t="n">
+        <v>0</v>
+      </c>
+      <c r="L152" t="s">
         <v>47</v>
-      </c>
-      <c r="B152" t="s">
-        <v>15</v>
-      </c>
-      <c r="C152" t="n">
-        <v>165.96</v>
-      </c>
-      <c r="D152" t="n">
-        <v>34.85</v>
-      </c>
-      <c r="E152" t="n">
-        <v>18.17</v>
-      </c>
-      <c r="F152" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="G152" t="n">
-        <v>-0.44</v>
-      </c>
-      <c r="H152" t="n">
-        <v>-0.59</v>
-      </c>
-      <c r="I152" t="n">
-        <v>-0.69</v>
-      </c>
-      <c r="J152" t="n">
-        <v>-1.72</v>
-      </c>
-      <c r="K152" t="n">
-        <v>0</v>
-      </c>
-      <c r="L152" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="s">
+        <v>48</v>
+      </c>
+      <c r="B153" t="s">
+        <v>15</v>
+      </c>
+      <c r="C153" t="n">
+        <v>190.62</v>
+      </c>
+      <c r="D153" t="n">
+        <v>222.75</v>
+      </c>
+      <c r="E153" t="n">
+        <v>18.63</v>
+      </c>
+      <c r="F153" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G153" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="H153" t="n">
+        <v>-0.69</v>
+      </c>
+      <c r="I153" t="n">
+        <v>-1.92</v>
+      </c>
+      <c r="J153" t="n">
+        <v>-3.03</v>
+      </c>
+      <c r="K153" t="n">
+        <v>0</v>
+      </c>
+      <c r="L153" t="s">
         <v>47</v>
-      </c>
-      <c r="B153" t="s">
-        <v>18</v>
-      </c>
-      <c r="C153" t="n">
-        <v>164.7</v>
-      </c>
-      <c r="D153" t="n">
-        <v>32.55</v>
-      </c>
-      <c r="E153" t="n">
-        <v>22.76</v>
-      </c>
-      <c r="F153" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="G153" t="n">
-        <v>-0.42</v>
-      </c>
-      <c r="H153" t="n">
-        <v>-0.42</v>
-      </c>
-      <c r="I153" t="n">
-        <v>-1.25</v>
-      </c>
-      <c r="J153" t="n">
-        <v>-2.08</v>
-      </c>
-      <c r="K153" t="n">
-        <v>0</v>
-      </c>
-      <c r="L153" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="s">
+        <v>48</v>
+      </c>
+      <c r="B154" t="s">
+        <v>13</v>
+      </c>
+      <c r="C154" t="n">
+        <v>188.79</v>
+      </c>
+      <c r="D154" t="n">
+        <v>192.87</v>
+      </c>
+      <c r="E154" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="F154" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="G154" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="H154" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="I154" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="J154" t="n">
+        <v>-0.59</v>
+      </c>
+      <c r="K154" t="n">
+        <v>0</v>
+      </c>
+      <c r="L154" t="s">
         <v>47</v>
-      </c>
-      <c r="B154" t="s">
-        <v>16</v>
-      </c>
-      <c r="C154" t="n">
-        <v>10.65</v>
-      </c>
-      <c r="D154" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="E154" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="F154" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="G154" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="H154" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="I154" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="J154" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="K154" t="n">
-        <v>1</v>
-      </c>
-      <c r="L154" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="s">
+        <v>48</v>
+      </c>
+      <c r="B155" t="s">
+        <v>16</v>
+      </c>
+      <c r="C155" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="D155" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="E155" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="F155" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="G155" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="H155" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="I155" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="J155" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="K155" t="n">
+        <v>1</v>
+      </c>
+      <c r="L155" t="s">
         <v>47</v>
-      </c>
-      <c r="B155" t="s">
-        <v>19</v>
-      </c>
-      <c r="C155" t="n">
-        <v>164.94</v>
-      </c>
-      <c r="D155" t="n">
-        <v>33.33</v>
-      </c>
-      <c r="E155" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="F155" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="G155" t="n">
-        <v>-0.42</v>
-      </c>
-      <c r="H155" t="n">
-        <v>-0.48</v>
-      </c>
-      <c r="I155" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="J155" t="n">
-        <v>-0.37</v>
-      </c>
-      <c r="K155" t="n">
-        <v>0</v>
-      </c>
-      <c r="L155" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s">
+        <v>48</v>
+      </c>
+      <c r="B156" t="s">
+        <v>19</v>
+      </c>
+      <c r="C156" t="n">
+        <v>188.85</v>
+      </c>
+      <c r="D156" t="n">
+        <v>194.41</v>
+      </c>
+      <c r="E156" t="n">
+        <v>6.28</v>
+      </c>
+      <c r="F156" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G156" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="H156" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="I156" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="J156" t="n">
+        <v>-0.46</v>
+      </c>
+      <c r="K156" t="n">
+        <v>0</v>
+      </c>
+      <c r="L156" t="s">
         <v>47</v>
-      </c>
-      <c r="B156" t="s">
-        <v>13</v>
-      </c>
-      <c r="C156" t="n">
-        <v>161.33</v>
-      </c>
-      <c r="D156" t="n">
-        <v>29.02</v>
-      </c>
-      <c r="E156"/>
-      <c r="F156"/>
-      <c r="G156" t="n">
-        <v>-0.36</v>
-      </c>
-      <c r="H156" t="n">
-        <v>-0.15</v>
-      </c>
-      <c r="I156"/>
-      <c r="J156" t="n">
-        <v>-0.51</v>
-      </c>
-      <c r="K156" t="n">
-        <v>0</v>
-      </c>
-      <c r="L156" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B157" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C157" t="n">
-        <v>164.27</v>
+        <v>189.17</v>
       </c>
       <c r="D157" t="n">
-        <v>32.16</v>
+        <v>197.76</v>
       </c>
       <c r="E157" t="n">
-        <v>11.34</v>
+        <v>7.56</v>
       </c>
       <c r="F157" t="n">
-        <v>0.19</v>
+        <v>0.85</v>
       </c>
       <c r="G157" t="n">
         <v>-0.41</v>
@@ -6450,676 +6432,700 @@
         <v>-0.39</v>
       </c>
       <c r="I157" t="n">
-        <v>0.13</v>
+        <v>0.06</v>
       </c>
       <c r="J157" t="n">
-        <v>-0.66</v>
+        <v>-0.73</v>
       </c>
       <c r="K157" t="n">
         <v>0</v>
       </c>
       <c r="L157" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B158" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C158" t="n">
-        <v>93.39</v>
+        <v>189.74</v>
       </c>
       <c r="D158" t="n">
-        <v>2.39</v>
+        <v>190.16</v>
       </c>
       <c r="E158" t="n">
-        <v>5.23</v>
+        <v>11.31</v>
       </c>
       <c r="F158" t="n">
-        <v>0</v>
+        <v>0.82</v>
       </c>
       <c r="G158" t="n">
-        <v>0.47</v>
+        <v>-0.41</v>
       </c>
       <c r="H158" t="n">
-        <v>-0.67</v>
+        <v>-0.53</v>
       </c>
       <c r="I158" t="n">
-        <v>0.51</v>
+        <v>0.39</v>
       </c>
       <c r="J158" t="n">
-        <v>0.3</v>
+        <v>-0.55</v>
       </c>
       <c r="K158" t="n">
         <v>0</v>
       </c>
       <c r="L158" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B159" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C159" t="n">
-        <v>95.56</v>
+        <v>188.36</v>
       </c>
       <c r="D159" t="n">
-        <v>2.09</v>
+        <v>165.61</v>
       </c>
       <c r="E159" t="n">
-        <v>15.34</v>
+        <v>13.27</v>
       </c>
       <c r="F159" t="n">
-        <v>0.02</v>
+        <v>0.45</v>
       </c>
       <c r="G159" t="n">
-        <v>0.37</v>
+        <v>-0.4</v>
       </c>
       <c r="H159" t="n">
-        <v>-0.11</v>
+        <v>-0.2</v>
       </c>
       <c r="I159" t="n">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="J159" t="n">
-        <v>0.43</v>
+        <v>-0.36</v>
       </c>
       <c r="K159" t="n">
         <v>0</v>
       </c>
       <c r="L159" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B160" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C160" t="n">
-        <v>106.17</v>
+        <v>189.39</v>
       </c>
       <c r="D160" t="n">
-        <v>2.73</v>
+        <v>181.67</v>
       </c>
       <c r="E160" t="n">
-        <v>4.05</v>
+        <v>15.92</v>
       </c>
       <c r="F160" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="G160" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="H160" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="I160" t="n">
         <v>0.02</v>
       </c>
-      <c r="G160" t="n">
-        <v>-0.15</v>
-      </c>
-      <c r="H160" t="n">
-        <v>-1.31</v>
-      </c>
-      <c r="I160" t="n">
-        <v>0.55</v>
-      </c>
       <c r="J160" t="n">
-        <v>-0.91</v>
+        <v>-0.8</v>
       </c>
       <c r="K160" t="n">
         <v>0</v>
       </c>
       <c r="L160" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B161" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C161" t="n">
-        <v>95.92</v>
+        <v>189.89</v>
       </c>
       <c r="D161" t="n">
-        <v>2.1</v>
+        <v>192.99</v>
       </c>
       <c r="E161" t="n">
-        <v>74.43</v>
+        <v>13.76</v>
       </c>
       <c r="F161" t="n">
-        <v>0</v>
+        <v>0.81</v>
       </c>
       <c r="G161" t="n">
-        <v>0.35</v>
+        <v>-0.42</v>
       </c>
       <c r="H161" t="n">
-        <v>-0.13</v>
+        <v>-0.56</v>
       </c>
       <c r="I161" t="n">
-        <v>-1.77</v>
+        <v>0.19</v>
       </c>
       <c r="J161" t="n">
-        <v>-1.55</v>
+        <v>-0.79</v>
       </c>
       <c r="K161" t="n">
         <v>0</v>
       </c>
       <c r="L161" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B162" t="s">
         <v>16</v>
       </c>
       <c r="C162" t="n">
-        <v>143.02</v>
+        <v>4.92</v>
       </c>
       <c r="D162" t="n">
-        <v>1.23</v>
+        <v>0.26</v>
       </c>
       <c r="E162" t="n">
-        <v>4.17</v>
+        <v>2.79</v>
       </c>
       <c r="F162" t="n">
-        <v>0.03</v>
+        <v>0.82</v>
       </c>
       <c r="G162" t="n">
-        <v>-1.93</v>
+        <v>2.04</v>
       </c>
       <c r="H162" t="n">
-        <v>1.52</v>
+        <v>2.02</v>
       </c>
       <c r="I162" t="n">
-        <v>0.54</v>
+        <v>1.07</v>
       </c>
       <c r="J162" t="n">
-        <v>0.13</v>
+        <v>5.13</v>
       </c>
       <c r="K162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L162" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B163" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C163" t="n">
-        <v>84.69</v>
+        <v>189.15</v>
       </c>
       <c r="D163" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="E163"/>
-      <c r="F163"/>
+        <v>175.31</v>
+      </c>
+      <c r="E163" t="n">
+        <v>39.94</v>
+      </c>
+      <c r="F163" t="n">
+        <v>0.33</v>
+      </c>
       <c r="G163" t="n">
-        <v>0.89</v>
+        <v>-0.41</v>
       </c>
       <c r="H163" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="I163"/>
+        <v>-0.33</v>
+      </c>
+      <c r="I163" t="n">
+        <v>-1.9</v>
+      </c>
       <c r="J163" t="n">
-        <v>1.59</v>
+        <v>-2.63</v>
       </c>
       <c r="K163" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L163" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B164" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C164" t="n">
-        <v>78.91</v>
+        <v>4.32</v>
       </c>
       <c r="D164" t="n">
-        <v>1.77</v>
+        <v>0.23</v>
       </c>
       <c r="E164" t="n">
-        <v>2.72</v>
+        <v>1.72</v>
       </c>
       <c r="F164" t="n">
-        <v>0.01</v>
+        <v>0.61</v>
       </c>
       <c r="G164" t="n">
-        <v>0.87</v>
+        <v>2.04</v>
       </c>
       <c r="H164" t="n">
-        <v>1.14</v>
+        <v>2.03</v>
       </c>
       <c r="I164" t="n">
-        <v>0.81</v>
+        <v>1.89</v>
       </c>
       <c r="J164" t="n">
-        <v>2.82</v>
+        <v>5.96</v>
       </c>
       <c r="K164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L164" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B165" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C165" t="n">
-        <v>128.64</v>
+        <v>180.64</v>
       </c>
       <c r="D165" t="n">
-        <v>6.95</v>
+        <v>81.49</v>
       </c>
       <c r="E165" t="n">
-        <v>4.45</v>
+        <v>9.34</v>
       </c>
       <c r="F165" t="n">
-        <v>0</v>
+        <v>0.63</v>
       </c>
       <c r="G165" t="n">
-        <v>-0.19</v>
+        <v>-0.41</v>
       </c>
       <c r="H165" t="n">
-        <v>0.18</v>
+        <v>-0.38</v>
       </c>
       <c r="I165" t="n">
-        <v>-1.12</v>
+        <v>0.01</v>
       </c>
       <c r="J165" t="n">
-        <v>-1.12</v>
+        <v>-0.77</v>
       </c>
       <c r="K165" t="n">
         <v>0</v>
       </c>
       <c r="L165" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B166" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C166" t="n">
-        <v>45.85</v>
+        <v>181.83</v>
       </c>
       <c r="D166" t="n">
-        <v>1.3</v>
+        <v>86.02</v>
       </c>
       <c r="E166" t="n">
-        <v>3.16</v>
+        <v>9.48</v>
       </c>
       <c r="F166" t="n">
-        <v>0.21</v>
+        <v>0.74</v>
       </c>
       <c r="G166" t="n">
-        <v>1.58</v>
+        <v>-0.42</v>
       </c>
       <c r="H166" t="n">
-        <v>1.23</v>
+        <v>-0.51</v>
       </c>
       <c r="I166" t="n">
-        <v>0.31</v>
+        <v>-0.02</v>
       </c>
       <c r="J166" t="n">
-        <v>3.12</v>
+        <v>-0.95</v>
       </c>
       <c r="K166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L166" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B167" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C167" t="n">
-        <v>155.1</v>
+        <v>178.63</v>
       </c>
       <c r="D167" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E167"/>
-      <c r="F167"/>
+        <v>76.01</v>
+      </c>
+      <c r="E167" t="n">
+        <v>13.38</v>
+      </c>
+      <c r="F167" t="n">
+        <v>0.16</v>
+      </c>
       <c r="G167" t="n">
-        <v>-0.75</v>
+        <v>-0.38</v>
       </c>
       <c r="H167" t="n">
-        <v>-0.84</v>
-      </c>
-      <c r="I167"/>
+        <v>-0.21</v>
+      </c>
+      <c r="I167" t="n">
+        <v>-0.98</v>
+      </c>
       <c r="J167" t="n">
-        <v>-1.59</v>
+        <v>-1.57</v>
       </c>
       <c r="K167" t="n">
         <v>0</v>
       </c>
       <c r="L167" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B168" t="s">
         <v>13</v>
       </c>
       <c r="C168" t="n">
-        <v>155.16</v>
+        <v>181.99</v>
       </c>
       <c r="D168" t="n">
-        <v>12.52</v>
-      </c>
-      <c r="E168"/>
-      <c r="F168"/>
+        <v>86.72</v>
+      </c>
+      <c r="E168" t="n">
+        <v>10.46</v>
+      </c>
+      <c r="F168" t="n">
+        <v>0.68</v>
+      </c>
       <c r="G168" t="n">
-        <v>-0.75</v>
+        <v>-0.42</v>
       </c>
       <c r="H168" t="n">
-        <v>-0.84</v>
-      </c>
-      <c r="I168"/>
+        <v>-0.53</v>
+      </c>
+      <c r="I168" t="n">
+        <v>-0.26</v>
+      </c>
       <c r="J168" t="n">
-        <v>-1.59</v>
+        <v>-1.22</v>
       </c>
       <c r="K168" t="n">
         <v>0</v>
       </c>
       <c r="L168" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B169" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C169" t="n">
-        <v>155.59</v>
+        <v>180.92</v>
       </c>
       <c r="D169" t="n">
-        <v>12.68</v>
-      </c>
-      <c r="E169"/>
-      <c r="F169"/>
+        <v>82.08</v>
+      </c>
+      <c r="E169" t="n">
+        <v>12.01</v>
+      </c>
+      <c r="F169" t="n">
+        <v>0.54</v>
+      </c>
       <c r="G169" t="n">
-        <v>-0.76</v>
+        <v>-0.41</v>
       </c>
       <c r="H169" t="n">
-        <v>-0.87</v>
-      </c>
-      <c r="I169"/>
+        <v>-0.39</v>
+      </c>
+      <c r="I169" t="n">
+        <v>-0.64</v>
+      </c>
       <c r="J169" t="n">
-        <v>-1.63</v>
+        <v>-1.45</v>
       </c>
       <c r="K169" t="n">
         <v>0</v>
       </c>
       <c r="L169" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B170" t="s">
         <v>13</v>
       </c>
       <c r="C170" t="n">
-        <v>199.23</v>
+        <v>185.65</v>
       </c>
       <c r="D170" t="n">
-        <v>6085.52</v>
+        <v>119.85</v>
       </c>
       <c r="E170" t="n">
-        <v>2.96</v>
+        <v>7.82</v>
       </c>
       <c r="F170" t="n">
         <v>0.79</v>
       </c>
       <c r="G170" t="n">
-        <v>-0.41</v>
+        <v>-0.44</v>
       </c>
       <c r="H170" t="n">
-        <v>-0.1</v>
+        <v>-0.85</v>
       </c>
       <c r="I170" t="n">
-        <v>0.02</v>
+        <v>0.11</v>
       </c>
       <c r="J170" t="n">
-        <v>-0.48</v>
+        <v>-1.19</v>
       </c>
       <c r="K170" t="n">
         <v>0</v>
       </c>
       <c r="L170" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B171" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C171" t="n">
-        <v>6.91</v>
+        <v>182.72</v>
       </c>
       <c r="D171" t="n">
-        <v>0.71</v>
+        <v>96.64</v>
       </c>
       <c r="E171" t="n">
-        <v>1.5</v>
+        <v>9.04</v>
       </c>
       <c r="F171" t="n">
-        <v>0.54</v>
+        <v>0.21</v>
       </c>
       <c r="G171" t="n">
-        <v>2.04</v>
+        <v>-0.4</v>
       </c>
       <c r="H171" t="n">
-        <v>1.64</v>
+        <v>-0.31</v>
       </c>
       <c r="I171" t="n">
-        <v>1.41</v>
+        <v>-0.25</v>
       </c>
       <c r="J171" t="n">
-        <v>5.09</v>
+        <v>-0.96</v>
       </c>
       <c r="K171" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L171" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B172" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C172" t="n">
-        <v>199.49</v>
+        <v>183.26</v>
       </c>
       <c r="D172" t="n">
-        <v>11011.09</v>
+        <v>100.11</v>
       </c>
       <c r="E172" t="n">
-        <v>2.44</v>
+        <v>9.47</v>
       </c>
       <c r="F172" t="n">
-        <v>0.82</v>
+        <v>0.54</v>
       </c>
       <c r="G172" t="n">
         <v>-0.41</v>
       </c>
       <c r="H172" t="n">
-        <v>-1.5</v>
+        <v>-0.39</v>
       </c>
       <c r="I172" t="n">
-        <v>0.51</v>
+        <v>-0.38</v>
       </c>
       <c r="J172" t="n">
-        <v>-1.4</v>
+        <v>-1.18</v>
       </c>
       <c r="K172" t="n">
         <v>0</v>
       </c>
       <c r="L172" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B173" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C173" t="n">
-        <v>199.3</v>
+        <v>183.24</v>
       </c>
       <c r="D173" t="n">
-        <v>6457.06</v>
+        <v>102.26</v>
       </c>
       <c r="E173" t="n">
-        <v>3.16</v>
+        <v>7.49</v>
       </c>
       <c r="F173" t="n">
-        <v>0.9</v>
+        <v>0.59</v>
       </c>
       <c r="G173" t="n">
         <v>-0.41</v>
       </c>
       <c r="H173" t="n">
-        <v>-0.2</v>
+        <v>-0.44</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.17</v>
+        <v>0.2</v>
       </c>
       <c r="J173" t="n">
-        <v>-0.78</v>
+        <v>-0.65</v>
       </c>
       <c r="K173" t="n">
         <v>0</v>
       </c>
       <c r="L173" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B174" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C174" t="n">
-        <v>199.15</v>
+        <v>7.43</v>
       </c>
       <c r="D174" t="n">
-        <v>5270.76</v>
+        <v>0.37</v>
       </c>
       <c r="E174" t="n">
-        <v>3.12</v>
+        <v>2.45</v>
       </c>
       <c r="F174" t="n">
-        <v>0.83</v>
+        <v>0.74</v>
       </c>
       <c r="G174" t="n">
-        <v>-0.41</v>
+        <v>2.04</v>
       </c>
       <c r="H174" t="n">
-        <v>0.14</v>
+        <v>1.96</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.14</v>
+        <v>1.69</v>
       </c>
       <c r="J174" t="n">
-        <v>-0.4</v>
+        <v>5.69</v>
       </c>
       <c r="K174" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L174" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B175" t="s">
         <v>15</v>
       </c>
       <c r="C175" t="n">
-        <v>199.3</v>
+        <v>180.19</v>
       </c>
       <c r="D175" t="n">
-        <v>5680.61</v>
+        <v>82.19</v>
       </c>
       <c r="E175" t="n">
-        <v>4.7</v>
+        <v>12.85</v>
       </c>
       <c r="F175" t="n">
-        <v>0.83</v>
+        <v>0.16</v>
       </c>
       <c r="G175" t="n">
-        <v>-0.41</v>
+        <v>-0.37</v>
       </c>
       <c r="H175" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="I175" t="n">
-        <v>-1.64</v>
+        <v>-1.37</v>
       </c>
       <c r="J175" t="n">
-        <v>-2.03</v>
+        <v>-1.71</v>
       </c>
       <c r="K175" t="n">
         <v>0</v>
       </c>
       <c r="L175" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="176">
@@ -7127,37 +7133,37 @@
         <v>52</v>
       </c>
       <c r="B176" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C176" t="n">
-        <v>188.34</v>
+        <v>163.26</v>
       </c>
       <c r="D176" t="n">
-        <v>188.45</v>
+        <v>34.38</v>
       </c>
       <c r="E176" t="n">
-        <v>5.69</v>
+        <v>4.99</v>
       </c>
       <c r="F176" t="n">
-        <v>0.66</v>
+        <v>0.74</v>
       </c>
       <c r="G176" t="n">
-        <v>-0.4</v>
+        <v>-0.41</v>
       </c>
       <c r="H176" t="n">
-        <v>-0.27</v>
+        <v>-0.5</v>
       </c>
       <c r="I176" t="n">
         <v>0.4</v>
       </c>
       <c r="J176" t="n">
-        <v>-0.27</v>
+        <v>-0.51</v>
       </c>
       <c r="K176" t="n">
         <v>0</v>
       </c>
       <c r="L176" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="177">
@@ -7165,37 +7171,37 @@
         <v>52</v>
       </c>
       <c r="B177" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C177" t="n">
-        <v>190.62</v>
+        <v>3.24</v>
       </c>
       <c r="D177" t="n">
-        <v>222.75</v>
+        <v>0.14</v>
       </c>
       <c r="E177" t="n">
-        <v>18.63</v>
+        <v>0.6</v>
       </c>
       <c r="F177" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="G177" t="n">
-        <v>-0.43</v>
+        <v>2.04</v>
       </c>
       <c r="H177" t="n">
-        <v>-0.69</v>
+        <v>2.03</v>
       </c>
       <c r="I177" t="n">
-        <v>-1.92</v>
+        <v>1.38</v>
       </c>
       <c r="J177" t="n">
-        <v>-3.03</v>
+        <v>5.45</v>
       </c>
       <c r="K177" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L177" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="178">
@@ -7203,37 +7209,37 @@
         <v>52</v>
       </c>
       <c r="B178" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C178" t="n">
-        <v>188.79</v>
+        <v>161.8</v>
       </c>
       <c r="D178" t="n">
-        <v>192.87</v>
+        <v>32.35</v>
       </c>
       <c r="E178" t="n">
-        <v>7.15</v>
+        <v>5.71</v>
       </c>
       <c r="F178" t="n">
-        <v>0.87</v>
+        <v>0.54</v>
       </c>
       <c r="G178" t="n">
-        <v>-0.4</v>
+        <v>-0.39</v>
       </c>
       <c r="H178" t="n">
-        <v>-0.33</v>
+        <v>-0.35</v>
       </c>
       <c r="I178" t="n">
-        <v>0.14</v>
+        <v>0.24</v>
       </c>
       <c r="J178" t="n">
-        <v>-0.59</v>
+        <v>-0.5</v>
       </c>
       <c r="K178" t="n">
         <v>0</v>
       </c>
       <c r="L178" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="179">
@@ -7241,37 +7247,37 @@
         <v>52</v>
       </c>
       <c r="B179" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C179" t="n">
-        <v>6.08</v>
+        <v>164.92</v>
       </c>
       <c r="D179" t="n">
-        <v>0.33</v>
+        <v>34.49</v>
       </c>
       <c r="E179" t="n">
-        <v>2.15</v>
+        <v>7.31</v>
       </c>
       <c r="F179" t="n">
-        <v>0.79</v>
+        <v>0.26</v>
       </c>
       <c r="G179" t="n">
-        <v>2.04</v>
+        <v>-0.43</v>
       </c>
       <c r="H179" t="n">
-        <v>2.02</v>
+        <v>-0.51</v>
       </c>
       <c r="I179" t="n">
-        <v>1.03</v>
+        <v>-0.11</v>
       </c>
       <c r="J179" t="n">
-        <v>5.09</v>
+        <v>-1.06</v>
       </c>
       <c r="K179" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L179" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="180">
@@ -7279,37 +7285,37 @@
         <v>52</v>
       </c>
       <c r="B180" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C180" t="n">
-        <v>188.85</v>
+        <v>162.79</v>
       </c>
       <c r="D180" t="n">
-        <v>194.41</v>
+        <v>31.5</v>
       </c>
       <c r="E180" t="n">
-        <v>6.28</v>
+        <v>14.34</v>
       </c>
       <c r="F180" t="n">
-        <v>0.88</v>
+        <v>0.25</v>
       </c>
       <c r="G180" t="n">
         <v>-0.4</v>
       </c>
       <c r="H180" t="n">
-        <v>-0.34</v>
+        <v>-0.29</v>
       </c>
       <c r="I180" t="n">
-        <v>0.29</v>
+        <v>-1.68</v>
       </c>
       <c r="J180" t="n">
-        <v>-0.46</v>
+        <v>-2.37</v>
       </c>
       <c r="K180" t="n">
         <v>0</v>
       </c>
       <c r="L180" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="181">
@@ -7320,34 +7326,34 @@
         <v>18</v>
       </c>
       <c r="C181" t="n">
-        <v>189.17</v>
+        <v>163.13</v>
       </c>
       <c r="D181" t="n">
-        <v>197.76</v>
+        <v>32.71</v>
       </c>
       <c r="E181" t="n">
-        <v>7.56</v>
+        <v>7.86</v>
       </c>
       <c r="F181" t="n">
-        <v>0.85</v>
+        <v>0.65</v>
       </c>
       <c r="G181" t="n">
         <v>-0.41</v>
       </c>
       <c r="H181" t="n">
-        <v>-0.39</v>
+        <v>-0.38</v>
       </c>
       <c r="I181" t="n">
-        <v>0.06</v>
+        <v>-0.24</v>
       </c>
       <c r="J181" t="n">
-        <v>-0.73</v>
+        <v>-1.02</v>
       </c>
       <c r="K181" t="n">
         <v>0</v>
       </c>
       <c r="L181" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="182">
@@ -7358,34 +7364,28 @@
         <v>13</v>
       </c>
       <c r="C182" t="n">
-        <v>189.74</v>
+        <v>190.93</v>
       </c>
       <c r="D182" t="n">
-        <v>190.16</v>
-      </c>
-      <c r="E182" t="n">
-        <v>11.31</v>
-      </c>
-      <c r="F182" t="n">
-        <v>0.82</v>
-      </c>
+        <v>4.39</v>
+      </c>
+      <c r="E182"/>
+      <c r="F182"/>
       <c r="G182" t="n">
-        <v>-0.41</v>
+        <v>-0.47</v>
       </c>
       <c r="H182" t="n">
-        <v>-0.53</v>
-      </c>
-      <c r="I182" t="n">
-        <v>0.39</v>
-      </c>
+        <v>-0.44</v>
+      </c>
+      <c r="I182"/>
       <c r="J182" t="n">
-        <v>-0.55</v>
+        <v>-0.91</v>
       </c>
       <c r="K182" t="n">
         <v>0</v>
       </c>
       <c r="L182" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="183">
@@ -7396,34 +7396,28 @@
         <v>17</v>
       </c>
       <c r="C183" t="n">
-        <v>188.36</v>
+        <v>190.95</v>
       </c>
       <c r="D183" t="n">
-        <v>165.61</v>
-      </c>
-      <c r="E183" t="n">
-        <v>13.27</v>
-      </c>
-      <c r="F183" t="n">
-        <v>0.45</v>
-      </c>
+        <v>4.39</v>
+      </c>
+      <c r="E183"/>
+      <c r="F183"/>
       <c r="G183" t="n">
-        <v>-0.4</v>
+        <v>-0.47</v>
       </c>
       <c r="H183" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="I183" t="n">
-        <v>0.23</v>
-      </c>
+        <v>-0.44</v>
+      </c>
+      <c r="I183"/>
       <c r="J183" t="n">
-        <v>-0.36</v>
+        <v>-0.91</v>
       </c>
       <c r="K183" t="n">
         <v>0</v>
       </c>
       <c r="L183" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="184">
@@ -7434,34 +7428,34 @@
         <v>18</v>
       </c>
       <c r="C184" t="n">
-        <v>189.39</v>
+        <v>187.99</v>
       </c>
       <c r="D184" t="n">
-        <v>181.67</v>
+        <v>4.35</v>
       </c>
       <c r="E184" t="n">
-        <v>15.92</v>
+        <v>63.66</v>
       </c>
       <c r="F184" t="n">
-        <v>0.77</v>
+        <v>0.07</v>
       </c>
       <c r="G184" t="n">
-        <v>-0.41</v>
+        <v>-0.34</v>
       </c>
       <c r="H184" t="n">
-        <v>-0.41</v>
+        <v>-0.36</v>
       </c>
       <c r="I184" t="n">
-        <v>0.02</v>
+        <v>-1.14</v>
       </c>
       <c r="J184" t="n">
-        <v>-0.8</v>
+        <v>-1.84</v>
       </c>
       <c r="K184" t="n">
         <v>0</v>
       </c>
       <c r="L184" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="185">
@@ -7472,34 +7466,28 @@
         <v>19</v>
       </c>
       <c r="C185" t="n">
-        <v>189.89</v>
+        <v>190.92</v>
       </c>
       <c r="D185" t="n">
-        <v>192.99</v>
-      </c>
-      <c r="E185" t="n">
-        <v>13.76</v>
-      </c>
-      <c r="F185" t="n">
-        <v>0.81</v>
-      </c>
+        <v>4.39</v>
+      </c>
+      <c r="E185"/>
+      <c r="F185"/>
       <c r="G185" t="n">
-        <v>-0.42</v>
+        <v>-0.47</v>
       </c>
       <c r="H185" t="n">
-        <v>-0.56</v>
-      </c>
-      <c r="I185" t="n">
-        <v>0.19</v>
-      </c>
+        <v>-0.44</v>
+      </c>
+      <c r="I185"/>
       <c r="J185" t="n">
-        <v>-0.79</v>
+        <v>-0.91</v>
       </c>
       <c r="K185" t="n">
         <v>0</v>
       </c>
       <c r="L185" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="186">
@@ -7510,34 +7498,34 @@
         <v>16</v>
       </c>
       <c r="C186" t="n">
-        <v>4.92</v>
+        <v>134.83</v>
       </c>
       <c r="D186" t="n">
-        <v>0.26</v>
+        <v>3.31</v>
       </c>
       <c r="E186" t="n">
-        <v>2.79</v>
+        <v>4.51</v>
       </c>
       <c r="F186" t="n">
-        <v>0.82</v>
+        <v>0.06</v>
       </c>
       <c r="G186" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="H186" t="n">
         <v>2.04</v>
       </c>
-      <c r="H186" t="n">
-        <v>2.02</v>
-      </c>
       <c r="I186" t="n">
-        <v>1.07</v>
+        <v>0.73</v>
       </c>
       <c r="J186" t="n">
-        <v>5.13</v>
+        <v>4.8</v>
       </c>
       <c r="K186" t="n">
         <v>1</v>
       </c>
       <c r="L186" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="187">
@@ -7548,1378 +7536,34 @@
         <v>15</v>
       </c>
       <c r="C187" t="n">
-        <v>189.15</v>
+        <v>186.57</v>
       </c>
       <c r="D187" t="n">
-        <v>175.31</v>
+        <v>4.36</v>
       </c>
       <c r="E187" t="n">
-        <v>39.94</v>
+        <v>14.47</v>
       </c>
       <c r="F187" t="n">
-        <v>0.33</v>
+        <v>0.46</v>
       </c>
       <c r="G187" t="n">
-        <v>-0.41</v>
+        <v>-0.28</v>
       </c>
       <c r="H187" t="n">
-        <v>-0.33</v>
+        <v>-0.36</v>
       </c>
       <c r="I187" t="n">
-        <v>-1.9</v>
+        <v>0.41</v>
       </c>
       <c r="J187" t="n">
-        <v>-2.63</v>
+        <v>-0.22</v>
       </c>
       <c r="K187" t="n">
         <v>0</v>
       </c>
       <c r="L187" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="s">
-        <v>54</v>
-      </c>
-      <c r="B188" t="s">
-        <v>16</v>
-      </c>
-      <c r="C188" t="n">
-        <v>4.32</v>
-      </c>
-      <c r="D188" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="E188" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="F188" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="G188" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="H188" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="I188" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="J188" t="n">
-        <v>5.96</v>
-      </c>
-      <c r="K188" t="n">
-        <v>1</v>
-      </c>
-      <c r="L188" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="s">
-        <v>54</v>
-      </c>
-      <c r="B189" t="s">
-        <v>17</v>
-      </c>
-      <c r="C189" t="n">
-        <v>180.64</v>
-      </c>
-      <c r="D189" t="n">
-        <v>81.49</v>
-      </c>
-      <c r="E189" t="n">
-        <v>9.34</v>
-      </c>
-      <c r="F189" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="G189" t="n">
-        <v>-0.41</v>
-      </c>
-      <c r="H189" t="n">
-        <v>-0.38</v>
-      </c>
-      <c r="I189" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="J189" t="n">
-        <v>-0.77</v>
-      </c>
-      <c r="K189" t="n">
-        <v>0</v>
-      </c>
-      <c r="L189" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="s">
-        <v>54</v>
-      </c>
-      <c r="B190" t="s">
-        <v>19</v>
-      </c>
-      <c r="C190" t="n">
-        <v>181.83</v>
-      </c>
-      <c r="D190" t="n">
-        <v>86.02</v>
-      </c>
-      <c r="E190" t="n">
-        <v>9.48</v>
-      </c>
-      <c r="F190" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="G190" t="n">
-        <v>-0.42</v>
-      </c>
-      <c r="H190" t="n">
-        <v>-0.51</v>
-      </c>
-      <c r="I190" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="J190" t="n">
-        <v>-0.95</v>
-      </c>
-      <c r="K190" t="n">
-        <v>0</v>
-      </c>
-      <c r="L190" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="s">
-        <v>54</v>
-      </c>
-      <c r="B191" t="s">
-        <v>15</v>
-      </c>
-      <c r="C191" t="n">
-        <v>178.63</v>
-      </c>
-      <c r="D191" t="n">
-        <v>76.01</v>
-      </c>
-      <c r="E191" t="n">
-        <v>13.38</v>
-      </c>
-      <c r="F191" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="G191" t="n">
-        <v>-0.38</v>
-      </c>
-      <c r="H191" t="n">
-        <v>-0.21</v>
-      </c>
-      <c r="I191" t="n">
-        <v>-0.98</v>
-      </c>
-      <c r="J191" t="n">
-        <v>-1.57</v>
-      </c>
-      <c r="K191" t="n">
-        <v>0</v>
-      </c>
-      <c r="L191" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="s">
-        <v>54</v>
-      </c>
-      <c r="B192" t="s">
-        <v>13</v>
-      </c>
-      <c r="C192" t="n">
-        <v>181.99</v>
-      </c>
-      <c r="D192" t="n">
-        <v>86.72</v>
-      </c>
-      <c r="E192" t="n">
-        <v>10.46</v>
-      </c>
-      <c r="F192" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="G192" t="n">
-        <v>-0.42</v>
-      </c>
-      <c r="H192" t="n">
-        <v>-0.53</v>
-      </c>
-      <c r="I192" t="n">
-        <v>-0.26</v>
-      </c>
-      <c r="J192" t="n">
-        <v>-1.22</v>
-      </c>
-      <c r="K192" t="n">
-        <v>0</v>
-      </c>
-      <c r="L192" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="s">
-        <v>54</v>
-      </c>
-      <c r="B193" t="s">
-        <v>18</v>
-      </c>
-      <c r="C193" t="n">
-        <v>180.92</v>
-      </c>
-      <c r="D193" t="n">
-        <v>82.08</v>
-      </c>
-      <c r="E193" t="n">
-        <v>12.01</v>
-      </c>
-      <c r="F193" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="G193" t="n">
-        <v>-0.41</v>
-      </c>
-      <c r="H193" t="n">
-        <v>-0.39</v>
-      </c>
-      <c r="I193" t="n">
-        <v>-0.64</v>
-      </c>
-      <c r="J193" t="n">
-        <v>-1.45</v>
-      </c>
-      <c r="K193" t="n">
-        <v>0</v>
-      </c>
-      <c r="L193" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="s">
-        <v>55</v>
-      </c>
-      <c r="B194" t="s">
-        <v>13</v>
-      </c>
-      <c r="C194" t="n">
-        <v>185.65</v>
-      </c>
-      <c r="D194" t="n">
-        <v>119.85</v>
-      </c>
-      <c r="E194" t="n">
-        <v>7.82</v>
-      </c>
-      <c r="F194" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="G194" t="n">
-        <v>-0.44</v>
-      </c>
-      <c r="H194" t="n">
-        <v>-0.85</v>
-      </c>
-      <c r="I194" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="J194" t="n">
-        <v>-1.19</v>
-      </c>
-      <c r="K194" t="n">
-        <v>0</v>
-      </c>
-      <c r="L194" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="s">
-        <v>55</v>
-      </c>
-      <c r="B195" t="s">
-        <v>17</v>
-      </c>
-      <c r="C195" t="n">
-        <v>182.72</v>
-      </c>
-      <c r="D195" t="n">
-        <v>96.64</v>
-      </c>
-      <c r="E195" t="n">
-        <v>9.04</v>
-      </c>
-      <c r="F195" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="G195" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="H195" t="n">
-        <v>-0.31</v>
-      </c>
-      <c r="I195" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="J195" t="n">
-        <v>-0.96</v>
-      </c>
-      <c r="K195" t="n">
-        <v>0</v>
-      </c>
-      <c r="L195" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="s">
-        <v>55</v>
-      </c>
-      <c r="B196" t="s">
-        <v>18</v>
-      </c>
-      <c r="C196" t="n">
-        <v>183.26</v>
-      </c>
-      <c r="D196" t="n">
-        <v>100.11</v>
-      </c>
-      <c r="E196" t="n">
-        <v>9.47</v>
-      </c>
-      <c r="F196" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="G196" t="n">
-        <v>-0.41</v>
-      </c>
-      <c r="H196" t="n">
-        <v>-0.39</v>
-      </c>
-      <c r="I196" t="n">
-        <v>-0.38</v>
-      </c>
-      <c r="J196" t="n">
-        <v>-1.18</v>
-      </c>
-      <c r="K196" t="n">
-        <v>0</v>
-      </c>
-      <c r="L196" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="s">
-        <v>55</v>
-      </c>
-      <c r="B197" t="s">
-        <v>19</v>
-      </c>
-      <c r="C197" t="n">
-        <v>183.24</v>
-      </c>
-      <c r="D197" t="n">
-        <v>102.26</v>
-      </c>
-      <c r="E197" t="n">
-        <v>7.49</v>
-      </c>
-      <c r="F197" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="G197" t="n">
-        <v>-0.41</v>
-      </c>
-      <c r="H197" t="n">
-        <v>-0.44</v>
-      </c>
-      <c r="I197" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J197" t="n">
-        <v>-0.65</v>
-      </c>
-      <c r="K197" t="n">
-        <v>0</v>
-      </c>
-      <c r="L197" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="s">
-        <v>55</v>
-      </c>
-      <c r="B198" t="s">
-        <v>16</v>
-      </c>
-      <c r="C198" t="n">
-        <v>7.43</v>
-      </c>
-      <c r="D198" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="E198" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="F198" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="G198" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="H198" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="I198" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="J198" t="n">
-        <v>5.69</v>
-      </c>
-      <c r="K198" t="n">
-        <v>1</v>
-      </c>
-      <c r="L198" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="s">
-        <v>55</v>
-      </c>
-      <c r="B199" t="s">
-        <v>15</v>
-      </c>
-      <c r="C199" t="n">
-        <v>180.19</v>
-      </c>
-      <c r="D199" t="n">
-        <v>82.19</v>
-      </c>
-      <c r="E199" t="n">
-        <v>12.85</v>
-      </c>
-      <c r="F199" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="G199" t="n">
-        <v>-0.37</v>
-      </c>
-      <c r="H199" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="I199" t="n">
-        <v>-1.37</v>
-      </c>
-      <c r="J199" t="n">
-        <v>-1.71</v>
-      </c>
-      <c r="K199" t="n">
-        <v>0</v>
-      </c>
-      <c r="L199" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="s">
-        <v>56</v>
-      </c>
-      <c r="B200" t="s">
-        <v>13</v>
-      </c>
-      <c r="C200" t="n">
-        <v>163.26</v>
-      </c>
-      <c r="D200" t="n">
-        <v>34.38</v>
-      </c>
-      <c r="E200" t="n">
-        <v>4.99</v>
-      </c>
-      <c r="F200" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="G200" t="n">
-        <v>-0.41</v>
-      </c>
-      <c r="H200" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="I200" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J200" t="n">
-        <v>-0.51</v>
-      </c>
-      <c r="K200" t="n">
-        <v>0</v>
-      </c>
-      <c r="L200" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="s">
-        <v>56</v>
-      </c>
-      <c r="B201" t="s">
-        <v>16</v>
-      </c>
-      <c r="C201" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="D201" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="E201" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="F201" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="G201" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="H201" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="I201" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="J201" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="K201" t="n">
-        <v>1</v>
-      </c>
-      <c r="L201" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="s">
-        <v>56</v>
-      </c>
-      <c r="B202" t="s">
-        <v>19</v>
-      </c>
-      <c r="C202" t="n">
-        <v>161.8</v>
-      </c>
-      <c r="D202" t="n">
-        <v>32.35</v>
-      </c>
-      <c r="E202" t="n">
-        <v>5.71</v>
-      </c>
-      <c r="F202" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="G202" t="n">
-        <v>-0.39</v>
-      </c>
-      <c r="H202" t="n">
-        <v>-0.35</v>
-      </c>
-      <c r="I202" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="J202" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="K202" t="n">
-        <v>0</v>
-      </c>
-      <c r="L202" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="s">
-        <v>56</v>
-      </c>
-      <c r="B203" t="s">
-        <v>17</v>
-      </c>
-      <c r="C203" t="n">
-        <v>164.92</v>
-      </c>
-      <c r="D203" t="n">
-        <v>34.49</v>
-      </c>
-      <c r="E203" t="n">
-        <v>7.31</v>
-      </c>
-      <c r="F203" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="G203" t="n">
-        <v>-0.43</v>
-      </c>
-      <c r="H203" t="n">
-        <v>-0.51</v>
-      </c>
-      <c r="I203" t="n">
-        <v>-0.11</v>
-      </c>
-      <c r="J203" t="n">
-        <v>-1.06</v>
-      </c>
-      <c r="K203" t="n">
-        <v>0</v>
-      </c>
-      <c r="L203" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="s">
-        <v>56</v>
-      </c>
-      <c r="B204" t="s">
-        <v>15</v>
-      </c>
-      <c r="C204" t="n">
-        <v>162.79</v>
-      </c>
-      <c r="D204" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="E204" t="n">
-        <v>14.34</v>
-      </c>
-      <c r="F204" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="G204" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="H204" t="n">
-        <v>-0.29</v>
-      </c>
-      <c r="I204" t="n">
-        <v>-1.68</v>
-      </c>
-      <c r="J204" t="n">
-        <v>-2.37</v>
-      </c>
-      <c r="K204" t="n">
-        <v>0</v>
-      </c>
-      <c r="L204" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="s">
-        <v>56</v>
-      </c>
-      <c r="B205" t="s">
-        <v>18</v>
-      </c>
-      <c r="C205" t="n">
-        <v>163.13</v>
-      </c>
-      <c r="D205" t="n">
-        <v>32.71</v>
-      </c>
-      <c r="E205" t="n">
-        <v>7.86</v>
-      </c>
-      <c r="F205" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="G205" t="n">
-        <v>-0.41</v>
-      </c>
-      <c r="H205" t="n">
-        <v>-0.38</v>
-      </c>
-      <c r="I205" t="n">
-        <v>-0.24</v>
-      </c>
-      <c r="J205" t="n">
-        <v>-1.02</v>
-      </c>
-      <c r="K205" t="n">
-        <v>0</v>
-      </c>
-      <c r="L205" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="s">
-        <v>57</v>
-      </c>
-      <c r="B206" t="s">
-        <v>13</v>
-      </c>
-      <c r="C206" t="n">
-        <v>190.93</v>
-      </c>
-      <c r="D206" t="n">
-        <v>4.39</v>
-      </c>
-      <c r="E206"/>
-      <c r="F206"/>
-      <c r="G206" t="n">
-        <v>-0.47</v>
-      </c>
-      <c r="H206" t="n">
-        <v>-0.44</v>
-      </c>
-      <c r="I206"/>
-      <c r="J206" t="n">
-        <v>-0.91</v>
-      </c>
-      <c r="K206" t="n">
-        <v>0</v>
-      </c>
-      <c r="L206" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="s">
-        <v>57</v>
-      </c>
-      <c r="B207" t="s">
-        <v>17</v>
-      </c>
-      <c r="C207" t="n">
-        <v>190.95</v>
-      </c>
-      <c r="D207" t="n">
-        <v>4.39</v>
-      </c>
-      <c r="E207"/>
-      <c r="F207"/>
-      <c r="G207" t="n">
-        <v>-0.47</v>
-      </c>
-      <c r="H207" t="n">
-        <v>-0.44</v>
-      </c>
-      <c r="I207"/>
-      <c r="J207" t="n">
-        <v>-0.91</v>
-      </c>
-      <c r="K207" t="n">
-        <v>0</v>
-      </c>
-      <c r="L207" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="s">
-        <v>57</v>
-      </c>
-      <c r="B208" t="s">
-        <v>18</v>
-      </c>
-      <c r="C208" t="n">
-        <v>187.99</v>
-      </c>
-      <c r="D208" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="E208" t="n">
-        <v>63.66</v>
-      </c>
-      <c r="F208" t="n">
-        <v>0.07</v>
-      </c>
-      <c r="G208" t="n">
-        <v>-0.34</v>
-      </c>
-      <c r="H208" t="n">
-        <v>-0.36</v>
-      </c>
-      <c r="I208" t="n">
-        <v>-1.14</v>
-      </c>
-      <c r="J208" t="n">
-        <v>-1.84</v>
-      </c>
-      <c r="K208" t="n">
-        <v>0</v>
-      </c>
-      <c r="L208" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="s">
-        <v>57</v>
-      </c>
-      <c r="B209" t="s">
-        <v>19</v>
-      </c>
-      <c r="C209" t="n">
-        <v>190.92</v>
-      </c>
-      <c r="D209" t="n">
-        <v>4.39</v>
-      </c>
-      <c r="E209"/>
-      <c r="F209"/>
-      <c r="G209" t="n">
-        <v>-0.47</v>
-      </c>
-      <c r="H209" t="n">
-        <v>-0.44</v>
-      </c>
-      <c r="I209"/>
-      <c r="J209" t="n">
-        <v>-0.91</v>
-      </c>
-      <c r="K209" t="n">
-        <v>0</v>
-      </c>
-      <c r="L209" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="s">
-        <v>57</v>
-      </c>
-      <c r="B210" t="s">
-        <v>16</v>
-      </c>
-      <c r="C210" t="n">
-        <v>134.83</v>
-      </c>
-      <c r="D210" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="E210" t="n">
-        <v>4.51</v>
-      </c>
-      <c r="F210" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="G210" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="H210" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="I210" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="J210" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="K210" t="n">
-        <v>1</v>
-      </c>
-      <c r="L210" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="s">
-        <v>57</v>
-      </c>
-      <c r="B211" t="s">
-        <v>15</v>
-      </c>
-      <c r="C211" t="n">
-        <v>186.57</v>
-      </c>
-      <c r="D211" t="n">
-        <v>4.36</v>
-      </c>
-      <c r="E211" t="n">
-        <v>14.47</v>
-      </c>
-      <c r="F211" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="G211" t="n">
-        <v>-0.28</v>
-      </c>
-      <c r="H211" t="n">
-        <v>-0.36</v>
-      </c>
-      <c r="I211" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="J211" t="n">
-        <v>-0.22</v>
-      </c>
-      <c r="K211" t="n">
-        <v>0</v>
-      </c>
-      <c r="L211" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="s">
-        <v>58</v>
-      </c>
-      <c r="B212" t="s">
-        <v>18</v>
-      </c>
-      <c r="C212" t="n">
-        <v>154</v>
-      </c>
-      <c r="D212" t="n">
-        <v>21.31</v>
-      </c>
-      <c r="E212" t="n">
-        <v>7.47</v>
-      </c>
-      <c r="F212" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="G212" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="H212" t="n">
-        <v>-0.36</v>
-      </c>
-      <c r="I212" t="n">
-        <v>-0.93</v>
-      </c>
-      <c r="J212" t="n">
-        <v>-1.7</v>
-      </c>
-      <c r="K212" t="n">
-        <v>0</v>
-      </c>
-      <c r="L212" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="s">
-        <v>58</v>
-      </c>
-      <c r="B213" t="s">
-        <v>15</v>
-      </c>
-      <c r="C213" t="n">
-        <v>154.08</v>
-      </c>
-      <c r="D213" t="n">
-        <v>21.56</v>
-      </c>
-      <c r="E213" t="n">
-        <v>5.73</v>
-      </c>
-      <c r="F213" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="G213" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="H213" t="n">
-        <v>-0.39</v>
-      </c>
-      <c r="I213" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="J213" t="n">
-        <v>-0.75</v>
-      </c>
-      <c r="K213" t="n">
-        <v>0</v>
-      </c>
-      <c r="L213" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="s">
-        <v>58</v>
-      </c>
-      <c r="B214" t="s">
-        <v>17</v>
-      </c>
-      <c r="C214" t="n">
-        <v>155.78</v>
-      </c>
-      <c r="D214" t="n">
-        <v>22.85</v>
-      </c>
-      <c r="E214" t="n">
-        <v>5.74</v>
-      </c>
-      <c r="F214" t="n">
-        <v>0</v>
-      </c>
-      <c r="G214" t="n">
-        <v>-0.43</v>
-      </c>
-      <c r="H214" t="n">
-        <v>-0.54</v>
-      </c>
-      <c r="I214" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="J214" t="n">
-        <v>-0.93</v>
-      </c>
-      <c r="K214" t="n">
-        <v>0</v>
-      </c>
-      <c r="L214" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="s">
-        <v>58</v>
-      </c>
-      <c r="B215" t="s">
-        <v>13</v>
-      </c>
-      <c r="C215" t="n">
-        <v>154.09</v>
-      </c>
-      <c r="D215" t="n">
-        <v>21.57</v>
-      </c>
-      <c r="E215" t="n">
-        <v>6.97</v>
-      </c>
-      <c r="F215" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="G215" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="H215" t="n">
-        <v>-0.39</v>
-      </c>
-      <c r="I215" t="n">
-        <v>-0.65</v>
-      </c>
-      <c r="J215" t="n">
-        <v>-1.45</v>
-      </c>
-      <c r="K215" t="n">
-        <v>0</v>
-      </c>
-      <c r="L215" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="s">
-        <v>58</v>
-      </c>
-      <c r="B216" t="s">
-        <v>19</v>
-      </c>
-      <c r="C216" t="n">
-        <v>153.44</v>
-      </c>
-      <c r="D216" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="E216" t="n">
-        <v>6.52</v>
-      </c>
-      <c r="F216" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="G216" t="n">
-        <v>-0.39</v>
-      </c>
-      <c r="H216" t="n">
-        <v>-0.35</v>
-      </c>
-      <c r="I216" t="n">
-        <v>-0.39</v>
-      </c>
-      <c r="J216" t="n">
-        <v>-1.14</v>
-      </c>
-      <c r="K216" t="n">
-        <v>0</v>
-      </c>
-      <c r="L216" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="s">
-        <v>58</v>
-      </c>
-      <c r="B217" t="s">
-        <v>16</v>
-      </c>
-      <c r="C217" t="n">
-        <v>11.12</v>
-      </c>
-      <c r="D217" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="E217" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="F217" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="G217" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="H217" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="I217" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="J217" t="n">
-        <v>5.96</v>
-      </c>
-      <c r="K217" t="n">
-        <v>1</v>
-      </c>
-      <c r="L217" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="s">
-        <v>59</v>
-      </c>
-      <c r="B218" t="s">
-        <v>15</v>
-      </c>
-      <c r="C218" t="n">
-        <v>169.01</v>
-      </c>
-      <c r="D218" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="E218" t="n">
-        <v>13.72</v>
-      </c>
-      <c r="F218" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="G218" t="n">
-        <v>-0.11</v>
-      </c>
-      <c r="H218" t="n">
-        <v>-1.84</v>
-      </c>
-      <c r="I218" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="J218" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="K218" t="n">
-        <v>0</v>
-      </c>
-      <c r="L218" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="s">
-        <v>59</v>
-      </c>
-      <c r="B219" t="s">
-        <v>18</v>
-      </c>
-      <c r="C219" t="n">
-        <v>175.86</v>
-      </c>
-      <c r="D219" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="E219" t="n">
-        <v>127.3</v>
-      </c>
-      <c r="F219" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="G219" t="n">
-        <v>-0.48</v>
-      </c>
-      <c r="H219" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="I219" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="J219" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="K219" t="n">
-        <v>0</v>
-      </c>
-      <c r="L219" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="s">
-        <v>59</v>
-      </c>
-      <c r="B220" t="s">
-        <v>16</v>
-      </c>
-      <c r="C220" t="n">
-        <v>129.83</v>
-      </c>
-      <c r="D220" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="E220" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="F220" t="n">
-        <v>0</v>
-      </c>
-      <c r="G220" t="n">
-        <v>2</v>
-      </c>
-      <c r="H220" t="n">
-        <v>-0.29</v>
-      </c>
-      <c r="I220" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="J220" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="K220" t="n">
-        <v>1</v>
-      </c>
-      <c r="L220" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="s">
-        <v>59</v>
-      </c>
-      <c r="B221" t="s">
-        <v>19</v>
-      </c>
-      <c r="C221" t="n">
-        <v>178.31</v>
-      </c>
-      <c r="D221" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="E221"/>
-      <c r="F221"/>
-      <c r="G221" t="n">
-        <v>-0.61</v>
-      </c>
-      <c r="H221" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="I221"/>
-      <c r="J221" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="K221" t="n">
-        <v>0</v>
-      </c>
-      <c r="L221" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="s">
-        <v>59</v>
-      </c>
-      <c r="B222" t="s">
-        <v>13</v>
-      </c>
-      <c r="C222" t="n">
-        <v>178.31</v>
-      </c>
-      <c r="D222" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="E222" t="n">
-        <v>346898.74</v>
-      </c>
-      <c r="F222" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="G222" t="n">
-        <v>-0.61</v>
-      </c>
-      <c r="H222" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="I222" t="n">
-        <v>-1.79</v>
-      </c>
-      <c r="J222" t="n">
-        <v>-1.76</v>
-      </c>
-      <c r="K222" t="n">
-        <v>0</v>
-      </c>
-      <c r="L222" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="s">
-        <v>59</v>
-      </c>
-      <c r="B223" t="s">
-        <v>17</v>
-      </c>
-      <c r="C223" t="n">
-        <v>170.47</v>
-      </c>
-      <c r="D223" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="E223" t="n">
-        <v>33.01</v>
-      </c>
-      <c r="F223" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G223" t="n">
-        <v>-0.19</v>
-      </c>
-      <c r="H223" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="I223" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="J223" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="K223" t="n">
-        <v>0</v>
-      </c>
-      <c r="L223" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
